--- a/Stock Selection/tickers_used.xlsx
+++ b/Stock Selection/tickers_used.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\RodWal-Capital-Insights\Stock Selection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7ABB6E9C-814E-4AC9-A54D-E2D21FC00A64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B914D7C-64B1-48BB-A434-BA8DBE28D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="99">
   <si>
     <t>Chapter</t>
   </si>
@@ -125,6 +125,9 @@
     <t>GC=F</t>
   </si>
   <si>
+    <t>Error: single positional indexer is out-of-bounds</t>
+  </si>
+  <si>
     <t>Unknown</t>
   </si>
   <si>
@@ -297,6 +300,36 @@
   </si>
   <si>
     <t>INTERNAL_ACCOUNT</t>
+  </si>
+  <si>
+    <t>HCA</t>
+  </si>
+  <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>MMM</t>
+  </si>
+  <si>
+    <t>PLTR</t>
+  </si>
+  <si>
+    <t>APTV</t>
+  </si>
+  <si>
+    <t>YUMC</t>
+  </si>
+  <si>
+    <t>PCG</t>
+  </si>
+  <si>
+    <t>JKS</t>
+  </si>
+  <si>
+    <t>SWI.US</t>
+  </si>
+  <si>
+    <t>CSIQ</t>
   </si>
 </sst>
 </file>
@@ -659,7 +692,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O56"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -770,10 +803,10 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>107.32758</v>
+        <v>107.319534</v>
       </c>
       <c r="H3">
-        <v>25.9375</v>
+        <v>25.935555000000001</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -838,7 +871,7 @@
         <v>6.17</v>
       </c>
       <c r="O4">
-        <v>63.310265281324462</v>
+        <v>63.310262996077803</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -926,7 +959,7 @@
         <v>3.82</v>
       </c>
       <c r="O6">
-        <v>21.31187285917801</v>
+        <v>21.31187017342349</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -980,14 +1013,14 @@
       <c r="C8" t="s">
         <v>29</v>
       </c>
-      <c r="D8">
-        <v>3363.60009765625</v>
+      <c r="D8" t="s">
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
@@ -1013,8 +1046,8 @@
       <c r="N8" t="s">
         <v>17</v>
       </c>
-      <c r="O8">
-        <v>18.385154558496271</v>
+      <c r="O8" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -1022,13 +1055,13 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9">
         <v>17.739999771118161</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9">
         <v>293</v>
@@ -1058,7 +1091,7 @@
         <v>1.4</v>
       </c>
       <c r="O9">
-        <v>43.554623070245263</v>
+        <v>43.554617681699511</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1066,7 +1099,7 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10">
         <v>107.370002746582</v>
@@ -1102,7 +1135,7 @@
         <v>7.43</v>
       </c>
       <c r="O10">
-        <v>27.41862311789248</v>
+        <v>27.41862315068677</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1110,7 +1143,7 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11">
         <v>131.28999328613281</v>
@@ -1146,7 +1179,7 @@
         <v>4.12</v>
       </c>
       <c r="O11">
-        <v>59.357584357307687</v>
+        <v>59.357581960677471</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1154,13 +1187,13 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12">
         <v>67.760002136230469</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12">
         <v>334</v>
@@ -1190,7 +1223,7 @@
         <v>3.68</v>
       </c>
       <c r="O12">
-        <v>29.58863788761473</v>
+        <v>29.588645725501209</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1198,7 +1231,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13">
         <v>22.10000038146973</v>
@@ -1234,7 +1267,7 @@
         <v>2.27</v>
       </c>
       <c r="O13">
-        <v>24.945068566312891</v>
+        <v>24.945068324670881</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1242,7 +1275,7 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14">
         <v>157.50999450683591</v>
@@ -1278,7 +1311,7 @@
         <v>9.69</v>
       </c>
       <c r="O14">
-        <v>48.80821519569097</v>
+        <v>48.808218959274669</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1286,7 +1319,7 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15">
         <v>195.27000427246091</v>
@@ -1322,7 +1355,7 @@
         <v>8.31</v>
       </c>
       <c r="O15">
-        <v>33.141225535154447</v>
+        <v>33.141226767082777</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -1330,7 +1363,7 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16">
         <v>129.3399963378906</v>
@@ -1366,21 +1399,21 @@
         <v>8.6300000000000008</v>
       </c>
       <c r="O16">
-        <v>19.73413524376193</v>
+        <v>19.734136344914148</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D17">
         <v>353.54000854492188</v>
       </c>
       <c r="E17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F17">
         <v>67</v>
@@ -1410,7 +1443,7 @@
         <v>12.66</v>
       </c>
       <c r="O17">
-        <v>22.10971610564506</v>
+        <v>22.109717700659509</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -1418,7 +1451,7 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18">
         <v>145.3800048828125</v>
@@ -1454,7 +1487,7 @@
         <v>12.23</v>
       </c>
       <c r="O18">
-        <v>43.532180305958697</v>
+        <v>43.53218655984147</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -1462,13 +1495,13 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19">
         <v>145.44999694824219</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19">
         <v>195</v>
@@ -1506,7 +1539,7 @@
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20">
         <v>136.69000244140619</v>
@@ -1542,7 +1575,7 @@
         <v>11.11</v>
       </c>
       <c r="O20">
-        <v>25.79231292718579</v>
+        <v>25.79230976342166</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1550,13 +1583,13 @@
         <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21">
         <v>479</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F21">
         <v>271</v>
@@ -1594,7 +1627,7 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22">
         <v>450.17999267578119</v>
@@ -1630,21 +1663,21 @@
         <v>14.95</v>
       </c>
       <c r="O22">
-        <v>25.781858850179859</v>
+        <v>25.781863764818549</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23">
         <v>563.58001708984375</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23">
         <v>54</v>
@@ -1674,7 +1707,7 @@
         <v>16.38</v>
       </c>
       <c r="O23">
-        <v>21.2751429549173</v>
+        <v>21.27514550792371</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -1682,13 +1715,13 @@
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24">
         <v>102.879997253418</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24">
         <v>362</v>
@@ -1718,7 +1751,7 @@
         <v>5.89</v>
       </c>
       <c r="O24">
-        <v>19.656869591453731</v>
+        <v>19.65686994671934</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -1726,7 +1759,7 @@
         <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25">
         <v>96.339996337890625</v>
@@ -1762,7 +1795,7 @@
         <v>2.72</v>
       </c>
       <c r="O25">
-        <v>24.09802726747127</v>
+        <v>24.098028023701101</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -1770,7 +1803,7 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D26">
         <v>732.489990234375</v>
@@ -1806,7 +1839,7 @@
         <v>26.7</v>
       </c>
       <c r="O26">
-        <v>48.76425576772759</v>
+        <v>48.764259272210182</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -1814,7 +1847,7 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27">
         <v>36.520000457763672</v>
@@ -1858,13 +1891,13 @@
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D28">
         <v>116.4899978637695</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F28">
         <v>359</v>
@@ -1894,7 +1927,7 @@
         <v>6.34</v>
       </c>
       <c r="O28">
-        <v>18.404550300892819</v>
+        <v>18.404557627172561</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -1902,7 +1935,7 @@
         <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D29">
         <v>141.55000305175781</v>
@@ -1938,21 +1971,21 @@
         <v>7.63</v>
       </c>
       <c r="O29">
-        <v>19.743231060055049</v>
+        <v>19.743229149536379</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D30">
         <v>21.129999160766602</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F30">
         <v>544</v>
@@ -1990,13 +2023,13 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D31">
         <v>168.4700012207031</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31">
         <v>50</v>
@@ -2026,7 +2059,7 @@
         <v>8.9600000000000009</v>
       </c>
       <c r="O31">
-        <v>31.4740836589251</v>
+        <v>31.474088422259349</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -2034,7 +2067,7 @@
         <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D32">
         <v>16.85000038146973</v>
@@ -2070,7 +2103,7 @@
         <v>2.75</v>
       </c>
       <c r="O32">
-        <v>51.371775149357653</v>
+        <v>51.371778338458142</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2078,7 +2111,7 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D33">
         <v>191.97999572753909</v>
@@ -2122,13 +2155,13 @@
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D34">
         <v>43.669998168945313</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F34">
         <v>366</v>
@@ -2158,21 +2191,21 @@
         <v>2.63</v>
       </c>
       <c r="O34">
-        <v>19.77101992297986</v>
+        <v>19.771024002747499</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D35">
         <v>41.569999694824219</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F35">
         <v>3668</v>
@@ -2202,7 +2235,7 @@
         <v>5.9</v>
       </c>
       <c r="O35">
-        <v>31.4946740521438</v>
+        <v>31.656146351618791</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -2210,7 +2243,7 @@
         <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D36">
         <v>59.740001678466797</v>
@@ -2246,21 +2279,21 @@
         <v>5.35</v>
       </c>
       <c r="O36">
-        <v>19.385074239325782</v>
+        <v>19.385087621465789</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D37">
         <v>13.26500034332275</v>
       </c>
       <c r="E37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F37">
         <v>528</v>
@@ -2290,21 +2323,21 @@
         <v>0.94</v>
       </c>
       <c r="O37">
-        <v>30.66095765866223</v>
+        <v>30.660960171448391</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D38">
         <v>17.64999961853027</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F38">
         <v>240</v>
@@ -2339,16 +2372,16 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D39">
         <v>15.14000034332275</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F39">
         <v>270</v>
@@ -2383,13 +2416,13 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2424,16 +2457,16 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D41">
         <v>22.29000091552734</v>
       </c>
       <c r="E41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F41" t="s">
         <v>17</v>
@@ -2463,8 +2496,7 @@
         <v>17</v>
       </c>
       <c r="O41">
-        <f>D41</f>
-        <v>22.29000091552734</v>
+        <v>178.0123664639892</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -2472,7 +2504,7 @@
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D42">
         <v>2.910000085830688</v>
@@ -2516,13 +2548,13 @@
         <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D43">
         <v>19.222000122070309</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F43" t="s">
         <v>17</v>
@@ -2557,16 +2589,16 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D44">
         <v>6.0819997787475586</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2601,16 +2633,16 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D45">
         <v>6.2369999885559082</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2645,16 +2677,16 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D46">
         <v>72.154998779296875</v>
       </c>
       <c r="E46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F46">
         <v>310</v>
@@ -2684,21 +2716,21 @@
         <v>17</v>
       </c>
       <c r="O46">
-        <v>14.013088892641701</v>
+        <v>14.01307295241938</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D47">
         <v>47.799999237060547</v>
       </c>
       <c r="E47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F47">
         <v>313</v>
@@ -2728,21 +2760,21 @@
         <v>17</v>
       </c>
       <c r="O47">
-        <v>18.619332640195051</v>
+        <v>18.619324203974081</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C48" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D48">
         <v>32.979999542236328</v>
       </c>
       <c r="E48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F48">
         <v>613</v>
@@ -2777,16 +2809,16 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D49">
         <v>579.1099853515625</v>
       </c>
       <c r="E49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F49">
         <v>129</v>
@@ -2816,21 +2848,21 @@
         <v>17</v>
       </c>
       <c r="O49">
-        <v>20.405476502245659</v>
+        <v>20.405477707469711</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D50">
         <v>51.520000457763672</v>
       </c>
       <c r="E50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F50" t="s">
         <v>17</v>
@@ -2865,16 +2897,16 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D51">
         <v>15.314200401306151</v>
       </c>
       <c r="E51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F51" t="s">
         <v>17</v>
@@ -2912,13 +2944,13 @@
         <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D52">
         <v>142.55000305175781</v>
       </c>
       <c r="E52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F52" t="s">
         <v>17</v>
@@ -2956,13 +2988,13 @@
         <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -2997,16 +3029,16 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D54">
         <v>20.114999771118161</v>
       </c>
       <c r="E54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -3041,16 +3073,16 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D55">
         <v>72.19000244140625</v>
       </c>
       <c r="E55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F55">
         <v>368</v>
@@ -3080,21 +3112,21 @@
         <v>17</v>
       </c>
       <c r="O55">
-        <v>5.3385344280682547</v>
+        <v>5.338531138389059</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -3125,6 +3157,402 @@
       </c>
       <c r="O56" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" t="s">
+        <v>89</v>
+      </c>
+      <c r="D57">
+        <v>376.58999633789063</v>
+      </c>
+      <c r="E57" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57">
+        <v>76</v>
+      </c>
+      <c r="G57">
+        <v>16.722470000000001</v>
+      </c>
+      <c r="H57">
+        <v>15.339715</v>
+      </c>
+      <c r="I57" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57">
+        <v>19.863</v>
+      </c>
+      <c r="K57">
+        <v>5778999808</v>
+      </c>
+      <c r="L57">
+        <v>8.0729203322391978</v>
+      </c>
+      <c r="M57">
+        <v>22.52</v>
+      </c>
+      <c r="N57">
+        <v>24.55</v>
+      </c>
+      <c r="O57">
+        <v>28.723445410094161</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58">
+        <v>147.6199951171875</v>
+      </c>
+      <c r="E58" t="s">
+        <v>90</v>
+      </c>
+      <c r="F58">
+        <v>198</v>
+      </c>
+      <c r="G58">
+        <v>18.383562000000001</v>
+      </c>
+      <c r="H58">
+        <v>18.686074999999999</v>
+      </c>
+      <c r="I58" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58">
+        <v>21.734999999999999</v>
+      </c>
+      <c r="K58">
+        <v>4419999744</v>
+      </c>
+      <c r="L58">
+        <v>18.031248104515921</v>
+      </c>
+      <c r="M58">
+        <v>8.0299999999999994</v>
+      </c>
+      <c r="N58">
+        <v>7.9</v>
+      </c>
+      <c r="O58">
+        <v>36.125455465902533</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" t="s">
+        <v>92</v>
+      </c>
+      <c r="D59">
+        <v>123.30999755859381</v>
+      </c>
+      <c r="E59" t="s">
+        <v>18</v>
+      </c>
+      <c r="F59" t="s">
+        <v>17</v>
+      </c>
+      <c r="G59">
+        <v>536.13043000000005</v>
+      </c>
+      <c r="H59">
+        <v>262.36169999999998</v>
+      </c>
+      <c r="I59" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59">
+        <v>13.976000000000001</v>
+      </c>
+      <c r="K59">
+        <v>570691008</v>
+      </c>
+      <c r="L59">
+        <v>18.32059821851664</v>
+      </c>
+      <c r="M59">
+        <v>0.23</v>
+      </c>
+      <c r="N59">
+        <v>0.47</v>
+      </c>
+      <c r="O59">
+        <v>72.49964215012254</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>21</v>
+      </c>
+      <c r="C60" t="s">
+        <v>93</v>
+      </c>
+      <c r="D60">
+        <v>66.05999755859375</v>
+      </c>
+      <c r="E60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" t="s">
+        <v>17</v>
+      </c>
+      <c r="G60">
+        <v>10.794117</v>
+      </c>
+      <c r="H60">
+        <v>9.4641830000000002</v>
+      </c>
+      <c r="I60" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60">
+        <v>15.811999999999999</v>
+      </c>
+      <c r="K60">
+        <v>1558000000</v>
+      </c>
+      <c r="L60">
+        <v>7.9340020612451809</v>
+      </c>
+      <c r="M60">
+        <v>6.12</v>
+      </c>
+      <c r="N60">
+        <v>6.98</v>
+      </c>
+      <c r="O60">
+        <v>40.483710644065383</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>21</v>
+      </c>
+      <c r="C61" t="s">
+        <v>94</v>
+      </c>
+      <c r="D61">
+        <v>42.619998931884773</v>
+      </c>
+      <c r="E61" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61">
+        <v>225</v>
+      </c>
+      <c r="G61">
+        <v>17.832633999999999</v>
+      </c>
+      <c r="H61">
+        <v>16.519380000000002</v>
+      </c>
+      <c r="I61" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61">
+        <v>15.000999999999999</v>
+      </c>
+      <c r="K61">
+        <v>916000000</v>
+      </c>
+      <c r="L61">
+        <v>8.087585993712608</v>
+      </c>
+      <c r="M61">
+        <v>2.39</v>
+      </c>
+      <c r="N61">
+        <v>2.58</v>
+      </c>
+      <c r="O61">
+        <v>41.850081042200891</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" t="s">
+        <v>95</v>
+      </c>
+      <c r="D62">
+        <v>17.04999923706055</v>
+      </c>
+      <c r="E62" t="s">
+        <v>37</v>
+      </c>
+      <c r="F62">
+        <v>59</v>
+      </c>
+      <c r="G62">
+        <v>15.642200000000001</v>
+      </c>
+      <c r="H62">
+        <v>11.520269000000001</v>
+      </c>
+      <c r="I62" t="s">
+        <v>17</v>
+      </c>
+      <c r="J62">
+        <v>38.176997999999998</v>
+      </c>
+      <c r="K62">
+        <v>2350000128</v>
+      </c>
+      <c r="L62">
+        <v>9.5758125530442939</v>
+      </c>
+      <c r="M62">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="N62">
+        <v>1.48</v>
+      </c>
+      <c r="O62">
+        <v>26.342930044731371</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" t="s">
+        <v>96</v>
+      </c>
+      <c r="D63">
+        <v>18.319999694824219</v>
+      </c>
+      <c r="E63" t="s">
+        <v>18</v>
+      </c>
+      <c r="F63">
+        <v>1638</v>
+      </c>
+      <c r="G63" t="s">
+        <v>17</v>
+      </c>
+      <c r="H63">
+        <v>9.4922284999999995</v>
+      </c>
+      <c r="I63" t="s">
+        <v>17</v>
+      </c>
+      <c r="J63">
+        <v>3.5609999999999999</v>
+      </c>
+      <c r="K63">
+        <v>-1873734016</v>
+      </c>
+      <c r="L63">
+        <v>-2.255997845024639</v>
+      </c>
+      <c r="M63">
+        <v>-5</v>
+      </c>
+      <c r="N63">
+        <v>1.93</v>
+      </c>
+      <c r="O63">
+        <v>74.665666684871098</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>24</v>
+      </c>
+      <c r="C64" t="s">
+        <v>97</v>
+      </c>
+      <c r="D64" t="s">
+        <v>85</v>
+      </c>
+      <c r="E64" t="s">
+        <v>31</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64" t="s">
+        <v>17</v>
+      </c>
+      <c r="H64" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" t="s">
+        <v>17</v>
+      </c>
+      <c r="J64" t="s">
+        <v>17</v>
+      </c>
+      <c r="K64" t="s">
+        <v>17</v>
+      </c>
+      <c r="L64" t="s">
+        <v>17</v>
+      </c>
+      <c r="M64" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64" t="s">
+        <v>17</v>
+      </c>
+      <c r="O64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>18</v>
+      </c>
+      <c r="C65" t="s">
+        <v>98</v>
+      </c>
+      <c r="D65">
+        <v>9.8000001907348633</v>
+      </c>
+      <c r="E65" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" t="s">
+        <v>17</v>
+      </c>
+      <c r="H65">
+        <v>3.3910033999999998</v>
+      </c>
+      <c r="I65" t="s">
+        <v>17</v>
+      </c>
+      <c r="J65">
+        <v>8.8730000000000011</v>
+      </c>
+      <c r="K65">
+        <v>-10272000</v>
+      </c>
+      <c r="L65">
+        <v>-0.17526250063880719</v>
+      </c>
+      <c r="M65">
+        <v>-0.34</v>
+      </c>
+      <c r="N65">
+        <v>2.89</v>
+      </c>
+      <c r="O65">
+        <v>83.449829096832588</v>
       </c>
     </row>
   </sheetData>

--- a/Stock Selection/tickers_used.xlsx
+++ b/Stock Selection/tickers_used.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\RodWal-Capital-Insights\Stock Selection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B914D7C-64B1-48BB-A434-BA8DBE28D955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41323AA1-A6F8-4B1E-9C7F-0060ABFB309E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="98">
   <si>
     <t>Chapter</t>
   </si>
@@ -123,9 +123,6 @@
   </si>
   <si>
     <t>GC=F</t>
-  </si>
-  <si>
-    <t>Error: single positional indexer is out-of-bounds</t>
   </si>
   <si>
     <t>Unknown</t>
@@ -348,6 +345,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -750,7 +748,7 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>29.79999923706055</v>
+        <v>30.20000076293945</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -759,10 +757,10 @@
         <v>17</v>
       </c>
       <c r="G2">
-        <v>2.5823223999999998</v>
+        <v>2.5834047999999998</v>
       </c>
       <c r="H2">
-        <v>-4.9013156999999996</v>
+        <v>-4.9671054000000003</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -777,13 +775,13 @@
         <v>1798.258469015796</v>
       </c>
       <c r="M2">
-        <v>11.54</v>
+        <v>11.69</v>
       </c>
       <c r="N2">
         <v>-6.08</v>
       </c>
       <c r="O2">
-        <v>61.1174732254267</v>
+        <v>56.482368320154073</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -794,7 +792,7 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>186.75</v>
+        <v>187.46000671386719</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -803,16 +801,16 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>107.319534</v>
+        <v>107.735634</v>
       </c>
       <c r="H3">
-        <v>25.935555000000001</v>
+        <v>26.036111999999999</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
       </c>
       <c r="J3">
-        <v>16.079001000000002</v>
+        <v>14.087</v>
       </c>
       <c r="K3">
         <v>1237799936</v>
@@ -827,7 +825,7 @@
         <v>7.2</v>
       </c>
       <c r="O3">
-        <v>36.618630263603222</v>
+        <v>36.359735554983807</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -838,7 +836,7 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>228.7200012207031</v>
+        <v>235.6499938964844</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -847,10 +845,10 @@
         <v>103</v>
       </c>
       <c r="G4">
-        <v>106.38139</v>
+        <v>106.14864</v>
       </c>
       <c r="H4">
-        <v>37.069690000000001</v>
+        <v>38.192867</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
@@ -865,13 +863,13 @@
         <v>19.066918134984039</v>
       </c>
       <c r="M4">
-        <v>2.15</v>
+        <v>2.2200000000000002</v>
       </c>
       <c r="N4">
         <v>6.17</v>
       </c>
       <c r="O4">
-        <v>63.310262996077803</v>
+        <v>63.370782175879469</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -882,7 +880,7 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>31.54000091552734</v>
+        <v>32.349998474121087</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -891,10 +889,10 @@
         <v>17</v>
       </c>
       <c r="G5">
-        <v>29.476635000000002</v>
+        <v>30.233643000000001</v>
       </c>
       <c r="H5">
-        <v>10.548495000000001</v>
+        <v>10.819397</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -915,7 +913,7 @@
         <v>2.99</v>
       </c>
       <c r="O5">
-        <v>43.604853827541383</v>
+        <v>43.610441392346402</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -926,19 +924,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>28.995000839233398</v>
+        <v>29.344999313354489</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
       </c>
       <c r="F6">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="G6">
-        <v>14.945876</v>
+        <v>15.204663</v>
       </c>
       <c r="H6">
-        <v>7.5903143999999996</v>
+        <v>7.6819369999999996</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -953,13 +951,13 @@
         <v>4.8087837924487724</v>
       </c>
       <c r="M6">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="N6">
         <v>3.82</v>
       </c>
       <c r="O6">
-        <v>21.31187017342349</v>
+        <v>21.330085944535611</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -970,7 +968,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>158.3800048828125</v>
+        <v>155.72999572753909</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -979,10 +977,10 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>13.456244</v>
+        <v>13.459809999999999</v>
       </c>
       <c r="H7">
-        <v>7.5925216999999998</v>
+        <v>7.4654837000000001</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -997,13 +995,13 @@
         <v>29.716643554944859</v>
       </c>
       <c r="M7">
-        <v>11.77</v>
+        <v>11.57</v>
       </c>
       <c r="N7">
         <v>20.86</v>
       </c>
       <c r="O7">
-        <v>60.409598728599512</v>
+        <v>60.412521133559487</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -1013,14 +1011,14 @@
       <c r="C8" t="s">
         <v>29</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8">
+        <v>3305</v>
+      </c>
+      <c r="E8" t="s">
         <v>30</v>
       </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+      <c r="F8" t="s">
+        <v>17</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
@@ -1046,8 +1044,8 @@
       <c r="N8" t="s">
         <v>17</v>
       </c>
-      <c r="O8" t="s">
-        <v>17</v>
+      <c r="O8">
+        <v>18.46454688434325</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -1055,22 +1053,22 @@
         <v>21</v>
       </c>
       <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9">
+        <v>18.389999389648441</v>
+      </c>
+      <c r="E9" t="s">
         <v>32</v>
-      </c>
-      <c r="D9">
-        <v>17.739999771118161</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
       </c>
       <c r="F9">
         <v>293</v>
       </c>
       <c r="G9">
-        <v>19.711110999999999</v>
+        <v>19.774193</v>
       </c>
       <c r="H9">
-        <v>12.671429</v>
+        <v>13.135714999999999</v>
       </c>
       <c r="I9" t="s">
         <v>17</v>
@@ -1085,13 +1083,13 @@
         <v>5.6327027632036586</v>
       </c>
       <c r="M9">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="N9">
         <v>1.4</v>
       </c>
       <c r="O9">
-        <v>43.554617681699511</v>
+        <v>43.657529423813877</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1099,10 +1097,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10">
-        <v>107.370002746582</v>
+        <v>109.0899963378906</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -1111,10 +1109,10 @@
         <v>294</v>
       </c>
       <c r="G10">
-        <v>22.556723000000002</v>
+        <v>22.585920000000002</v>
       </c>
       <c r="H10">
-        <v>14.450875</v>
+        <v>14.682368</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -1129,13 +1127,13 @@
         <v>20.75865694250961</v>
       </c>
       <c r="M10">
-        <v>4.76</v>
+        <v>4.83</v>
       </c>
       <c r="N10">
         <v>7.43</v>
       </c>
       <c r="O10">
-        <v>27.41862315068677</v>
+        <v>27.298737286424331</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1143,10 +1141,10 @@
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11">
-        <v>131.28999328613281</v>
+        <v>135.5</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -1155,10 +1153,10 @@
         <v>3</v>
       </c>
       <c r="G11">
-        <v>44.656460000000003</v>
+        <v>44.572369999999999</v>
       </c>
       <c r="H11">
-        <v>31.866505</v>
+        <v>32.888350000000003</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -1173,13 +1171,13 @@
         <v>55.848023297201912</v>
       </c>
       <c r="M11">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
       <c r="N11">
         <v>4.12</v>
       </c>
       <c r="O11">
-        <v>59.357581960677471</v>
+        <v>59.037127409653422</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1187,22 +1185,22 @@
         <v>24</v>
       </c>
       <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12">
+        <v>68.040000915527344</v>
+      </c>
+      <c r="E12" t="s">
         <v>36</v>
-      </c>
-      <c r="D12">
-        <v>67.760002136230469</v>
-      </c>
-      <c r="E12" t="s">
-        <v>37</v>
       </c>
       <c r="F12">
         <v>334</v>
       </c>
       <c r="G12">
-        <v>25.378277000000001</v>
+        <v>25.388059999999999</v>
       </c>
       <c r="H12">
-        <v>18.413043999999999</v>
+        <v>18.489129999999999</v>
       </c>
       <c r="I12" t="s">
         <v>17</v>
@@ -1217,13 +1215,13 @@
         <v>21.809331679631502</v>
       </c>
       <c r="M12">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="N12">
         <v>3.68</v>
       </c>
       <c r="O12">
-        <v>29.588645725501209</v>
+        <v>29.566196065798561</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1231,22 +1229,22 @@
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13">
-        <v>22.10000038146973</v>
+        <v>22.20000076293945</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
       </c>
       <c r="F13">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G13">
-        <v>13.47561</v>
+        <v>13.536586</v>
       </c>
       <c r="H13">
-        <v>9.7356829999999999</v>
+        <v>9.7797365000000003</v>
       </c>
       <c r="I13" t="s">
         <v>17</v>
@@ -1267,7 +1265,7 @@
         <v>2.27</v>
       </c>
       <c r="O13">
-        <v>24.945068324670881</v>
+        <v>24.94803089464801</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1275,10 +1273,10 @@
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14">
-        <v>157.50999450683591</v>
+        <v>161.83000183105469</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -1287,10 +1285,10 @@
         <v>117</v>
       </c>
       <c r="G14">
-        <v>19.161798000000001</v>
+        <v>19.151479999999999</v>
       </c>
       <c r="H14">
-        <v>16.254902000000001</v>
+        <v>16.700724000000001</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1305,13 +1303,13 @@
         <v>24.059240782505299</v>
       </c>
       <c r="M14">
-        <v>8.2200000000000006</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="N14">
         <v>9.69</v>
       </c>
       <c r="O14">
-        <v>48.808218959274669</v>
+        <v>48.890279759235497</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1319,10 +1317,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15">
-        <v>195.27000427246091</v>
+        <v>200.21000671386719</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -1331,10 +1329,10 @@
         <v>53</v>
       </c>
       <c r="G15">
-        <v>30.415887999999999</v>
+        <v>30.380880000000001</v>
       </c>
       <c r="H15">
-        <v>23.498194000000002</v>
+        <v>24.092659000000001</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1349,13 +1347,13 @@
         <v>24.301263745783849</v>
       </c>
       <c r="M15">
-        <v>6.42</v>
+        <v>6.59</v>
       </c>
       <c r="N15">
         <v>8.31</v>
       </c>
       <c r="O15">
-        <v>33.141226767082777</v>
+        <v>33.236151997598753</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -1363,10 +1361,10 @@
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16">
-        <v>129.3399963378906</v>
+        <v>131.3699951171875</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
@@ -1375,10 +1373,10 @@
         <v>440.00000000000011</v>
       </c>
       <c r="G16">
-        <v>19.020588</v>
+        <v>19.011578</v>
       </c>
       <c r="H16">
-        <v>14.987253000000001</v>
+        <v>15.222479</v>
       </c>
       <c r="I16" t="s">
         <v>17</v>
@@ -1393,36 +1391,36 @@
         <v>10.23786431925341</v>
       </c>
       <c r="M16">
-        <v>6.8</v>
+        <v>6.91</v>
       </c>
       <c r="N16">
         <v>8.6300000000000008</v>
       </c>
       <c r="O16">
-        <v>19.734136344914148</v>
+        <v>19.64583858046521</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
         <v>42</v>
       </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
       <c r="D17">
-        <v>353.54000854492188</v>
+        <v>359.29998779296881</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17">
         <v>67</v>
       </c>
       <c r="G17">
-        <v>35.60322</v>
+        <v>35.574252999999999</v>
       </c>
       <c r="H17">
-        <v>27.925750000000001</v>
+        <v>28.380725999999999</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
@@ -1437,13 +1435,13 @@
         <v>52.210202623591513</v>
       </c>
       <c r="M17">
-        <v>9.93</v>
+        <v>10.1</v>
       </c>
       <c r="N17">
         <v>12.66</v>
       </c>
       <c r="O17">
-        <v>22.109717700659509</v>
+        <v>22.117081359639869</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -1451,10 +1449,10 @@
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D18">
-        <v>145.3800048828125</v>
+        <v>148.6300048828125</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
@@ -1463,10 +1461,10 @@
         <v>245</v>
       </c>
       <c r="G18">
-        <v>14.834694000000001</v>
+        <v>14.833333</v>
       </c>
       <c r="H18">
-        <v>11.887162999999999</v>
+        <v>12.152903999999999</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1481,13 +1479,13 @@
         <v>26.04881181510946</v>
       </c>
       <c r="M18">
-        <v>9.8000000000000007</v>
+        <v>10.02</v>
       </c>
       <c r="N18">
         <v>12.23</v>
       </c>
       <c r="O18">
-        <v>43.53218655984147</v>
+        <v>43.573196246127658</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -1495,22 +1493,22 @@
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D19">
-        <v>145.44999694824219</v>
+        <v>144.0899963378906</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19">
         <v>195</v>
       </c>
       <c r="G19">
-        <v>28.974104000000001</v>
+        <v>28.991952999999999</v>
       </c>
       <c r="H19">
-        <v>23.922696999999999</v>
+        <v>23.699013000000001</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1525,13 +1523,13 @@
         <v>18.415610746600951</v>
       </c>
       <c r="M19">
-        <v>5.0199999999999996</v>
+        <v>4.97</v>
       </c>
       <c r="N19">
         <v>6.08</v>
       </c>
       <c r="O19">
-        <v>22.128176176470379</v>
+        <v>22.10877271740592</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -1539,10 +1537,10 @@
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D20">
-        <v>136.69000244140619</v>
+        <v>139.41999816894531</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
@@ -1551,10 +1549,10 @@
         <v>234</v>
       </c>
       <c r="G20">
-        <v>14.403584</v>
+        <v>14.691254000000001</v>
       </c>
       <c r="H20">
-        <v>12.303331</v>
+        <v>12.549054999999999</v>
       </c>
       <c r="I20" t="s">
         <v>17</v>
@@ -1575,7 +1573,7 @@
         <v>11.11</v>
       </c>
       <c r="O20">
-        <v>25.79230976342166</v>
+        <v>25.837538279320292</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1583,22 +1581,22 @@
         <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21">
-        <v>479</v>
+        <v>481.89999389648438</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G21">
-        <v>19.083666000000001</v>
+        <v>19.168655000000001</v>
       </c>
       <c r="H21">
-        <v>16.466138999999998</v>
+        <v>16.565829999999998</v>
       </c>
       <c r="I21" t="s">
         <v>17</v>
@@ -1613,13 +1611,13 @@
         <v>14.81997561254024</v>
       </c>
       <c r="M21">
-        <v>25.1</v>
+        <v>25.14</v>
       </c>
       <c r="N21">
         <v>29.09</v>
       </c>
       <c r="O21">
-        <v>32.071723913684387</v>
+        <v>32.074653185219127</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -1627,10 +1625,10 @@
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D22">
-        <v>450.17999267578119</v>
+        <v>460.69000244140619</v>
       </c>
       <c r="E22" t="s">
         <v>18</v>
@@ -1639,10 +1637,10 @@
         <v>74</v>
       </c>
       <c r="G22">
-        <v>34.843649999999997</v>
+        <v>34.847957999999998</v>
       </c>
       <c r="H22">
-        <v>30.112375</v>
+        <v>30.815386</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1657,36 +1655,36 @@
         <v>35.789415272465227</v>
       </c>
       <c r="M22">
-        <v>12.92</v>
+        <v>13.22</v>
       </c>
       <c r="N22">
         <v>14.95</v>
       </c>
       <c r="O22">
-        <v>25.781863764818549</v>
+        <v>25.885506196322378</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23">
-        <v>563.58001708984375</v>
+        <v>574.54998779296875</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23">
         <v>54</v>
       </c>
       <c r="G23">
-        <v>39.521740000000001</v>
+        <v>39.515129999999999</v>
       </c>
       <c r="H23">
-        <v>34.406596999999998</v>
+        <v>35.076312999999999</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1701,13 +1699,13 @@
         <v>45.213112751383562</v>
       </c>
       <c r="M23">
-        <v>14.26</v>
+        <v>14.54</v>
       </c>
       <c r="N23">
         <v>16.38</v>
       </c>
       <c r="O23">
-        <v>21.27514550792371</v>
+        <v>21.305040612810259</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -1715,22 +1713,22 @@
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D24">
-        <v>102.879997253418</v>
+        <v>102.9100036621094</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F24">
         <v>362</v>
       </c>
       <c r="G24">
-        <v>19.899419999999999</v>
+        <v>19.866796000000001</v>
       </c>
       <c r="H24">
-        <v>17.466892000000001</v>
+        <v>17.471986999999999</v>
       </c>
       <c r="I24" t="s">
         <v>17</v>
@@ -1745,13 +1743,13 @@
         <v>13.71198897276127</v>
       </c>
       <c r="M24">
-        <v>5.17</v>
+        <v>5.18</v>
       </c>
       <c r="N24">
         <v>5.89</v>
       </c>
       <c r="O24">
-        <v>19.65686994671934</v>
+        <v>19.651102753352479</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -1759,10 +1757,10 @@
         <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D25">
-        <v>96.339996337890625</v>
+        <v>97.580001831054688</v>
       </c>
       <c r="E25" t="s">
         <v>23</v>
@@ -1771,10 +1769,10 @@
         <v>98</v>
       </c>
       <c r="G25">
-        <v>41.170940000000002</v>
+        <v>41.173000000000002</v>
       </c>
       <c r="H25">
-        <v>35.419117</v>
+        <v>35.875</v>
       </c>
       <c r="I25" t="s">
         <v>17</v>
@@ -1789,13 +1787,13 @@
         <v>2.7469543815742412</v>
       </c>
       <c r="M25">
-        <v>2.34</v>
+        <v>2.37</v>
       </c>
       <c r="N25">
         <v>2.72</v>
       </c>
       <c r="O25">
-        <v>24.098028023701101</v>
+        <v>24.113924695476651</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -1803,10 +1801,10 @@
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26">
-        <v>732.489990234375</v>
+        <v>756.78997802734375</v>
       </c>
       <c r="E26" t="s">
         <v>18</v>
@@ -1815,10 +1813,10 @@
         <v>114</v>
       </c>
       <c r="G26">
-        <v>29.241116999999999</v>
+        <v>29.242270999999999</v>
       </c>
       <c r="H26">
-        <v>27.434082</v>
+        <v>28.344193000000001</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1833,13 +1831,13 @@
         <v>28.33459111814113</v>
       </c>
       <c r="M26">
-        <v>25.05</v>
+        <v>25.88</v>
       </c>
       <c r="N26">
         <v>26.7</v>
       </c>
       <c r="O26">
-        <v>48.764259272210182</v>
+        <v>48.739271307499337</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -1847,10 +1845,10 @@
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27">
-        <v>36.520000457763672</v>
+        <v>36.569999694824219</v>
       </c>
       <c r="E27" t="s">
         <v>26</v>
@@ -1859,10 +1857,10 @@
         <v>17</v>
       </c>
       <c r="G27">
-        <v>8.5128199999999996</v>
+        <v>8.5046510000000008</v>
       </c>
       <c r="H27">
-        <v>7.770213</v>
+        <v>7.7808514000000004</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1877,13 +1875,13 @@
         <v>7.9344361198138351</v>
       </c>
       <c r="M27">
-        <v>4.29</v>
+        <v>4.3</v>
       </c>
       <c r="N27">
         <v>4.7</v>
       </c>
       <c r="O27">
-        <v>49.214570980089768</v>
+        <v>48.884813960092302</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -1891,22 +1889,22 @@
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28">
-        <v>116.4899978637695</v>
+        <v>116.379997253418</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28">
         <v>359</v>
       </c>
       <c r="G28">
-        <v>19.350498000000002</v>
+        <v>19.332225999999999</v>
       </c>
       <c r="H28">
-        <v>18.373816000000001</v>
+        <v>18.356466000000001</v>
       </c>
       <c r="I28" t="s">
         <v>17</v>
@@ -1927,7 +1925,7 @@
         <v>6.34</v>
       </c>
       <c r="O28">
-        <v>18.404557627172561</v>
+        <v>18.375187587169581</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -1935,10 +1933,10 @@
         <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D29">
-        <v>141.55000305175781</v>
+        <v>142.8500061035156</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
@@ -1947,10 +1945,10 @@
         <v>356</v>
       </c>
       <c r="G29">
-        <v>19.258505</v>
+        <v>19.278003999999999</v>
       </c>
       <c r="H29">
-        <v>18.551770000000001</v>
+        <v>18.722149999999999</v>
       </c>
       <c r="I29" t="s">
         <v>17</v>
@@ -1965,36 +1963,36 @@
         <v>12.48164484200357</v>
       </c>
       <c r="M29">
-        <v>7.35</v>
+        <v>7.41</v>
       </c>
       <c r="N29">
         <v>7.63</v>
       </c>
       <c r="O29">
-        <v>19.743229149536379</v>
+        <v>19.640844170614599</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30">
-        <v>21.129999160766602</v>
+        <v>21.329999923706051</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30">
         <v>544</v>
       </c>
       <c r="G30">
-        <v>9.4753360000000004</v>
+        <v>9.48</v>
       </c>
       <c r="H30">
-        <v>9.6484009999999998</v>
+        <v>9.7397259999999992</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -2009,13 +2007,13 @@
         <v>25.984840469640911</v>
       </c>
       <c r="M30">
-        <v>2.23</v>
+        <v>2.25</v>
       </c>
       <c r="N30">
         <v>2.19</v>
       </c>
       <c r="O30">
-        <v>28.0276728644027</v>
+        <v>28.040326796780111</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -2023,22 +2021,22 @@
         <v>18</v>
       </c>
       <c r="C31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31">
+        <v>172.8999938964844</v>
+      </c>
+      <c r="E31" t="s">
         <v>57</v>
-      </c>
-      <c r="D31">
-        <v>168.4700012207031</v>
-      </c>
-      <c r="E31" t="s">
-        <v>58</v>
       </c>
       <c r="F31">
         <v>50</v>
       </c>
       <c r="G31">
-        <v>18.802455999999999</v>
+        <v>18.793478</v>
       </c>
       <c r="H31">
-        <v>18.802455999999999</v>
+        <v>19.296875</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -2053,13 +2051,13 @@
         <v>30.856819860861741</v>
       </c>
       <c r="M31">
-        <v>8.9600000000000009</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="N31">
         <v>8.9600000000000009</v>
       </c>
       <c r="O31">
-        <v>31.474088422259349</v>
+        <v>31.57447392820206</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -2067,10 +2065,10 @@
         <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D32">
-        <v>16.85000038146973</v>
+        <v>17.309999465942379</v>
       </c>
       <c r="E32" t="s">
         <v>26</v>
@@ -2079,10 +2077,10 @@
         <v>593</v>
       </c>
       <c r="G32">
-        <v>6.0394269999999999</v>
+        <v>6.0313587000000002</v>
       </c>
       <c r="H32">
-        <v>6.1272729999999997</v>
+        <v>6.2945450000000003</v>
       </c>
       <c r="I32" t="s">
         <v>17</v>
@@ -2097,13 +2095,13 @@
         <v>10.041387718820969</v>
       </c>
       <c r="M32">
-        <v>2.79</v>
+        <v>2.87</v>
       </c>
       <c r="N32">
         <v>2.75</v>
       </c>
       <c r="O32">
-        <v>51.371778338458142</v>
+        <v>51.423452697626203</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2111,10 +2109,10 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D33">
-        <v>191.97999572753909</v>
+        <v>197.67999267578119</v>
       </c>
       <c r="E33" t="s">
         <v>18</v>
@@ -2123,10 +2121,10 @@
         <v>171</v>
       </c>
       <c r="G33">
-        <v>23.102284999999998</v>
+        <v>23.093456</v>
       </c>
       <c r="H33">
-        <v>23.759900999999999</v>
+        <v>24.465344999999999</v>
       </c>
       <c r="I33" t="s">
         <v>17</v>
@@ -2141,13 +2139,13 @@
         <v>41.686769633025442</v>
       </c>
       <c r="M33">
-        <v>8.31</v>
+        <v>8.56</v>
       </c>
       <c r="N33">
         <v>8.08</v>
       </c>
       <c r="O33">
-        <v>46.638653030630437</v>
+        <v>46.723772979619227</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -2155,22 +2153,22 @@
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D34">
-        <v>43.669998168945313</v>
+        <v>43.909999847412109</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F34">
         <v>366</v>
       </c>
       <c r="G34">
-        <v>16.234200000000001</v>
+        <v>16.262962000000002</v>
       </c>
       <c r="H34">
-        <v>16.604559999999999</v>
+        <v>16.695816000000001</v>
       </c>
       <c r="I34" t="s">
         <v>17</v>
@@ -2185,36 +2183,36 @@
         <v>11.435082528811259</v>
       </c>
       <c r="M34">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="N34">
         <v>2.63</v>
       </c>
       <c r="O34">
-        <v>19.771024002747499</v>
+        <v>19.775772900904482</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D35">
-        <v>41.569999694824219</v>
+        <v>42.220001220703118</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F35">
-        <v>3668</v>
+        <v>3611</v>
       </c>
       <c r="G35">
-        <v>6.5879554999999996</v>
+        <v>6.6803800000000004</v>
       </c>
       <c r="H35">
-        <v>7.0457625000000004</v>
+        <v>7.1559324000000002</v>
       </c>
       <c r="I35" t="s">
         <v>17</v>
@@ -2229,13 +2227,13 @@
         <v>28.104146008031432</v>
       </c>
       <c r="M35">
-        <v>6.31</v>
+        <v>6.32</v>
       </c>
       <c r="N35">
         <v>5.9</v>
       </c>
       <c r="O35">
-        <v>31.656146351618791</v>
+        <v>29.778117136617379</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -2243,10 +2241,10 @@
         <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D36">
-        <v>59.740001678466797</v>
+        <v>59.619998931884773</v>
       </c>
       <c r="E36" t="s">
         <v>23</v>
@@ -2255,10 +2253,10 @@
         <v>683</v>
       </c>
       <c r="G36">
-        <v>10.023490000000001</v>
+        <v>10.020168</v>
       </c>
       <c r="H36">
-        <v>11.166356</v>
+        <v>11.143926</v>
       </c>
       <c r="I36" t="s">
         <v>17</v>
@@ -2273,36 +2271,36 @@
         <v>50.301292507937191</v>
       </c>
       <c r="M36">
-        <v>5.96</v>
+        <v>5.95</v>
       </c>
       <c r="N36">
         <v>5.35</v>
       </c>
       <c r="O36">
-        <v>19.385087621465789</v>
+        <v>19.387509952118549</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D37">
-        <v>13.26500034332275</v>
+        <v>13.545000076293951</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F37">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="G37">
-        <v>7.4943504000000001</v>
+        <v>7.6525426000000003</v>
       </c>
       <c r="H37">
-        <v>14.111703</v>
+        <v>14.4095745</v>
       </c>
       <c r="I37" t="s">
         <v>17</v>
@@ -2323,30 +2321,30 @@
         <v>0.94</v>
       </c>
       <c r="O37">
-        <v>30.660960171448391</v>
+        <v>30.676104934717809</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D38">
-        <v>17.64999961853027</v>
+        <v>17.909999847412109</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F38">
         <v>240</v>
       </c>
       <c r="G38">
-        <v>8.7810950000000005</v>
+        <v>8.9104480000000006</v>
       </c>
       <c r="H38">
-        <v>16.809525000000001</v>
+        <v>17.057144000000001</v>
       </c>
       <c r="I38" t="s">
         <v>17</v>
@@ -2367,30 +2365,30 @@
         <v>1.05</v>
       </c>
       <c r="O38">
-        <v>36.089845036897728</v>
+        <v>36.087641615791412</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D39">
-        <v>15.14000034332275</v>
+        <v>15.44999980926514</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F39">
         <v>270</v>
       </c>
       <c r="G39">
-        <v>12.015872999999999</v>
+        <v>12.0703125</v>
       </c>
       <c r="H39">
-        <v>36.926830000000002</v>
+        <v>37.682926000000002</v>
       </c>
       <c r="I39" t="s">
         <v>17</v>
@@ -2405,24 +2403,24 @@
         <v>22.5677633341305</v>
       </c>
       <c r="M39">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="N39">
         <v>0.41</v>
       </c>
       <c r="O39">
-        <v>36.547157672795578</v>
+        <v>36.550201469016137</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" t="s">
         <v>67</v>
       </c>
-      <c r="D40" t="s">
-        <v>68</v>
-      </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2457,16 +2455,16 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" t="s">
         <v>69</v>
       </c>
-      <c r="C41" t="s">
-        <v>70</v>
-      </c>
       <c r="D41">
-        <v>22.29000091552734</v>
+        <v>18.95999908447266</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
         <v>17</v>
@@ -2496,7 +2494,8 @@
         <v>17</v>
       </c>
       <c r="O41">
-        <v>178.0123664639892</v>
+        <f>D41</f>
+        <v>18.95999908447266</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -2504,10 +2503,10 @@
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D42">
-        <v>2.910000085830688</v>
+        <v>2.9900000095367432</v>
       </c>
       <c r="E42" t="s">
         <v>18</v>
@@ -2519,7 +2518,7 @@
         <v>17</v>
       </c>
       <c r="H42">
-        <v>-0.52717393999999995</v>
+        <v>-0.54166669999999995</v>
       </c>
       <c r="I42" t="s">
         <v>17</v>
@@ -2534,13 +2533,13 @@
         <v>-120.67624899812979</v>
       </c>
       <c r="M42">
-        <v>-96</v>
+        <v>-98.64</v>
       </c>
       <c r="N42">
         <v>-5.52</v>
       </c>
       <c r="O42">
-        <v>171.86565863326859</v>
+        <v>171.77474564289861</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -2548,13 +2547,13 @@
         <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D43">
-        <v>19.222000122070309</v>
+        <v>19.264999389648441</v>
       </c>
       <c r="E43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
         <v>17</v>
@@ -2584,21 +2583,21 @@
         <v>17</v>
       </c>
       <c r="O43">
-        <v>14.89446702581613</v>
+        <v>14.918007299961481</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" t="s">
         <v>73</v>
       </c>
-      <c r="C44" t="s">
-        <v>74</v>
-      </c>
       <c r="D44">
-        <v>6.0819997787475586</v>
+        <v>6.0900001525878906</v>
       </c>
       <c r="E44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2628,21 +2627,21 @@
         <v>17</v>
       </c>
       <c r="O44">
-        <v>2.6941869718976328</v>
+        <v>2.7012905395376561</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45">
-        <v>6.2369999885559082</v>
+        <v>6.2420001029968262</v>
       </c>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2672,27 +2671,27 @@
         <v>17</v>
       </c>
       <c r="O45">
-        <v>2.7250838030108131</v>
+        <v>2.729150301069823</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D46">
-        <v>72.154998779296875</v>
+        <v>72.959999084472656</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F46">
         <v>310</v>
       </c>
       <c r="G46">
-        <v>14.852036</v>
+        <v>15.017734000000001</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2716,27 +2715,27 @@
         <v>17</v>
       </c>
       <c r="O46">
-        <v>14.01307295241938</v>
+        <v>14.07923688731044</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D47">
-        <v>47.799999237060547</v>
+        <v>47.630001068115227</v>
       </c>
       <c r="E47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F47">
         <v>313</v>
       </c>
       <c r="G47">
-        <v>15.380974999999999</v>
+        <v>15.326273</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2760,21 +2759,21 @@
         <v>17</v>
       </c>
       <c r="O47">
-        <v>18.619324203974081</v>
+        <v>18.620997635231369</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" t="s">
         <v>78</v>
       </c>
-      <c r="C48" t="s">
-        <v>79</v>
-      </c>
       <c r="D48">
-        <v>32.979999542236328</v>
+        <v>32.709999084472663</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F48">
         <v>613</v>
@@ -2783,7 +2782,7 @@
         <v>17</v>
       </c>
       <c r="H48">
-        <v>8.2864319999999996</v>
+        <v>8.2185930000000003</v>
       </c>
       <c r="I48" t="s">
         <v>17</v>
@@ -2798,33 +2797,33 @@
         <v>-8.9286898337138769</v>
       </c>
       <c r="M48">
-        <v>-1.41</v>
+        <v>-1.4</v>
       </c>
       <c r="N48">
         <v>3.98</v>
       </c>
       <c r="O48">
-        <v>43.360333106517778</v>
+        <v>43.363535234331437</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D49">
-        <v>579.1099853515625</v>
+        <v>591.1500244140625</v>
       </c>
       <c r="E49" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F49">
         <v>129</v>
       </c>
       <c r="G49">
-        <v>25.232693000000001</v>
+        <v>25.757294000000002</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -2848,21 +2847,21 @@
         <v>17</v>
       </c>
       <c r="O49">
-        <v>20.405477707469711</v>
+        <v>20.507394401626321</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D50">
-        <v>51.520000457763672</v>
+        <v>51.595001220703118</v>
       </c>
       <c r="E50" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F50" t="s">
         <v>17</v>
@@ -2892,21 +2891,21 @@
         <v>17</v>
       </c>
       <c r="O50">
-        <v>48.940888547455323</v>
+        <v>48.884896600077823</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C51" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D51">
-        <v>15.314200401306151</v>
+        <v>15.39640045166016</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F51" t="s">
         <v>17</v>
@@ -2936,7 +2935,7 @@
         <v>17</v>
       </c>
       <c r="O51">
-        <v>25.309566032603321</v>
+        <v>25.263358554322309</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -2944,13 +2943,13 @@
         <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D52">
-        <v>142.55000305175781</v>
+        <v>144.3320007324219</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F52" t="s">
         <v>17</v>
@@ -2980,7 +2979,7 @@
         <v>17</v>
       </c>
       <c r="O52">
-        <v>11.118649914109509</v>
+        <v>11.1882302103756</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
@@ -2988,13 +2987,13 @@
         <v>28</v>
       </c>
       <c r="C53" t="s">
+        <v>83</v>
+      </c>
+      <c r="D53" t="s">
         <v>84</v>
       </c>
-      <c r="D53" t="s">
-        <v>85</v>
-      </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -3029,22 +3028,22 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D54">
-        <v>20.114999771118161</v>
+        <v>20.659999847412109</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>30.682176999999999</v>
+        <v>31.513487000000001</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -3068,21 +3067,21 @@
         <v>17</v>
       </c>
       <c r="O54">
-        <v>25.951270089232089</v>
+        <v>26.142747802293378</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D55">
-        <v>72.19000244140625</v>
+        <v>72.529998779296875</v>
       </c>
       <c r="E55" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F55">
         <v>368</v>
@@ -3112,21 +3111,21 @@
         <v>17</v>
       </c>
       <c r="O55">
-        <v>5.338531138389059</v>
+        <v>5.3345531782892728</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C56" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D56" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -3164,10 +3163,10 @@
         <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D57">
-        <v>376.58999633789063</v>
+        <v>378.80999755859381</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -3176,10 +3175,10 @@
         <v>76</v>
       </c>
       <c r="G57">
-        <v>16.722470000000001</v>
+        <v>16.724502999999999</v>
       </c>
       <c r="H57">
-        <v>15.339715</v>
+        <v>15.430142999999999</v>
       </c>
       <c r="I57" t="s">
         <v>17</v>
@@ -3194,36 +3193,36 @@
         <v>8.0729203322391978</v>
       </c>
       <c r="M57">
-        <v>22.52</v>
+        <v>22.65</v>
       </c>
       <c r="N57">
         <v>24.55</v>
       </c>
       <c r="O57">
-        <v>28.723445410094161</v>
+        <v>28.727717430972021</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" t="s">
         <v>90</v>
       </c>
-      <c r="C58" t="s">
-        <v>91</v>
-      </c>
       <c r="D58">
-        <v>147.6199951171875</v>
+        <v>149.49000549316409</v>
       </c>
       <c r="E58" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F58">
         <v>198</v>
       </c>
       <c r="G58">
-        <v>18.383562000000001</v>
+        <v>18.387454999999999</v>
       </c>
       <c r="H58">
-        <v>18.686074999999999</v>
+        <v>18.922785000000001</v>
       </c>
       <c r="I58" t="s">
         <v>17</v>
@@ -3238,13 +3237,13 @@
         <v>18.031248104515921</v>
       </c>
       <c r="M58">
-        <v>8.0299999999999994</v>
+        <v>8.1300000000000008</v>
       </c>
       <c r="N58">
         <v>7.9</v>
       </c>
       <c r="O58">
-        <v>36.125455465902533</v>
+        <v>36.121758109140991</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -3252,10 +3251,10 @@
         <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D59">
-        <v>123.30999755859381</v>
+        <v>123.38999938964839</v>
       </c>
       <c r="E59" t="s">
         <v>18</v>
@@ -3264,10 +3263,10 @@
         <v>17</v>
       </c>
       <c r="G59">
-        <v>536.13043000000005</v>
+        <v>536.47829999999999</v>
       </c>
       <c r="H59">
-        <v>262.36169999999998</v>
+        <v>262.53192000000001</v>
       </c>
       <c r="I59" t="s">
         <v>17</v>
@@ -3288,7 +3287,7 @@
         <v>0.47</v>
       </c>
       <c r="O59">
-        <v>72.49964215012254</v>
+        <v>72.500848292283507</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
@@ -3296,22 +3295,22 @@
         <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D60">
-        <v>66.05999755859375</v>
+        <v>68.400001525878906</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F60" t="s">
         <v>17</v>
       </c>
       <c r="G60">
-        <v>10.794117</v>
+        <v>11.176470999999999</v>
       </c>
       <c r="H60">
-        <v>9.4641830000000002</v>
+        <v>9.7994269999999997</v>
       </c>
       <c r="I60" t="s">
         <v>17</v>
@@ -3332,7 +3331,7 @@
         <v>6.98</v>
       </c>
       <c r="O60">
-        <v>40.483710644065383</v>
+        <v>40.63828107845432</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -3340,22 +3339,22 @@
         <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D61">
-        <v>42.619998931884773</v>
+        <v>43.240001678466797</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F61">
         <v>225</v>
       </c>
       <c r="G61">
-        <v>17.832633999999999</v>
+        <v>17.794239000000001</v>
       </c>
       <c r="H61">
-        <v>16.519380000000002</v>
+        <v>16.759691</v>
       </c>
       <c r="I61" t="s">
         <v>17</v>
@@ -3370,13 +3369,13 @@
         <v>8.087585993712608</v>
       </c>
       <c r="M61">
-        <v>2.39</v>
+        <v>2.4300000000000002</v>
       </c>
       <c r="N61">
         <v>2.58</v>
       </c>
       <c r="O61">
-        <v>41.850081042200891</v>
+        <v>41.871952367344093</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -3384,13 +3383,13 @@
         <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62">
         <v>17.04999923706055</v>
       </c>
       <c r="E62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F62">
         <v>59</v>
@@ -3420,7 +3419,7 @@
         <v>1.48</v>
       </c>
       <c r="O62">
-        <v>26.342930044731371</v>
+        <v>26.31099989111252</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -3428,10 +3427,10 @@
         <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63">
-        <v>18.319999694824219</v>
+        <v>18.530000686645511</v>
       </c>
       <c r="E63" t="s">
         <v>18</v>
@@ -3443,7 +3442,7 @@
         <v>17</v>
       </c>
       <c r="H63">
-        <v>9.4922284999999995</v>
+        <v>9.6010369999999998</v>
       </c>
       <c r="I63" t="s">
         <v>17</v>
@@ -3458,13 +3457,13 @@
         <v>-2.255997845024639</v>
       </c>
       <c r="M63">
-        <v>-5</v>
+        <v>-5.0599999999999996</v>
       </c>
       <c r="N63">
         <v>1.93</v>
       </c>
       <c r="O63">
-        <v>74.665666684871098</v>
+        <v>74.640377401574568</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -3472,13 +3471,13 @@
         <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3516,10 +3515,10 @@
         <v>18</v>
       </c>
       <c r="C65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D65">
-        <v>9.8000001907348633</v>
+        <v>10.02999973297119</v>
       </c>
       <c r="E65" t="s">
         <v>18</v>
@@ -3531,7 +3530,7 @@
         <v>17</v>
       </c>
       <c r="H65">
-        <v>3.3910033999999998</v>
+        <v>3.4705879999999998</v>
       </c>
       <c r="I65" t="s">
         <v>17</v>
@@ -3546,13 +3545,13 @@
         <v>-0.17526250063880719</v>
       </c>
       <c r="M65">
-        <v>-0.34</v>
+        <v>-0.35</v>
       </c>
       <c r="N65">
         <v>2.89</v>
       </c>
       <c r="O65">
-        <v>83.449829096832588</v>
+        <v>83.340722348137703</v>
       </c>
     </row>
   </sheetData>

--- a/Stock Selection/tickers_used.xlsx
+++ b/Stock Selection/tickers_used.xlsx
@@ -5,30 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional_WorkTools\Github\RodWal-Capital-Insights\Stock Selection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serw1\OneDrive - RodWal\Professional_WorkTools\Github\RodWal-Capital-Insights\Stock Selection\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41323AA1-A6F8-4B1E-9C7F-0060ABFB309E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB560BE1-8830-4BF2-BF81-63C3B609A93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -748,7 +735,7 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>30.20000076293945</v>
+        <v>30.829999923706051</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -757,10 +744,10 @@
         <v>17</v>
       </c>
       <c r="G2">
-        <v>2.5834047999999998</v>
+        <v>2.6171476999999999</v>
       </c>
       <c r="H2">
-        <v>-4.9671054000000003</v>
+        <v>-5.0707234999999997</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -775,13 +762,13 @@
         <v>1798.258469015796</v>
       </c>
       <c r="M2">
-        <v>11.69</v>
+        <v>11.78</v>
       </c>
       <c r="N2">
         <v>-6.08</v>
       </c>
       <c r="O2">
-        <v>56.482368320154073</v>
+        <v>56.484486469511793</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
@@ -792,7 +779,7 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>187.46000671386719</v>
+        <v>187.80000305175781</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -801,10 +788,10 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>107.735634</v>
+        <v>107.314285</v>
       </c>
       <c r="H3">
-        <v>26.036111999999999</v>
+        <v>26.083334000000001</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -819,13 +806,13 @@
         <v>13.94751334966173</v>
       </c>
       <c r="M3">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="N3">
         <v>7.2</v>
       </c>
       <c r="O3">
-        <v>36.359735554983807</v>
+        <v>36.356775114503669</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
@@ -836,19 +823,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>235.6499938964844</v>
+        <v>239.42999267578119</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G4">
-        <v>106.14864</v>
+        <v>108.83181</v>
       </c>
       <c r="H4">
-        <v>38.192867</v>
+        <v>38.805508000000003</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
@@ -863,13 +850,13 @@
         <v>19.066918134984039</v>
       </c>
       <c r="M4">
-        <v>2.2200000000000002</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N4">
         <v>6.17</v>
       </c>
       <c r="O4">
-        <v>63.370782175879469</v>
+        <v>63.357475641560967</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
@@ -880,7 +867,7 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>32.349998474121087</v>
+        <v>31.469999313354489</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -889,10 +876,10 @@
         <v>17</v>
       </c>
       <c r="G5">
-        <v>30.233643000000001</v>
+        <v>29.411213</v>
       </c>
       <c r="H5">
-        <v>10.819397</v>
+        <v>10.525084</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -913,7 +900,7 @@
         <v>2.99</v>
       </c>
       <c r="O5">
-        <v>43.610441392346402</v>
+        <v>43.450846774346608</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -924,19 +911,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>29.344999313354489</v>
+        <v>29.305000305175781</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
       </c>
       <c r="F6">
-        <v>437</v>
+        <v>436.00000000000011</v>
       </c>
       <c r="G6">
-        <v>15.204663</v>
+        <v>15.263021</v>
       </c>
       <c r="H6">
-        <v>7.6819369999999996</v>
+        <v>7.6714663999999999</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -951,13 +938,13 @@
         <v>4.8087837924487724</v>
       </c>
       <c r="M6">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="N6">
         <v>3.82</v>
       </c>
       <c r="O6">
-        <v>21.330085944535611</v>
+        <v>21.329994598960209</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -968,7 +955,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>155.72999572753909</v>
+        <v>156.44999694824219</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -977,10 +964,10 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>13.459809999999999</v>
+        <v>13.224852</v>
       </c>
       <c r="H7">
-        <v>7.4654837000000001</v>
+        <v>7.4999995000000004</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -995,13 +982,13 @@
         <v>29.716643554944859</v>
       </c>
       <c r="M7">
-        <v>11.57</v>
+        <v>11.83</v>
       </c>
       <c r="N7">
         <v>20.86</v>
       </c>
       <c r="O7">
-        <v>60.412521133559487</v>
+        <v>60.413345412687491</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -1012,7 +999,7 @@
         <v>29</v>
       </c>
       <c r="D8">
-        <v>3305</v>
+        <v>3260.199951171875</v>
       </c>
       <c r="E8" t="s">
         <v>30</v>
@@ -1045,7 +1032,7 @@
         <v>17</v>
       </c>
       <c r="O8">
-        <v>18.46454688434325</v>
+        <v>18.448452573226909</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -1056,19 +1043,19 @@
         <v>31</v>
       </c>
       <c r="D9">
-        <v>18.389999389648441</v>
+        <v>18.04000091552734</v>
       </c>
       <c r="E9" t="s">
         <v>32</v>
       </c>
       <c r="F9">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="G9">
-        <v>19.774193</v>
+        <v>20.500001999999999</v>
       </c>
       <c r="H9">
-        <v>13.135714999999999</v>
+        <v>12.8857155</v>
       </c>
       <c r="I9" t="s">
         <v>17</v>
@@ -1083,13 +1070,13 @@
         <v>5.6327027632036586</v>
       </c>
       <c r="M9">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="N9">
         <v>1.4</v>
       </c>
       <c r="O9">
-        <v>43.657529423813877</v>
+        <v>43.691519627393063</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1100,19 +1087,19 @@
         <v>33</v>
       </c>
       <c r="D10">
-        <v>109.0899963378906</v>
+        <v>108.44000244140619</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
       <c r="F10">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="G10">
-        <v>22.585920000000002</v>
+        <v>22.781510999999998</v>
       </c>
       <c r="H10">
-        <v>14.682368</v>
+        <v>14.594886000000001</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -1127,13 +1114,13 @@
         <v>20.75865694250961</v>
       </c>
       <c r="M10">
-        <v>4.83</v>
+        <v>4.76</v>
       </c>
       <c r="N10">
         <v>7.43</v>
       </c>
       <c r="O10">
-        <v>27.298737286424331</v>
+        <v>27.295692253699631</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -1144,7 +1131,7 @@
         <v>34</v>
       </c>
       <c r="D11">
-        <v>135.5</v>
+        <v>134.80999755859381</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -1153,10 +1140,10 @@
         <v>3</v>
       </c>
       <c r="G11">
-        <v>44.572369999999999</v>
+        <v>45.853740000000002</v>
       </c>
       <c r="H11">
-        <v>32.888350000000003</v>
+        <v>32.720874999999999</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -1171,13 +1158,13 @@
         <v>55.848023297201912</v>
       </c>
       <c r="M11">
-        <v>3.04</v>
+        <v>2.94</v>
       </c>
       <c r="N11">
         <v>4.12</v>
       </c>
       <c r="O11">
-        <v>59.037127409653422</v>
+        <v>59.036794904209543</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -1188,19 +1175,19 @@
         <v>35</v>
       </c>
       <c r="D12">
-        <v>68.040000915527344</v>
+        <v>67.209999084472656</v>
       </c>
       <c r="E12" t="s">
         <v>36</v>
       </c>
       <c r="F12">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G12">
-        <v>25.388059999999999</v>
+        <v>25.555132</v>
       </c>
       <c r="H12">
-        <v>18.489129999999999</v>
+        <v>18.263586</v>
       </c>
       <c r="I12" t="s">
         <v>17</v>
@@ -1215,13 +1202,13 @@
         <v>21.809331679631502</v>
       </c>
       <c r="M12">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="N12">
         <v>3.68</v>
       </c>
       <c r="O12">
-        <v>29.566196065798561</v>
+        <v>29.571018858470129</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -1232,19 +1219,19 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>22.20000076293945</v>
+        <v>22.14999961853027</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
       </c>
       <c r="F13">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="G13">
-        <v>13.536586</v>
+        <v>13.506098</v>
       </c>
       <c r="H13">
-        <v>9.7797365000000003</v>
+        <v>9.7577095000000007</v>
       </c>
       <c r="I13" t="s">
         <v>17</v>
@@ -1265,7 +1252,7 @@
         <v>2.27</v>
       </c>
       <c r="O13">
-        <v>24.94803089464801</v>
+        <v>24.949584665052491</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -1276,19 +1263,19 @@
         <v>38</v>
       </c>
       <c r="D14">
-        <v>161.83000183105469</v>
+        <v>161.5899963378906</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
       </c>
       <c r="F14">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G14">
-        <v>19.151479999999999</v>
+        <v>19.658149999999999</v>
       </c>
       <c r="H14">
-        <v>16.700724000000001</v>
+        <v>16.675954999999998</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1303,13 +1290,13 @@
         <v>24.059240782505299</v>
       </c>
       <c r="M14">
-        <v>8.4499999999999993</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="N14">
         <v>9.69</v>
       </c>
       <c r="O14">
-        <v>48.890279759235497</v>
+        <v>48.880903238838357</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1320,19 +1307,19 @@
         <v>39</v>
       </c>
       <c r="D15">
-        <v>200.21000671386719</v>
+        <v>200.41999816894531</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
       </c>
       <c r="F15">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G15">
-        <v>30.380880000000001</v>
+        <v>31.266770999999999</v>
       </c>
       <c r="H15">
-        <v>24.092659000000001</v>
+        <v>24.117930000000001</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1347,13 +1334,13 @@
         <v>24.301263745783849</v>
       </c>
       <c r="M15">
-        <v>6.59</v>
+        <v>6.41</v>
       </c>
       <c r="N15">
         <v>8.31</v>
       </c>
       <c r="O15">
-        <v>33.236151997598753</v>
+        <v>33.236012291211281</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -1364,19 +1351,19 @@
         <v>40</v>
       </c>
       <c r="D16">
-        <v>131.3699951171875</v>
+        <v>130.66999816894531</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
       </c>
       <c r="F16">
-        <v>440.00000000000011</v>
+        <v>434.99999999999989</v>
       </c>
       <c r="G16">
-        <v>19.011578</v>
+        <v>19.244475999999999</v>
       </c>
       <c r="H16">
-        <v>15.222479</v>
+        <v>15.141367000000001</v>
       </c>
       <c r="I16" t="s">
         <v>17</v>
@@ -1391,13 +1378,13 @@
         <v>10.23786431925341</v>
       </c>
       <c r="M16">
-        <v>6.91</v>
+        <v>6.79</v>
       </c>
       <c r="N16">
         <v>8.6300000000000008</v>
       </c>
       <c r="O16">
-        <v>19.64583858046521</v>
+        <v>19.613846104488751</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -1408,19 +1395,19 @@
         <v>42</v>
       </c>
       <c r="D17">
-        <v>359.29998779296881</v>
+        <v>359.73001098632813</v>
       </c>
       <c r="E17" t="s">
         <v>41</v>
       </c>
       <c r="F17">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17">
-        <v>35.574252999999999</v>
+        <v>36.117469999999997</v>
       </c>
       <c r="H17">
-        <v>28.380725999999999</v>
+        <v>28.414694000000001</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
@@ -1435,13 +1422,13 @@
         <v>52.210202623591513</v>
       </c>
       <c r="M17">
-        <v>10.1</v>
+        <v>9.9600000000000009</v>
       </c>
       <c r="N17">
         <v>12.66</v>
       </c>
       <c r="O17">
-        <v>22.117081359639869</v>
+        <v>22.098051588980521</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
@@ -1452,19 +1439,19 @@
         <v>43</v>
       </c>
       <c r="D18">
-        <v>148.6300048828125</v>
+        <v>147.6000061035156</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
       </c>
       <c r="F18">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="G18">
-        <v>14.833333</v>
+        <v>15.061225</v>
       </c>
       <c r="H18">
-        <v>12.152903999999999</v>
+        <v>12.068685</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1479,13 +1466,13 @@
         <v>26.04881181510946</v>
       </c>
       <c r="M18">
-        <v>10.02</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="N18">
         <v>12.23</v>
       </c>
       <c r="O18">
-        <v>43.573196246127658</v>
+        <v>43.522607164441943</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -1496,19 +1483,19 @@
         <v>44</v>
       </c>
       <c r="D19">
-        <v>144.0899963378906</v>
+        <v>143.1499938964844</v>
       </c>
       <c r="E19" t="s">
         <v>32</v>
       </c>
       <c r="F19">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G19">
-        <v>28.991952999999999</v>
+        <v>28.744978</v>
       </c>
       <c r="H19">
-        <v>23.699013000000001</v>
+        <v>23.544407</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1523,13 +1510,13 @@
         <v>18.415610746600951</v>
       </c>
       <c r="M19">
-        <v>4.97</v>
+        <v>4.9800000000000004</v>
       </c>
       <c r="N19">
         <v>6.08</v>
       </c>
       <c r="O19">
-        <v>22.10877271740592</v>
+        <v>22.084124051759829</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
@@ -1540,19 +1527,19 @@
         <v>45</v>
       </c>
       <c r="D20">
-        <v>139.41999816894531</v>
+        <v>138.0899963378906</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
       </c>
       <c r="F20">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G20">
-        <v>14.691254000000001</v>
+        <v>14.706068999999999</v>
       </c>
       <c r="H20">
-        <v>12.549054999999999</v>
+        <v>12.429342999999999</v>
       </c>
       <c r="I20" t="s">
         <v>17</v>
@@ -1567,13 +1554,13 @@
         <v>8.5314496054901205</v>
       </c>
       <c r="M20">
-        <v>9.49</v>
+        <v>9.39</v>
       </c>
       <c r="N20">
         <v>11.11</v>
       </c>
       <c r="O20">
-        <v>25.837538279320292</v>
+        <v>25.840963928382148</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -1584,19 +1571,19 @@
         <v>46</v>
       </c>
       <c r="D21">
-        <v>481.89999389648438</v>
+        <v>483.64999389648438</v>
       </c>
       <c r="E21" t="s">
         <v>32</v>
       </c>
       <c r="F21">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G21">
-        <v>19.168655000000001</v>
+        <v>19.26125</v>
       </c>
       <c r="H21">
-        <v>16.565829999999998</v>
+        <v>16.625988</v>
       </c>
       <c r="I21" t="s">
         <v>17</v>
@@ -1611,13 +1598,13 @@
         <v>14.81997561254024</v>
       </c>
       <c r="M21">
-        <v>25.14</v>
+        <v>25.11</v>
       </c>
       <c r="N21">
         <v>29.09</v>
       </c>
       <c r="O21">
-        <v>32.074653185219127</v>
+        <v>32.0530756528807</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
@@ -1628,19 +1615,19 @@
         <v>47</v>
       </c>
       <c r="D22">
-        <v>460.69000244140619</v>
+        <v>457.3599853515625</v>
       </c>
       <c r="E22" t="s">
         <v>18</v>
       </c>
       <c r="F22">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G22">
-        <v>34.847957999999998</v>
+        <v>35.592216000000001</v>
       </c>
       <c r="H22">
-        <v>30.815386</v>
+        <v>30.592642000000001</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1655,13 +1642,13 @@
         <v>35.789415272465227</v>
       </c>
       <c r="M22">
-        <v>13.22</v>
+        <v>12.85</v>
       </c>
       <c r="N22">
         <v>14.95</v>
       </c>
       <c r="O22">
-        <v>25.885506196322378</v>
+        <v>25.895119354504359</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -1672,19 +1659,19 @@
         <v>48</v>
       </c>
       <c r="D23">
-        <v>574.54998779296875</v>
+        <v>575.91998291015625</v>
       </c>
       <c r="E23" t="s">
         <v>41</v>
       </c>
       <c r="F23">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G23">
-        <v>39.515129999999999</v>
+        <v>40.330531999999998</v>
       </c>
       <c r="H23">
-        <v>35.076312999999999</v>
+        <v>35.159950000000002</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1699,13 +1686,13 @@
         <v>45.213112751383562</v>
       </c>
       <c r="M23">
-        <v>14.54</v>
+        <v>14.28</v>
       </c>
       <c r="N23">
         <v>16.38</v>
       </c>
       <c r="O23">
-        <v>21.305040612810259</v>
+        <v>21.29364441448611</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -1716,19 +1703,19 @@
         <v>49</v>
       </c>
       <c r="D24">
-        <v>102.9100036621094</v>
+        <v>101.6800003051758</v>
       </c>
       <c r="E24" t="s">
         <v>36</v>
       </c>
       <c r="F24">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G24">
-        <v>19.866796000000001</v>
+        <v>19.898240000000001</v>
       </c>
       <c r="H24">
-        <v>17.471986999999999</v>
+        <v>17.263159000000002</v>
       </c>
       <c r="I24" t="s">
         <v>17</v>
@@ -1743,13 +1730,13 @@
         <v>13.71198897276127</v>
       </c>
       <c r="M24">
-        <v>5.18</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="N24">
         <v>5.89</v>
       </c>
       <c r="O24">
-        <v>19.651102753352479</v>
+        <v>19.644063427409019</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
@@ -1760,19 +1747,19 @@
         <v>50</v>
       </c>
       <c r="D25">
-        <v>97.580001831054688</v>
+        <v>97.239997863769531</v>
       </c>
       <c r="E25" t="s">
         <v>23</v>
       </c>
       <c r="F25">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G25">
-        <v>41.173000000000002</v>
+        <v>41.555557</v>
       </c>
       <c r="H25">
-        <v>35.875</v>
+        <v>35.75</v>
       </c>
       <c r="I25" t="s">
         <v>17</v>
@@ -1787,13 +1774,13 @@
         <v>2.7469543815742412</v>
       </c>
       <c r="M25">
-        <v>2.37</v>
+        <v>2.34</v>
       </c>
       <c r="N25">
         <v>2.72</v>
       </c>
       <c r="O25">
-        <v>24.113924695476651</v>
+        <v>24.116996744382401</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -1804,19 +1791,19 @@
         <v>51</v>
       </c>
       <c r="D26">
-        <v>756.78997802734375</v>
+        <v>746.510009765625</v>
       </c>
       <c r="E26" t="s">
         <v>18</v>
       </c>
       <c r="F26">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G26">
-        <v>29.242270999999999</v>
+        <v>29.588190000000001</v>
       </c>
       <c r="H26">
-        <v>28.344193000000001</v>
+        <v>27.959174999999998</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1831,13 +1818,13 @@
         <v>28.33459111814113</v>
       </c>
       <c r="M26">
-        <v>25.88</v>
+        <v>25.23</v>
       </c>
       <c r="N26">
         <v>26.7</v>
       </c>
       <c r="O26">
-        <v>48.739271307499337</v>
+        <v>48.632940880201943</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -1848,7 +1835,7 @@
         <v>52</v>
       </c>
       <c r="D27">
-        <v>36.569999694824219</v>
+        <v>36.959999084472663</v>
       </c>
       <c r="E27" t="s">
         <v>26</v>
@@ -1857,10 +1844,10 @@
         <v>17</v>
       </c>
       <c r="G27">
-        <v>8.5046510000000008</v>
+        <v>8.5161289999999994</v>
       </c>
       <c r="H27">
-        <v>7.7808514000000004</v>
+        <v>7.8638300000000001</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1875,13 +1862,13 @@
         <v>7.9344361198138351</v>
       </c>
       <c r="M27">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="N27">
         <v>4.7</v>
       </c>
       <c r="O27">
-        <v>48.884813960092302</v>
+        <v>48.886746359729202</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
@@ -1892,7 +1879,7 @@
         <v>53</v>
       </c>
       <c r="D28">
-        <v>116.379997253418</v>
+        <v>114.4499969482422</v>
       </c>
       <c r="E28" t="s">
         <v>36</v>
@@ -1901,10 +1888,10 @@
         <v>359</v>
       </c>
       <c r="G28">
-        <v>19.332225999999999</v>
+        <v>19.300169</v>
       </c>
       <c r="H28">
-        <v>18.356466000000001</v>
+        <v>18.052050000000001</v>
       </c>
       <c r="I28" t="s">
         <v>17</v>
@@ -1919,13 +1906,13 @@
         <v>15.220239866756501</v>
       </c>
       <c r="M28">
-        <v>6.02</v>
+        <v>5.93</v>
       </c>
       <c r="N28">
         <v>6.34</v>
       </c>
       <c r="O28">
-        <v>18.375187587169581</v>
+        <v>18.43932052986969</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -1936,19 +1923,19 @@
         <v>54</v>
       </c>
       <c r="D29">
-        <v>142.8500061035156</v>
+        <v>142.67999267578119</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
       </c>
       <c r="F29">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="G29">
-        <v>19.278003999999999</v>
+        <v>19.465209999999999</v>
       </c>
       <c r="H29">
-        <v>18.722149999999999</v>
+        <v>18.699867000000001</v>
       </c>
       <c r="I29" t="s">
         <v>17</v>
@@ -1963,13 +1950,13 @@
         <v>12.48164484200357</v>
       </c>
       <c r="M29">
-        <v>7.41</v>
+        <v>7.33</v>
       </c>
       <c r="N29">
         <v>7.63</v>
       </c>
       <c r="O29">
-        <v>19.640844170614599</v>
+        <v>19.623872206665808</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -1980,19 +1967,19 @@
         <v>55</v>
       </c>
       <c r="D30">
-        <v>21.329999923706051</v>
+        <v>20.989999771118161</v>
       </c>
       <c r="E30" t="s">
         <v>41</v>
       </c>
       <c r="F30">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="G30">
-        <v>9.48</v>
+        <v>9.4977370000000008</v>
       </c>
       <c r="H30">
-        <v>9.7397259999999992</v>
+        <v>9.5844749999999994</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -2007,13 +1994,13 @@
         <v>25.984840469640911</v>
       </c>
       <c r="M30">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="N30">
         <v>2.19</v>
       </c>
       <c r="O30">
-        <v>28.040326796780111</v>
+        <v>28.04122875956385</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -2024,19 +2011,19 @@
         <v>56</v>
       </c>
       <c r="D31">
-        <v>172.8999938964844</v>
+        <v>172.36000061035159</v>
       </c>
       <c r="E31" t="s">
         <v>57</v>
       </c>
       <c r="F31">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G31">
-        <v>18.793478</v>
+        <v>19.236606999999999</v>
       </c>
       <c r="H31">
-        <v>19.296875</v>
+        <v>19.236606999999999</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -2051,13 +2038,13 @@
         <v>30.856819860861741</v>
       </c>
       <c r="M31">
-        <v>9.1999999999999993</v>
+        <v>8.9600000000000009</v>
       </c>
       <c r="N31">
         <v>8.9600000000000009</v>
       </c>
       <c r="O31">
-        <v>31.57447392820206</v>
+        <v>31.574767010973741</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
@@ -2068,19 +2055,19 @@
         <v>58</v>
       </c>
       <c r="D32">
-        <v>17.309999465942379</v>
+        <v>17.180000305175781</v>
       </c>
       <c r="E32" t="s">
         <v>26</v>
       </c>
       <c r="F32">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="G32">
-        <v>6.0313587000000002</v>
+        <v>6.2021660000000001</v>
       </c>
       <c r="H32">
-        <v>6.2945450000000003</v>
+        <v>6.2472729999999999</v>
       </c>
       <c r="I32" t="s">
         <v>17</v>
@@ -2095,13 +2082,13 @@
         <v>10.041387718820969</v>
       </c>
       <c r="M32">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="N32">
         <v>2.75</v>
       </c>
       <c r="O32">
-        <v>51.423452697626203</v>
+        <v>51.384809324994137</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -2112,19 +2099,19 @@
         <v>59</v>
       </c>
       <c r="D33">
-        <v>197.67999267578119</v>
+        <v>196.13999938964841</v>
       </c>
       <c r="E33" t="s">
         <v>18</v>
       </c>
       <c r="F33">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G33">
-        <v>23.093456</v>
+        <v>23.517983999999998</v>
       </c>
       <c r="H33">
-        <v>24.465344999999999</v>
+        <v>24.274754000000001</v>
       </c>
       <c r="I33" t="s">
         <v>17</v>
@@ -2139,13 +2126,13 @@
         <v>41.686769633025442</v>
       </c>
       <c r="M33">
-        <v>8.56</v>
+        <v>8.34</v>
       </c>
       <c r="N33">
         <v>8.08</v>
       </c>
       <c r="O33">
-        <v>46.723772979619227</v>
+        <v>46.612931232233286</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -2156,19 +2143,19 @@
         <v>60</v>
       </c>
       <c r="D34">
-        <v>43.909999847412109</v>
+        <v>43.279998779296882</v>
       </c>
       <c r="E34" t="s">
         <v>36</v>
       </c>
       <c r="F34">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G34">
-        <v>16.262962000000002</v>
+        <v>16.332075</v>
       </c>
       <c r="H34">
-        <v>16.695816000000001</v>
+        <v>16.456271999999998</v>
       </c>
       <c r="I34" t="s">
         <v>17</v>
@@ -2183,13 +2170,13 @@
         <v>11.435082528811259</v>
       </c>
       <c r="M34">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="N34">
         <v>2.63</v>
       </c>
       <c r="O34">
-        <v>19.775772900904482</v>
+        <v>19.759314059154189</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
@@ -2200,7 +2187,7 @@
         <v>61</v>
       </c>
       <c r="D35">
-        <v>42.220001220703118</v>
+        <v>42.330001831054688</v>
       </c>
       <c r="E35" t="s">
         <v>41</v>
@@ -2209,10 +2196,10 @@
         <v>3611</v>
       </c>
       <c r="G35">
-        <v>6.6803800000000004</v>
+        <v>6.6766562</v>
       </c>
       <c r="H35">
-        <v>7.1559324000000002</v>
+        <v>7.1745763</v>
       </c>
       <c r="I35" t="s">
         <v>17</v>
@@ -2227,13 +2214,13 @@
         <v>28.104146008031432</v>
       </c>
       <c r="M35">
-        <v>6.32</v>
+        <v>6.34</v>
       </c>
       <c r="N35">
         <v>5.9</v>
       </c>
       <c r="O35">
-        <v>29.778117136617379</v>
+        <v>31.389912667582848</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
@@ -2244,19 +2231,19 @@
         <v>62</v>
       </c>
       <c r="D36">
-        <v>59.619998931884773</v>
+        <v>59.479999542236328</v>
       </c>
       <c r="E36" t="s">
         <v>23</v>
       </c>
       <c r="F36">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="G36">
-        <v>10.020168</v>
+        <v>9.9798659999999995</v>
       </c>
       <c r="H36">
-        <v>11.143926</v>
+        <v>11.117756999999999</v>
       </c>
       <c r="I36" t="s">
         <v>17</v>
@@ -2271,13 +2258,13 @@
         <v>50.301292507937191</v>
       </c>
       <c r="M36">
-        <v>5.95</v>
+        <v>5.96</v>
       </c>
       <c r="N36">
         <v>5.35</v>
       </c>
       <c r="O36">
-        <v>19.387509952118549</v>
+        <v>19.371332500047799</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -2288,19 +2275,19 @@
         <v>63</v>
       </c>
       <c r="D37">
-        <v>13.545000076293951</v>
+        <v>13.239999771118161</v>
       </c>
       <c r="E37" t="s">
         <v>41</v>
       </c>
       <c r="F37">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="G37">
-        <v>7.6525426000000003</v>
+        <v>7.480226</v>
       </c>
       <c r="H37">
-        <v>14.4095745</v>
+        <v>14.085106</v>
       </c>
       <c r="I37" t="s">
         <v>17</v>
@@ -2321,7 +2308,7 @@
         <v>0.94</v>
       </c>
       <c r="O37">
-        <v>30.676104934717809</v>
+        <v>30.76432809533885</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
@@ -2332,19 +2319,19 @@
         <v>64</v>
       </c>
       <c r="D38">
-        <v>17.909999847412109</v>
+        <v>17.64999961853027</v>
       </c>
       <c r="E38" t="s">
         <v>41</v>
       </c>
       <c r="F38">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G38">
-        <v>8.9104480000000006</v>
+        <v>8.8249999999999993</v>
       </c>
       <c r="H38">
-        <v>17.057144000000001</v>
+        <v>16.809525000000001</v>
       </c>
       <c r="I38" t="s">
         <v>17</v>
@@ -2359,13 +2346,13 @@
         <v>22.63225720298977</v>
       </c>
       <c r="M38">
-        <v>2.0099999999999998</v>
+        <v>2</v>
       </c>
       <c r="N38">
         <v>1.05</v>
       </c>
       <c r="O38">
-        <v>36.087641615791412</v>
+        <v>36.030116409956229</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
@@ -2376,19 +2363,19 @@
         <v>65</v>
       </c>
       <c r="D39">
-        <v>15.44999980926514</v>
+        <v>15.11999988555908</v>
       </c>
       <c r="E39" t="s">
         <v>41</v>
       </c>
       <c r="F39">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="G39">
-        <v>12.0703125</v>
+        <v>12.193548</v>
       </c>
       <c r="H39">
-        <v>37.682926000000002</v>
+        <v>36.878048</v>
       </c>
       <c r="I39" t="s">
         <v>17</v>
@@ -2403,13 +2390,13 @@
         <v>22.5677633341305</v>
       </c>
       <c r="M39">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="N39">
         <v>0.41</v>
       </c>
       <c r="O39">
-        <v>36.550201469016137</v>
+        <v>36.591370228535979</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -2461,7 +2448,7 @@
         <v>69</v>
       </c>
       <c r="D41">
-        <v>18.95999908447266</v>
+        <v>19.309999465942379</v>
       </c>
       <c r="E41" t="s">
         <v>30</v>
@@ -2494,8 +2481,7 @@
         <v>17</v>
       </c>
       <c r="O41">
-        <f>D41</f>
-        <v>18.95999908447266</v>
+        <v>19.309999465942379</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -2506,7 +2492,7 @@
         <v>70</v>
       </c>
       <c r="D42">
-        <v>2.9900000095367432</v>
+        <v>2.9000000953674321</v>
       </c>
       <c r="E42" t="s">
         <v>18</v>
@@ -2518,7 +2504,7 @@
         <v>17</v>
       </c>
       <c r="H42">
-        <v>-0.54166669999999995</v>
+        <v>-0.52536229999999995</v>
       </c>
       <c r="I42" t="s">
         <v>17</v>
@@ -2533,13 +2519,13 @@
         <v>-120.67624899812979</v>
       </c>
       <c r="M42">
-        <v>-98.64</v>
+        <v>-96</v>
       </c>
       <c r="N42">
         <v>-5.52</v>
       </c>
       <c r="O42">
-        <v>171.77474564289861</v>
+        <v>171.77674673633391</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
@@ -2550,7 +2536,7 @@
         <v>71</v>
       </c>
       <c r="D43">
-        <v>19.264999389648441</v>
+        <v>19.384000778198239</v>
       </c>
       <c r="E43" t="s">
         <v>30</v>
@@ -2583,7 +2569,7 @@
         <v>17</v>
       </c>
       <c r="O43">
-        <v>14.918007299961481</v>
+        <v>14.91661087801284</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
@@ -2594,7 +2580,7 @@
         <v>73</v>
       </c>
       <c r="D44">
-        <v>6.0900001525878906</v>
+        <v>6.0809998512268066</v>
       </c>
       <c r="E44" t="s">
         <v>30</v>
@@ -2627,7 +2613,7 @@
         <v>17</v>
       </c>
       <c r="O44">
-        <v>2.7012905395376561</v>
+        <v>2.7014011886478619</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
@@ -2638,7 +2624,7 @@
         <v>74</v>
       </c>
       <c r="D45">
-        <v>6.2420001029968262</v>
+        <v>6.2430000305175781</v>
       </c>
       <c r="E45" t="s">
         <v>30</v>
@@ -2671,7 +2657,7 @@
         <v>17</v>
       </c>
       <c r="O45">
-        <v>2.729150301069823</v>
+        <v>2.7237334950374641</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
@@ -2682,7 +2668,7 @@
         <v>75</v>
       </c>
       <c r="D46">
-        <v>72.959999084472656</v>
+        <v>72.529998779296875</v>
       </c>
       <c r="E46" t="s">
         <v>30</v>
@@ -2691,7 +2677,7 @@
         <v>310</v>
       </c>
       <c r="G46">
-        <v>15.017734000000001</v>
+        <v>14.929224</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2715,7 +2701,7 @@
         <v>17</v>
       </c>
       <c r="O46">
-        <v>14.07923688731044</v>
+        <v>14.06586937988955</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
@@ -2726,7 +2712,7 @@
         <v>76</v>
       </c>
       <c r="D47">
-        <v>47.630001068115227</v>
+        <v>47.340000152587891</v>
       </c>
       <c r="E47" t="s">
         <v>30</v>
@@ -2735,7 +2721,7 @@
         <v>313</v>
       </c>
       <c r="G47">
-        <v>15.326273</v>
+        <v>15.232957000000001</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2759,7 +2745,7 @@
         <v>17</v>
       </c>
       <c r="O47">
-        <v>18.620997635231369</v>
+        <v>18.586794711464769</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
@@ -2770,7 +2756,7 @@
         <v>78</v>
       </c>
       <c r="D48">
-        <v>32.709999084472663</v>
+        <v>31.329999923706051</v>
       </c>
       <c r="E48" t="s">
         <v>77</v>
@@ -2782,7 +2768,7 @@
         <v>17</v>
       </c>
       <c r="H48">
-        <v>8.2185930000000003</v>
+        <v>7.8718589999999997</v>
       </c>
       <c r="I48" t="s">
         <v>17</v>
@@ -2797,13 +2783,13 @@
         <v>-8.9286898337138769</v>
       </c>
       <c r="M48">
-        <v>-1.4</v>
+        <v>-1.36</v>
       </c>
       <c r="N48">
         <v>3.98</v>
       </c>
       <c r="O48">
-        <v>43.363535234331437</v>
+        <v>43.253192279057693</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -2814,7 +2800,7 @@
         <v>79</v>
       </c>
       <c r="D49">
-        <v>591.1500244140625</v>
+        <v>587.72998046875</v>
       </c>
       <c r="E49" t="s">
         <v>30</v>
@@ -2823,7 +2809,7 @@
         <v>129</v>
       </c>
       <c r="G49">
-        <v>25.757294000000002</v>
+        <v>25.608277999999999</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -2847,7 +2833,7 @@
         <v>17</v>
       </c>
       <c r="O49">
-        <v>20.507394401626321</v>
+        <v>20.503184215131778</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
@@ -2858,7 +2844,7 @@
         <v>80</v>
       </c>
       <c r="D50">
-        <v>51.595001220703118</v>
+        <v>50.639999389648438</v>
       </c>
       <c r="E50" t="s">
         <v>30</v>
@@ -2891,7 +2877,7 @@
         <v>17</v>
       </c>
       <c r="O50">
-        <v>48.884896600077823</v>
+        <v>48.802430069394923</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
@@ -2902,7 +2888,7 @@
         <v>81</v>
       </c>
       <c r="D51">
-        <v>15.39640045166016</v>
+        <v>15.382399559021</v>
       </c>
       <c r="E51" t="s">
         <v>30</v>
@@ -2935,7 +2921,7 @@
         <v>17</v>
       </c>
       <c r="O51">
-        <v>25.263358554322309</v>
+        <v>25.26344986420008</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -2946,7 +2932,7 @@
         <v>82</v>
       </c>
       <c r="D52">
-        <v>144.3320007324219</v>
+        <v>145.85499572753909</v>
       </c>
       <c r="E52" t="s">
         <v>30</v>
@@ -2979,7 +2965,7 @@
         <v>17</v>
       </c>
       <c r="O52">
-        <v>11.1882302103756</v>
+        <v>11.23544605437033</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
@@ -3034,7 +3020,7 @@
         <v>85</v>
       </c>
       <c r="D54">
-        <v>20.659999847412109</v>
+        <v>20.440000534057621</v>
       </c>
       <c r="E54" t="s">
         <v>30</v>
@@ -3043,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="G54">
-        <v>31.513487000000001</v>
+        <v>31.177914000000001</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -3067,7 +3053,7 @@
         <v>17</v>
       </c>
       <c r="O54">
-        <v>26.142747802293378</v>
+        <v>26.11299617967083</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
@@ -3078,7 +3064,7 @@
         <v>86</v>
       </c>
       <c r="D55">
-        <v>72.529998779296875</v>
+        <v>72.370002746582031</v>
       </c>
       <c r="E55" t="s">
         <v>30</v>
@@ -3111,7 +3097,7 @@
         <v>17</v>
       </c>
       <c r="O55">
-        <v>5.3345531782892728</v>
+        <v>5.3259126971205326</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
@@ -3166,7 +3152,7 @@
         <v>88</v>
       </c>
       <c r="D57">
-        <v>378.80999755859381</v>
+        <v>378.44000244140619</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -3175,10 +3161,10 @@
         <v>76</v>
       </c>
       <c r="G57">
-        <v>16.724502999999999</v>
+        <v>16.834520000000001</v>
       </c>
       <c r="H57">
-        <v>15.430142999999999</v>
+        <v>15.4150715</v>
       </c>
       <c r="I57" t="s">
         <v>17</v>
@@ -3193,13 +3179,13 @@
         <v>8.0729203322391978</v>
       </c>
       <c r="M57">
-        <v>22.65</v>
+        <v>22.48</v>
       </c>
       <c r="N57">
         <v>24.55</v>
       </c>
       <c r="O57">
-        <v>28.727717430972021</v>
+        <v>28.66129029726293</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
@@ -3210,19 +3196,19 @@
         <v>90</v>
       </c>
       <c r="D58">
-        <v>149.49000549316409</v>
+        <v>148.6600036621094</v>
       </c>
       <c r="E58" t="s">
         <v>89</v>
       </c>
       <c r="F58">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G58">
-        <v>18.387454999999999</v>
+        <v>18.513076999999999</v>
       </c>
       <c r="H58">
-        <v>18.922785000000001</v>
+        <v>18.817722</v>
       </c>
       <c r="I58" t="s">
         <v>17</v>
@@ -3237,13 +3223,13 @@
         <v>18.031248104515921</v>
       </c>
       <c r="M58">
-        <v>8.1300000000000008</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="N58">
         <v>7.9</v>
       </c>
       <c r="O58">
-        <v>36.121758109140991</v>
+        <v>36.104685815826308</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
@@ -3254,7 +3240,7 @@
         <v>91</v>
       </c>
       <c r="D59">
-        <v>123.38999938964839</v>
+        <v>123.7600021362305</v>
       </c>
       <c r="E59" t="s">
         <v>18</v>
@@ -3263,10 +3249,10 @@
         <v>17</v>
       </c>
       <c r="G59">
-        <v>536.47829999999999</v>
+        <v>515.66669999999999</v>
       </c>
       <c r="H59">
-        <v>262.53192000000001</v>
+        <v>263.31914999999998</v>
       </c>
       <c r="I59" t="s">
         <v>17</v>
@@ -3281,13 +3267,13 @@
         <v>18.32059821851664</v>
       </c>
       <c r="M59">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="N59">
         <v>0.47</v>
       </c>
       <c r="O59">
-        <v>72.500848292283507</v>
+        <v>72.49017292245648</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
@@ -3298,7 +3284,7 @@
         <v>92</v>
       </c>
       <c r="D60">
-        <v>68.400001525878906</v>
+        <v>67.709999084472656</v>
       </c>
       <c r="E60" t="s">
         <v>32</v>
@@ -3307,10 +3293,10 @@
         <v>17</v>
       </c>
       <c r="G60">
-        <v>11.176470999999999</v>
+        <v>11.063725</v>
       </c>
       <c r="H60">
-        <v>9.7994269999999997</v>
+        <v>9.7005730000000003</v>
       </c>
       <c r="I60" t="s">
         <v>17</v>
@@ -3331,7 +3317,7 @@
         <v>6.98</v>
       </c>
       <c r="O60">
-        <v>40.63828107845432</v>
+        <v>40.605089472070219</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -3342,19 +3328,19 @@
         <v>93</v>
       </c>
       <c r="D61">
-        <v>43.240001678466797</v>
+        <v>43.479999542236328</v>
       </c>
       <c r="E61" t="s">
         <v>32</v>
       </c>
       <c r="F61">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G61">
-        <v>17.794239000000001</v>
+        <v>18.116665000000001</v>
       </c>
       <c r="H61">
-        <v>16.759691</v>
+        <v>16.852713000000001</v>
       </c>
       <c r="I61" t="s">
         <v>17</v>
@@ -3369,13 +3355,13 @@
         <v>8.087585993712608</v>
       </c>
       <c r="M61">
-        <v>2.4300000000000002</v>
+        <v>2.4</v>
       </c>
       <c r="N61">
         <v>2.58</v>
       </c>
       <c r="O61">
-        <v>41.871952367344093</v>
+        <v>41.784308731570867</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
@@ -3386,7 +3372,7 @@
         <v>94</v>
       </c>
       <c r="D62">
-        <v>17.04999923706055</v>
+        <v>16.89999961853027</v>
       </c>
       <c r="E62" t="s">
         <v>36</v>
@@ -3395,10 +3381,10 @@
         <v>59</v>
       </c>
       <c r="G62">
-        <v>15.642200000000001</v>
+        <v>15.648148000000001</v>
       </c>
       <c r="H62">
-        <v>11.520269000000001</v>
+        <v>11.418919000000001</v>
       </c>
       <c r="I62" t="s">
         <v>17</v>
@@ -3413,13 +3399,13 @@
         <v>9.5758125530442939</v>
       </c>
       <c r="M62">
-        <v>1.0900000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="N62">
         <v>1.48</v>
       </c>
       <c r="O62">
-        <v>26.31099989111252</v>
+        <v>26.31747093750727</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -3430,19 +3416,19 @@
         <v>95</v>
       </c>
       <c r="D63">
-        <v>18.530000686645511</v>
+        <v>18.360000610351559</v>
       </c>
       <c r="E63" t="s">
         <v>18</v>
       </c>
       <c r="F63">
-        <v>1638</v>
+        <v>1634</v>
       </c>
       <c r="G63" t="s">
         <v>17</v>
       </c>
       <c r="H63">
-        <v>9.6010369999999998</v>
+        <v>9.5129540000000006</v>
       </c>
       <c r="I63" t="s">
         <v>17</v>
@@ -3457,13 +3443,13 @@
         <v>-2.255997845024639</v>
       </c>
       <c r="M63">
-        <v>-5.0599999999999996</v>
+        <v>-5</v>
       </c>
       <c r="N63">
         <v>1.93</v>
       </c>
       <c r="O63">
-        <v>74.640377401574568</v>
+        <v>74.526006142663462</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
@@ -3518,7 +3504,7 @@
         <v>97</v>
       </c>
       <c r="D65">
-        <v>10.02999973297119</v>
+        <v>10.159999847412109</v>
       </c>
       <c r="E65" t="s">
         <v>18</v>
@@ -3530,7 +3516,7 @@
         <v>17</v>
       </c>
       <c r="H65">
-        <v>3.4705879999999998</v>
+        <v>3.5155706000000002</v>
       </c>
       <c r="I65" t="s">
         <v>17</v>
@@ -3545,13 +3531,13 @@
         <v>-0.17526250063880719</v>
       </c>
       <c r="M65">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="N65">
         <v>2.89</v>
       </c>
       <c r="O65">
-        <v>83.340722348137703</v>
+        <v>83.313806007676703</v>
       </c>
     </row>
   </sheetData>

--- a/Stock Selection/tickers_used.xlsx
+++ b/Stock Selection/tickers_used.xlsx
@@ -5,22 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\serw1\OneDrive - RodWal\Professional_WorkTools\Github\RodWal-Capital-Insights\Stock Selection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/RodWal-Capital-Insights/Stock Selection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB560BE1-8830-4BF2-BF81-63C3B609A93F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_4B2915855F41D20F62355476585DCE3A8747AAD9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{731557F9-6281-4F17-86E3-6BD87DEA9731}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="99">
   <si>
     <t>Chapter</t>
   </si>
@@ -110,6 +123,9 @@
   </si>
   <si>
     <t>GC=F</t>
+  </si>
+  <si>
+    <t>Error: single positional indexer is out-of-bounds</t>
   </si>
   <si>
     <t>Unknown</t>
@@ -332,7 +348,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -678,9 +693,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -727,7 +742,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -735,7 +750,7 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>30.829999923706051</v>
+        <v>32.090000152587891</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -744,10 +759,10 @@
         <v>17</v>
       </c>
       <c r="G2">
-        <v>2.6171476999999999</v>
+        <v>2.7807626999999999</v>
       </c>
       <c r="H2">
-        <v>-5.0707234999999997</v>
+        <v>-5.2779610000000003</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -762,16 +777,16 @@
         <v>1798.258469015796</v>
       </c>
       <c r="M2">
-        <v>11.78</v>
+        <v>11.54</v>
       </c>
       <c r="N2">
         <v>-6.08</v>
       </c>
       <c r="O2">
-        <v>56.484486469511793</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+        <v>56.481983456781727</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -779,7 +794,7 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>187.80000305175781</v>
+        <v>192.41999816894531</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -788,10 +803,10 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>107.314285</v>
+        <v>111.22543</v>
       </c>
       <c r="H3">
-        <v>26.083334000000001</v>
+        <v>26.725000000000001</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -806,16 +821,16 @@
         <v>13.94751334966173</v>
       </c>
       <c r="M3">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="N3">
         <v>7.2</v>
       </c>
       <c r="O3">
-        <v>36.356775114503669</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>36.242896395286991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -823,19 +838,19 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>239.42999267578119</v>
+        <v>242.07000732421881</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G4">
-        <v>108.83181</v>
+        <v>112.5907</v>
       </c>
       <c r="H4">
-        <v>38.805508000000003</v>
+        <v>39.233387</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
@@ -850,16 +865,16 @@
         <v>19.066918134984039</v>
       </c>
       <c r="M4">
-        <v>2.2000000000000002</v>
+        <v>2.15</v>
       </c>
       <c r="N4">
         <v>6.17</v>
       </c>
       <c r="O4">
-        <v>63.357475641560967</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>63.254562931019137</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -867,7 +882,7 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>31.469999313354489</v>
+        <v>31.159999847412109</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -876,10 +891,10 @@
         <v>17</v>
       </c>
       <c r="G5">
-        <v>29.411213</v>
+        <v>29.121493999999998</v>
       </c>
       <c r="H5">
-        <v>10.525084</v>
+        <v>10.421405</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -900,10 +915,10 @@
         <v>2.99</v>
       </c>
       <c r="O5">
-        <v>43.450846774346608</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>43.385903025986948</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -911,19 +926,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>29.305000305175781</v>
+        <v>29.229999542236332</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
       </c>
       <c r="F6">
-        <v>436.00000000000011</v>
+        <v>438</v>
       </c>
       <c r="G6">
-        <v>15.263021</v>
+        <v>15.145078</v>
       </c>
       <c r="H6">
-        <v>7.6714663999999999</v>
+        <v>7.6518325999999997</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -938,16 +953,16 @@
         <v>4.8087837924487724</v>
       </c>
       <c r="M6">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="N6">
         <v>3.82</v>
       </c>
       <c r="O6">
-        <v>21.329994598960209</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>21.317009154977502</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -955,7 +970,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>156.44999694824219</v>
+        <v>158.08000183105469</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -964,10 +979,10 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>13.224852</v>
+        <v>13.419354999999999</v>
       </c>
       <c r="H7">
-        <v>7.4999995000000004</v>
+        <v>7.5781400000000003</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -982,30 +997,30 @@
         <v>29.716643554944859</v>
       </c>
       <c r="M7">
-        <v>11.83</v>
+        <v>11.78</v>
       </c>
       <c r="N7">
         <v>20.86</v>
       </c>
       <c r="O7">
-        <v>60.413345412687491</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>60.408752216552678</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>29</v>
       </c>
-      <c r="D8">
-        <v>3260.199951171875</v>
+      <c r="D8" t="s">
+        <v>30</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F8" t="s">
-        <v>17</v>
+        <v>31</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
@@ -1031,31 +1046,31 @@
       <c r="N8" t="s">
         <v>17</v>
       </c>
-      <c r="O8">
-        <v>18.448452573226909</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>18.04000091552734</v>
+        <v>17.35000038146973</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>283</v>
+        <v>300</v>
       </c>
       <c r="G9">
-        <v>20.500001999999999</v>
+        <v>19.277778999999999</v>
       </c>
       <c r="H9">
-        <v>12.8857155</v>
+        <v>12.392858</v>
       </c>
       <c r="I9" t="s">
         <v>17</v>
@@ -1070,36 +1085,36 @@
         <v>5.6327027632036586</v>
       </c>
       <c r="M9">
-        <v>0.88</v>
+        <v>0.9</v>
       </c>
       <c r="N9">
         <v>1.4</v>
       </c>
       <c r="O9">
-        <v>43.691519627393063</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>43.59653161446694</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10">
-        <v>108.44000244140619</v>
+        <v>110.0800018310547</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
       <c r="F10">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="G10">
-        <v>22.781510999999998</v>
+        <v>23.126048999999998</v>
       </c>
       <c r="H10">
-        <v>14.594886000000001</v>
+        <v>14.815613000000001</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -1120,18 +1135,18 @@
         <v>7.43</v>
       </c>
       <c r="O10">
-        <v>27.295692253699631</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>27.404183030306822</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11">
-        <v>134.80999755859381</v>
+        <v>135.1300048828125</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -1140,54 +1155,54 @@
         <v>3</v>
       </c>
       <c r="G11">
-        <v>45.853740000000002</v>
+        <v>43.731395999999997</v>
       </c>
       <c r="H11">
-        <v>32.720874999999999</v>
+        <v>32.798546000000002</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
       </c>
       <c r="J11">
-        <v>63.845999999999997</v>
+        <v>59.419995999999998</v>
       </c>
       <c r="K11">
-        <v>72879996928</v>
+        <v>76773998592</v>
       </c>
       <c r="L11">
-        <v>55.848023297201912</v>
+        <v>51.694442005172633</v>
       </c>
       <c r="M11">
-        <v>2.94</v>
+        <v>3.09</v>
       </c>
       <c r="N11">
         <v>4.12</v>
       </c>
       <c r="O11">
-        <v>59.036794904209543</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>59.061403712338908</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12">
-        <v>67.209999084472656</v>
+        <v>70.639999389648438</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="G12">
-        <v>25.555132</v>
+        <v>26.456928000000001</v>
       </c>
       <c r="H12">
-        <v>18.263586</v>
+        <v>19.195651999999999</v>
       </c>
       <c r="I12" t="s">
         <v>17</v>
@@ -1202,36 +1217,36 @@
         <v>21.809331679631502</v>
       </c>
       <c r="M12">
-        <v>2.63</v>
+        <v>2.67</v>
       </c>
       <c r="N12">
         <v>3.68</v>
       </c>
       <c r="O12">
-        <v>29.571018858470129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>29.629583601540769</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13">
-        <v>22.14999961853027</v>
+        <v>22.229999542236332</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
       </c>
       <c r="F13">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G13">
-        <v>13.506098</v>
+        <v>13.554878</v>
       </c>
       <c r="H13">
-        <v>9.7577095000000007</v>
+        <v>9.7929519999999997</v>
       </c>
       <c r="I13" t="s">
         <v>17</v>
@@ -1252,30 +1267,30 @@
         <v>2.27</v>
       </c>
       <c r="O13">
-        <v>24.949584665052491</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>24.93436661262972</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14">
-        <v>161.5899963378906</v>
+        <v>156.75</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
       </c>
       <c r="F14">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G14">
-        <v>19.658149999999999</v>
+        <v>19.092569999999998</v>
       </c>
       <c r="H14">
-        <v>16.675954999999998</v>
+        <v>16.176472</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1290,24 +1305,24 @@
         <v>24.059240782505299</v>
       </c>
       <c r="M14">
-        <v>8.2200000000000006</v>
+        <v>8.2100000000000009</v>
       </c>
       <c r="N14">
         <v>9.69</v>
       </c>
       <c r="O14">
-        <v>48.880903238838357</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>48.908876698407347</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15">
-        <v>200.41999816894531</v>
+        <v>200.8500061035156</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -1316,10 +1331,10 @@
         <v>52</v>
       </c>
       <c r="G15">
-        <v>31.266770999999999</v>
+        <v>31.236393</v>
       </c>
       <c r="H15">
-        <v>24.117930000000001</v>
+        <v>24.169674000000001</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1334,36 +1349,36 @@
         <v>24.301263745783849</v>
       </c>
       <c r="M15">
-        <v>6.41</v>
+        <v>6.43</v>
       </c>
       <c r="N15">
         <v>8.31</v>
       </c>
       <c r="O15">
-        <v>33.236012291211281</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>33.23293560720505</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16">
-        <v>130.66999816894531</v>
+        <v>131.44999694824219</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
       </c>
       <c r="F16">
-        <v>434.99999999999989</v>
+        <v>433</v>
       </c>
       <c r="G16">
-        <v>19.244475999999999</v>
+        <v>19.330881000000002</v>
       </c>
       <c r="H16">
-        <v>15.141367000000001</v>
+        <v>15.23175</v>
       </c>
       <c r="I16" t="s">
         <v>17</v>
@@ -1378,36 +1393,36 @@
         <v>10.23786431925341</v>
       </c>
       <c r="M16">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="N16">
         <v>8.6300000000000008</v>
       </c>
       <c r="O16">
-        <v>19.613846104488751</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <v>19.582690445835969</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17">
+        <v>365.19000244140619</v>
+      </c>
+      <c r="E17" t="s">
         <v>42</v>
       </c>
-      <c r="D17">
-        <v>359.73001098632813</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
-      </c>
       <c r="F17">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G17">
-        <v>36.117469999999997</v>
+        <v>36.776435999999997</v>
       </c>
       <c r="H17">
-        <v>28.414694000000001</v>
+        <v>28.845972</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
@@ -1422,36 +1437,36 @@
         <v>52.210202623591513</v>
       </c>
       <c r="M17">
-        <v>9.9600000000000009</v>
+        <v>9.93</v>
       </c>
       <c r="N17">
         <v>12.66</v>
       </c>
       <c r="O17">
-        <v>22.098051588980521</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>22.100144995778599</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18">
-        <v>147.6000061035156</v>
+        <v>145.19999694824219</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
       </c>
       <c r="F18">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G18">
-        <v>15.061225</v>
+        <v>14.816326</v>
       </c>
       <c r="H18">
-        <v>12.068685</v>
+        <v>11.872445000000001</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1472,30 +1487,30 @@
         <v>12.23</v>
       </c>
       <c r="O18">
-        <v>43.522607164441943</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+        <v>43.557804880980491</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19">
-        <v>143.1499938964844</v>
+        <v>143.94000244140619</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19">
         <v>197</v>
       </c>
       <c r="G19">
-        <v>28.744978</v>
+        <v>28.673307000000001</v>
       </c>
       <c r="H19">
-        <v>23.544407</v>
+        <v>23.674343</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1510,24 +1525,24 @@
         <v>18.415610746600951</v>
       </c>
       <c r="M19">
-        <v>4.9800000000000004</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="N19">
         <v>6.08</v>
       </c>
       <c r="O19">
-        <v>22.084124051759829</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+        <v>22.010444012934261</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20">
-        <v>138.0899963378906</v>
+        <v>139.1199951171875</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
@@ -1536,10 +1551,10 @@
         <v>230</v>
       </c>
       <c r="G20">
-        <v>14.706068999999999</v>
+        <v>14.690600999999999</v>
       </c>
       <c r="H20">
-        <v>12.429342999999999</v>
+        <v>12.522052</v>
       </c>
       <c r="I20" t="s">
         <v>17</v>
@@ -1554,36 +1569,36 @@
         <v>8.5314496054901205</v>
       </c>
       <c r="M20">
-        <v>9.39</v>
+        <v>9.4700000000000006</v>
       </c>
       <c r="N20">
         <v>11.11</v>
       </c>
       <c r="O20">
-        <v>25.840963928382148</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>25.816430111704971</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21">
-        <v>483.64999389648438</v>
+        <v>478.25</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F21">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G21">
-        <v>19.26125</v>
+        <v>19.046195999999998</v>
       </c>
       <c r="H21">
-        <v>16.625988</v>
+        <v>16.440356999999999</v>
       </c>
       <c r="I21" t="s">
         <v>17</v>
@@ -1604,18 +1619,18 @@
         <v>29.09</v>
       </c>
       <c r="O21">
-        <v>32.0530756528807</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>31.908045416524729</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22">
-        <v>457.3599853515625</v>
+        <v>460.3599853515625</v>
       </c>
       <c r="E22" t="s">
         <v>18</v>
@@ -1624,10 +1639,10 @@
         <v>72</v>
       </c>
       <c r="G22">
-        <v>35.592216000000001</v>
+        <v>35.576507999999997</v>
       </c>
       <c r="H22">
-        <v>30.592642000000001</v>
+        <v>30.793310000000002</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1642,36 +1657,36 @@
         <v>35.789415272465227</v>
       </c>
       <c r="M22">
-        <v>12.85</v>
+        <v>12.94</v>
       </c>
       <c r="N22">
         <v>14.95</v>
       </c>
       <c r="O22">
-        <v>25.895119354504359</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <v>25.66652697473976</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23">
-        <v>575.91998291015625</v>
+        <v>585.5999755859375</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G23">
-        <v>40.330531999999998</v>
+        <v>40.979706</v>
       </c>
       <c r="H23">
-        <v>35.159950000000002</v>
+        <v>35.750915999999997</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1686,36 +1701,36 @@
         <v>45.213112751383562</v>
       </c>
       <c r="M23">
-        <v>14.28</v>
+        <v>14.29</v>
       </c>
       <c r="N23">
         <v>16.38</v>
       </c>
       <c r="O23">
-        <v>21.29364441448611</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>21.305920868511311</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24">
-        <v>101.6800003051758</v>
+        <v>103.4899978637695</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G24">
-        <v>19.898240000000001</v>
+        <v>19.978764999999999</v>
       </c>
       <c r="H24">
-        <v>17.263159000000002</v>
+        <v>17.570460000000001</v>
       </c>
       <c r="I24" t="s">
         <v>17</v>
@@ -1730,36 +1745,36 @@
         <v>13.71198897276127</v>
       </c>
       <c r="M24">
-        <v>5.1100000000000003</v>
+        <v>5.18</v>
       </c>
       <c r="N24">
         <v>5.89</v>
       </c>
       <c r="O24">
-        <v>19.644063427409019</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>19.5287722803991</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25">
-        <v>97.239997863769531</v>
+        <v>98.720001220703125</v>
       </c>
       <c r="E25" t="s">
         <v>23</v>
       </c>
       <c r="F25">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G25">
-        <v>41.555557</v>
+        <v>42.188037999999999</v>
       </c>
       <c r="H25">
-        <v>35.75</v>
+        <v>36.294117</v>
       </c>
       <c r="I25" t="s">
         <v>17</v>
@@ -1780,30 +1795,30 @@
         <v>2.72</v>
       </c>
       <c r="O25">
-        <v>24.116996744382401</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <v>24.136404990110162</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D26">
-        <v>746.510009765625</v>
+        <v>736.77001953125</v>
       </c>
       <c r="E26" t="s">
         <v>18</v>
       </c>
       <c r="F26">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G26">
-        <v>29.588190000000001</v>
+        <v>29.672574999999998</v>
       </c>
       <c r="H26">
-        <v>27.959174999999998</v>
+        <v>27.594380999999998</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1818,24 +1833,24 @@
         <v>28.33459111814113</v>
       </c>
       <c r="M26">
-        <v>25.23</v>
+        <v>24.83</v>
       </c>
       <c r="N26">
         <v>26.7</v>
       </c>
       <c r="O26">
-        <v>48.632940880201943</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+        <v>48.639664239828797</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27">
-        <v>36.959999084472663</v>
+        <v>35.380001068115227</v>
       </c>
       <c r="E27" t="s">
         <v>26</v>
@@ -1844,10 +1859,10 @@
         <v>17</v>
       </c>
       <c r="G27">
-        <v>8.5161289999999994</v>
+        <v>8.2470870000000005</v>
       </c>
       <c r="H27">
-        <v>7.8638300000000001</v>
+        <v>7.52766</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1862,36 +1877,36 @@
         <v>7.9344361198138351</v>
       </c>
       <c r="M27">
-        <v>4.34</v>
+        <v>4.29</v>
       </c>
       <c r="N27">
         <v>4.7</v>
       </c>
       <c r="O27">
-        <v>48.886746359729202</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>48.4992367840483</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D28">
-        <v>114.4499969482422</v>
+        <v>117.7200012207031</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F28">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="G28">
-        <v>19.300169</v>
+        <v>19.522387999999999</v>
       </c>
       <c r="H28">
-        <v>18.052050000000001</v>
+        <v>18.567823000000001</v>
       </c>
       <c r="I28" t="s">
         <v>17</v>
@@ -1906,36 +1921,36 @@
         <v>15.220239866756501</v>
       </c>
       <c r="M28">
-        <v>5.93</v>
+        <v>6.03</v>
       </c>
       <c r="N28">
         <v>6.34</v>
       </c>
       <c r="O28">
-        <v>18.43932052986969</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+        <v>18.408465518113481</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D29">
-        <v>142.67999267578119</v>
+        <v>143.75999450683591</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
       </c>
       <c r="F29">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="G29">
-        <v>19.465209999999999</v>
+        <v>19.585830000000001</v>
       </c>
       <c r="H29">
-        <v>18.699867000000001</v>
+        <v>18.841415000000001</v>
       </c>
       <c r="I29" t="s">
         <v>17</v>
@@ -1950,36 +1965,36 @@
         <v>12.48164484200357</v>
       </c>
       <c r="M29">
-        <v>7.33</v>
+        <v>7.34</v>
       </c>
       <c r="N29">
         <v>7.63</v>
       </c>
       <c r="O29">
-        <v>19.623872206665808</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+        <v>19.410803664500161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D30">
-        <v>20.989999771118161</v>
+        <v>21.260000228881839</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F30">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="G30">
-        <v>9.4977370000000008</v>
+        <v>9.6199089999999998</v>
       </c>
       <c r="H30">
-        <v>9.5844749999999994</v>
+        <v>9.7077629999999999</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -2000,30 +2015,30 @@
         <v>2.19</v>
       </c>
       <c r="O30">
-        <v>28.04122875956385</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+        <v>27.989167428580419</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D31">
-        <v>172.36000061035159</v>
+        <v>171.74000549316409</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31">
         <v>49</v>
       </c>
       <c r="G31">
-        <v>19.236606999999999</v>
+        <v>19.167411999999999</v>
       </c>
       <c r="H31">
-        <v>19.236606999999999</v>
+        <v>19.167411999999999</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -2044,30 +2059,30 @@
         <v>8.9600000000000009</v>
       </c>
       <c r="O31">
-        <v>31.574767010973741</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+        <v>31.4997403111159</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D32">
-        <v>17.180000305175781</v>
+        <v>17.010000228881839</v>
       </c>
       <c r="E32" t="s">
         <v>26</v>
       </c>
       <c r="F32">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="G32">
-        <v>6.2021660000000001</v>
+        <v>6.0967745999999998</v>
       </c>
       <c r="H32">
-        <v>6.2472729999999999</v>
+        <v>6.1854550000000001</v>
       </c>
       <c r="I32" t="s">
         <v>17</v>
@@ -2082,36 +2097,36 @@
         <v>10.041387718820969</v>
       </c>
       <c r="M32">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="N32">
         <v>2.75</v>
       </c>
       <c r="O32">
-        <v>51.384809324994137</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+        <v>51.304260338805967</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D33">
-        <v>196.13999938964841</v>
+        <v>193.32000732421881</v>
       </c>
       <c r="E33" t="s">
         <v>18</v>
       </c>
       <c r="F33">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G33">
-        <v>23.517983999999998</v>
+        <v>23.207684</v>
       </c>
       <c r="H33">
-        <v>24.274754000000001</v>
+        <v>23.925743000000001</v>
       </c>
       <c r="I33" t="s">
         <v>17</v>
@@ -2126,36 +2141,36 @@
         <v>41.686769633025442</v>
       </c>
       <c r="M33">
-        <v>8.34</v>
+        <v>8.33</v>
       </c>
       <c r="N33">
         <v>8.08</v>
       </c>
       <c r="O33">
-        <v>46.612931232233286</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+        <v>46.628764253827377</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D34">
-        <v>43.279998779296882</v>
+        <v>43.819999694824219</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F34">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G34">
-        <v>16.332075</v>
+        <v>16.289963</v>
       </c>
       <c r="H34">
-        <v>16.456271999999998</v>
+        <v>16.661595999999999</v>
       </c>
       <c r="I34" t="s">
         <v>17</v>
@@ -2170,36 +2185,36 @@
         <v>11.435082528811259</v>
       </c>
       <c r="M34">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="N34">
         <v>2.63</v>
       </c>
       <c r="O34">
-        <v>19.759314059154189</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+        <v>19.608933461138701</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D35">
-        <v>42.330001831054688</v>
+        <v>41.430000305175781</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F35">
-        <v>3611</v>
+        <v>3680</v>
       </c>
       <c r="G35">
-        <v>6.6766562</v>
+        <v>6.5244099999999996</v>
       </c>
       <c r="H35">
-        <v>7.1745763</v>
+        <v>7.0220336999999997</v>
       </c>
       <c r="I35" t="s">
         <v>17</v>
@@ -2214,36 +2229,36 @@
         <v>28.104146008031432</v>
       </c>
       <c r="M35">
-        <v>6.34</v>
+        <v>6.35</v>
       </c>
       <c r="N35">
         <v>5.9</v>
       </c>
       <c r="O35">
-        <v>31.389912667582848</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+        <v>31.46845266789218</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D36">
-        <v>59.479999542236328</v>
+        <v>60.610000610351563</v>
       </c>
       <c r="E36" t="s">
         <v>23</v>
       </c>
       <c r="F36">
-        <v>686</v>
+        <v>673</v>
       </c>
       <c r="G36">
-        <v>9.9798659999999995</v>
+        <v>10.169463</v>
       </c>
       <c r="H36">
-        <v>11.117756999999999</v>
+        <v>11.328972</v>
       </c>
       <c r="I36" t="s">
         <v>17</v>
@@ -2264,30 +2279,30 @@
         <v>5.35</v>
       </c>
       <c r="O36">
-        <v>19.371332500047799</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+        <v>19.37592196843892</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D37">
-        <v>13.239999771118161</v>
+        <v>13.210000038146971</v>
       </c>
       <c r="E37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F37">
-        <v>517</v>
+        <v>530</v>
       </c>
       <c r="G37">
-        <v>7.480226</v>
+        <v>7.4632769999999997</v>
       </c>
       <c r="H37">
-        <v>14.085106</v>
+        <v>14.053191</v>
       </c>
       <c r="I37" t="s">
         <v>17</v>
@@ -2308,30 +2323,30 @@
         <v>0.94</v>
       </c>
       <c r="O37">
-        <v>30.76432809533885</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+        <v>30.651188255012919</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D38">
-        <v>17.64999961853027</v>
+        <v>17.829999923706051</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F38">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G38">
-        <v>8.8249999999999993</v>
+        <v>8.8706460000000007</v>
       </c>
       <c r="H38">
-        <v>16.809525000000001</v>
+        <v>16.980953</v>
       </c>
       <c r="I38" t="s">
         <v>17</v>
@@ -2346,36 +2361,36 @@
         <v>22.63225720298977</v>
       </c>
       <c r="M38">
-        <v>2</v>
+        <v>2.0099999999999998</v>
       </c>
       <c r="N38">
         <v>1.05</v>
       </c>
       <c r="O38">
-        <v>36.030116409956229</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+        <v>35.9546416978243</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D39">
-        <v>15.11999988555908</v>
+        <v>15.409999847412109</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F39">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G39">
-        <v>12.193548</v>
+        <v>12.427419</v>
       </c>
       <c r="H39">
-        <v>36.878048</v>
+        <v>37.585365000000003</v>
       </c>
       <c r="I39" t="s">
         <v>17</v>
@@ -2396,18 +2411,18 @@
         <v>0.41</v>
       </c>
       <c r="O39">
-        <v>36.591370228535979</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+        <v>36.547889626665622</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2440,18 +2455,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D41">
-        <v>19.309999465942379</v>
+        <v>18.569999694824219</v>
       </c>
       <c r="E41" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F41" t="s">
         <v>17</v>
@@ -2481,18 +2496,19 @@
         <v>17</v>
       </c>
       <c r="O41">
-        <v>19.309999465942379</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+        <f>D41</f>
+        <v>18.569999694824219</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D42">
-        <v>2.9000000953674321</v>
+        <v>3.0499999523162842</v>
       </c>
       <c r="E42" t="s">
         <v>18</v>
@@ -2504,7 +2520,7 @@
         <v>17</v>
       </c>
       <c r="H42">
-        <v>-0.52536229999999995</v>
+        <v>-0.55253624999999995</v>
       </c>
       <c r="I42" t="s">
         <v>17</v>
@@ -2525,21 +2541,21 @@
         <v>-5.52</v>
       </c>
       <c r="O42">
-        <v>171.77674673633391</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+        <v>168.36300614703711</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>28</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D43">
-        <v>19.384000778198239</v>
+        <v>19.41500091552734</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F43" t="s">
         <v>17</v>
@@ -2569,21 +2585,21 @@
         <v>17</v>
       </c>
       <c r="O43">
-        <v>14.91661087801284</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+        <v>14.845675850408311</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D44">
-        <v>6.0809998512268066</v>
+        <v>6.0929999351501456</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2613,21 +2629,21 @@
         <v>17</v>
       </c>
       <c r="O44">
-        <v>2.7014011886478619</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.6968399079145029</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D45">
-        <v>6.2430000305175781</v>
+        <v>6.2470002174377441</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2657,27 +2673,27 @@
         <v>17</v>
       </c>
       <c r="O45">
-        <v>2.7237334950374641</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.7216890458586769</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D46">
-        <v>72.529998779296875</v>
+        <v>72.772499084472656</v>
       </c>
       <c r="E46" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F46">
         <v>310</v>
       </c>
       <c r="G46">
-        <v>14.929224</v>
+        <v>14.979139</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2701,27 +2717,27 @@
         <v>17</v>
       </c>
       <c r="O46">
-        <v>14.06586937988955</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+        <v>13.9713823441376</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D47">
-        <v>47.340000152587891</v>
+        <v>47</v>
       </c>
       <c r="E47" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F47">
         <v>313</v>
       </c>
       <c r="G47">
-        <v>15.232957000000001</v>
+        <v>15.123552</v>
       </c>
       <c r="H47" t="s">
         <v>17</v>
@@ -2745,71 +2761,71 @@
         <v>17</v>
       </c>
       <c r="O47">
-        <v>18.586794711464769</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+        <v>18.607037242969241</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C48" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48">
+        <v>30.430000305175781</v>
+      </c>
+      <c r="E48" t="s">
         <v>78</v>
-      </c>
-      <c r="D48">
-        <v>31.329999923706051</v>
-      </c>
-      <c r="E48" t="s">
-        <v>77</v>
       </c>
       <c r="F48">
         <v>613</v>
       </c>
-      <c r="G48" t="s">
-        <v>17</v>
+      <c r="G48">
+        <v>14.421802</v>
       </c>
       <c r="H48">
-        <v>7.8718589999999997</v>
+        <v>7.6457286</v>
       </c>
       <c r="I48" t="s">
         <v>17</v>
       </c>
       <c r="J48">
-        <v>30.811</v>
+        <v>29.632000000000001</v>
       </c>
       <c r="K48">
-        <v>-404359008</v>
+        <v>602676992</v>
       </c>
       <c r="L48">
-        <v>-8.9286898337138769</v>
+        <v>13.44998752814737</v>
       </c>
       <c r="M48">
-        <v>-1.36</v>
+        <v>2.11</v>
       </c>
       <c r="N48">
         <v>3.98</v>
       </c>
       <c r="O48">
-        <v>43.253192279057693</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+        <v>43.37049360710914</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D49">
-        <v>587.72998046875</v>
+        <v>589.3900146484375</v>
       </c>
       <c r="E49" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F49">
         <v>129</v>
       </c>
       <c r="G49">
-        <v>25.608277999999999</v>
+        <v>25.680609</v>
       </c>
       <c r="H49" t="s">
         <v>17</v>
@@ -2833,21 +2849,21 @@
         <v>17</v>
       </c>
       <c r="O49">
-        <v>20.503184215131778</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+        <v>20.47577451540911</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D50">
-        <v>50.639999389648438</v>
+        <v>49.594001770019531</v>
       </c>
       <c r="E50" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F50" t="s">
         <v>17</v>
@@ -2877,21 +2893,21 @@
         <v>17</v>
       </c>
       <c r="O50">
-        <v>48.802430069394923</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+        <v>48.826061606836177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D51">
-        <v>15.382399559021</v>
+        <v>15.162599563598629</v>
       </c>
       <c r="E51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F51" t="s">
         <v>17</v>
@@ -2921,21 +2937,21 @@
         <v>17</v>
       </c>
       <c r="O51">
-        <v>25.26344986420008</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
+        <v>25.26302034088506</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D52">
-        <v>145.85499572753909</v>
+        <v>144.02099609375</v>
       </c>
       <c r="E52" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F52" t="s">
         <v>17</v>
@@ -2965,21 +2981,21 @@
         <v>17</v>
       </c>
       <c r="O52">
-        <v>11.23544605437033</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
+        <v>11.276721655654679</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>28</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -3012,24 +3028,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D54">
-        <v>20.440000534057621</v>
+        <v>20.354999542236332</v>
       </c>
       <c r="E54" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>31.177914000000001</v>
+        <v>31.048258000000001</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -3053,21 +3069,21 @@
         <v>17</v>
       </c>
       <c r="O54">
-        <v>26.11299617967083</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+        <v>26.152699379998602</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D55">
-        <v>72.370002746582031</v>
+        <v>72.769996643066406</v>
       </c>
       <c r="E55" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F55">
         <v>368</v>
@@ -3097,21 +3113,21 @@
         <v>17</v>
       </c>
       <c r="O55">
-        <v>5.3259126971205326</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+        <v>5.3119995185633773</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E56" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -3144,15 +3160,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D57">
-        <v>378.44000244140619</v>
+        <v>381.3900146484375</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -3161,10 +3177,10 @@
         <v>76</v>
       </c>
       <c r="G57">
-        <v>16.834520000000001</v>
+        <v>16.950665999999998</v>
       </c>
       <c r="H57">
-        <v>15.4150715</v>
+        <v>15.535235</v>
       </c>
       <c r="I57" t="s">
         <v>17</v>
@@ -3179,36 +3195,36 @@
         <v>8.0729203322391978</v>
       </c>
       <c r="M57">
-        <v>22.48</v>
+        <v>22.5</v>
       </c>
       <c r="N57">
         <v>24.55</v>
       </c>
       <c r="O57">
-        <v>28.66129029726293</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+        <v>28.47876722205304</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C58" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58">
+        <v>148.3500061035156</v>
+      </c>
+      <c r="E58" t="s">
         <v>90</v>
       </c>
-      <c r="D58">
-        <v>148.6600036621094</v>
-      </c>
-      <c r="E58" t="s">
-        <v>89</v>
-      </c>
       <c r="F58">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G58">
-        <v>18.513076999999999</v>
+        <v>18.474471999999999</v>
       </c>
       <c r="H58">
-        <v>18.817722</v>
+        <v>18.778482</v>
       </c>
       <c r="I58" t="s">
         <v>17</v>
@@ -3229,18 +3245,18 @@
         <v>7.9</v>
       </c>
       <c r="O58">
-        <v>36.104685815826308</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+        <v>36.075637474594878</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D59">
-        <v>123.7600021362305</v>
+        <v>131.7799987792969</v>
       </c>
       <c r="E59" t="s">
         <v>18</v>
@@ -3249,10 +3265,10 @@
         <v>17</v>
       </c>
       <c r="G59">
-        <v>515.66669999999999</v>
+        <v>599</v>
       </c>
       <c r="H59">
-        <v>263.31914999999998</v>
+        <v>280.38297</v>
       </c>
       <c r="I59" t="s">
         <v>17</v>
@@ -3267,36 +3283,36 @@
         <v>18.32059821851664</v>
       </c>
       <c r="M59">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="N59">
         <v>0.47</v>
       </c>
       <c r="O59">
-        <v>72.49017292245648</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+        <v>72.783241688775817</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D60">
-        <v>67.709999084472656</v>
+        <v>66.80999755859375</v>
       </c>
       <c r="E60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F60" t="s">
         <v>17</v>
       </c>
       <c r="G60">
-        <v>11.063725</v>
+        <v>10.916665999999999</v>
       </c>
       <c r="H60">
-        <v>9.7005730000000003</v>
+        <v>9.5716319999999993</v>
       </c>
       <c r="I60" t="s">
         <v>17</v>
@@ -3317,30 +3333,30 @@
         <v>6.98</v>
       </c>
       <c r="O60">
-        <v>40.605089472070219</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+        <v>40.613994794929283</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D61">
-        <v>43.479999542236328</v>
+        <v>43.650001525878913</v>
       </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F61">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G61">
-        <v>18.116665000000001</v>
+        <v>18.263597000000001</v>
       </c>
       <c r="H61">
-        <v>16.852713000000001</v>
+        <v>16.918606</v>
       </c>
       <c r="I61" t="s">
         <v>17</v>
@@ -3355,36 +3371,36 @@
         <v>8.087585993712608</v>
       </c>
       <c r="M61">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="N61">
         <v>2.58</v>
       </c>
       <c r="O61">
-        <v>41.784308731570867</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+        <v>41.926996580445383</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D62">
-        <v>16.89999961853027</v>
+        <v>16.879999160766602</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F62">
         <v>59</v>
       </c>
       <c r="G62">
-        <v>15.648148000000001</v>
+        <v>15.486238</v>
       </c>
       <c r="H62">
-        <v>11.418919000000001</v>
+        <v>11.405405</v>
       </c>
       <c r="I62" t="s">
         <v>17</v>
@@ -3399,36 +3415,36 @@
         <v>9.5758125530442939</v>
       </c>
       <c r="M62">
-        <v>1.08</v>
+        <v>1.0900000000000001</v>
       </c>
       <c r="N62">
         <v>1.48</v>
       </c>
       <c r="O62">
-        <v>26.31747093750727</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+        <v>26.301098247026331</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D63">
-        <v>18.360000610351559</v>
+        <v>18.079999923706051</v>
       </c>
       <c r="E63" t="s">
         <v>18</v>
       </c>
       <c r="F63">
-        <v>1634</v>
+        <v>1659</v>
       </c>
       <c r="G63" t="s">
         <v>17</v>
       </c>
       <c r="H63">
-        <v>9.5129540000000006</v>
+        <v>9.3678760000000008</v>
       </c>
       <c r="I63" t="s">
         <v>17</v>
@@ -3449,21 +3465,21 @@
         <v>1.93</v>
       </c>
       <c r="O63">
-        <v>74.526006142663462</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+        <v>74.536967647107673</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D64" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E64" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3496,15 +3512,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
       <c r="C65" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D65">
-        <v>10.159999847412109</v>
+        <v>10.52999973297119</v>
       </c>
       <c r="E65" t="s">
         <v>18</v>
@@ -3516,7 +3532,7 @@
         <v>17</v>
       </c>
       <c r="H65">
-        <v>3.5155706000000002</v>
+        <v>3.6435982999999998</v>
       </c>
       <c r="I65" t="s">
         <v>17</v>
@@ -3537,7 +3553,7 @@
         <v>2.89</v>
       </c>
       <c r="O65">
-        <v>83.313806007676703</v>
+        <v>83.35565568621584</v>
       </c>
     </row>
   </sheetData>

--- a/Stock Selection/tickers_used.xlsx
+++ b/Stock Selection/tickers_used.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/RodWal-Capital-Insights/Stock Selection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_4B2915855F41D20F62355476585DCE3A8747AAD9" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{731557F9-6281-4F17-86E3-6BD87DEA9731}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_2BB9D44F1E6E680F62355476585DCE3A8747A1ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35CA111A-A3C1-4A59-862C-8C7DB03CE62E}"/>
   <bookViews>
-    <workbookView xWindow="2928" yWindow="2928" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="100">
   <si>
     <t>Chapter</t>
   </si>
@@ -125,9 +125,6 @@
     <t>GC=F</t>
   </si>
   <si>
-    <t>Error: single positional indexer is out-of-bounds</t>
-  </si>
-  <si>
     <t>Unknown</t>
   </si>
   <si>
@@ -330,6 +327,12 @@
   </si>
   <si>
     <t>CSIQ</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>BAP</t>
   </si>
 </sst>
 </file>
@@ -692,10 +695,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O65"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:O67"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -742,7 +745,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
@@ -750,7 +753,7 @@
         <v>16</v>
       </c>
       <c r="D2">
-        <v>32.090000152587891</v>
+        <v>35.5</v>
       </c>
       <c r="E2" t="s">
         <v>15</v>
@@ -759,10 +762,10 @@
         <v>17</v>
       </c>
       <c r="G2">
-        <v>2.7807626999999999</v>
+        <v>3.0762564999999999</v>
       </c>
       <c r="H2">
-        <v>-5.2779610000000003</v>
+        <v>-5.8388156999999996</v>
       </c>
       <c r="I2" t="s">
         <v>17</v>
@@ -783,10 +786,10 @@
         <v>-6.08</v>
       </c>
       <c r="O2">
-        <v>56.481983456781727</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+        <v>51.84013469955979</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -794,7 +797,7 @@
         <v>19</v>
       </c>
       <c r="D3">
-        <v>192.41999816894531</v>
+        <v>199.7799987792969</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -803,10 +806,10 @@
         <v>17</v>
       </c>
       <c r="G3">
-        <v>111.22543</v>
+        <v>114.81609</v>
       </c>
       <c r="H3">
-        <v>26.725000000000001</v>
+        <v>27.747223000000002</v>
       </c>
       <c r="I3" t="s">
         <v>17</v>
@@ -821,16 +824,16 @@
         <v>13.94751334966173</v>
       </c>
       <c r="M3">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="N3">
         <v>7.2</v>
       </c>
       <c r="O3">
-        <v>36.242896395286991</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+        <v>36.182015501162681</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -838,43 +841,43 @@
         <v>20</v>
       </c>
       <c r="D4">
-        <v>242.07000732421881</v>
+        <v>251.25999450683591</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="G4">
-        <v>112.5907</v>
+        <v>91.700729999999993</v>
       </c>
       <c r="H4">
-        <v>39.233387</v>
+        <v>40.722850000000001</v>
       </c>
       <c r="I4" t="s">
         <v>17</v>
       </c>
       <c r="J4">
-        <v>52.890999999999998</v>
+        <v>54.54</v>
       </c>
       <c r="K4">
-        <v>10396999680</v>
+        <v>13240999936</v>
       </c>
       <c r="L4">
-        <v>19.066918134984039</v>
+        <v>23.211092846353111</v>
       </c>
       <c r="M4">
-        <v>2.15</v>
+        <v>2.74</v>
       </c>
       <c r="N4">
         <v>6.17</v>
       </c>
       <c r="O4">
-        <v>63.254562931019137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+        <v>61.833101755022092</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -882,7 +885,7 @@
         <v>22</v>
       </c>
       <c r="D5">
-        <v>31.159999847412109</v>
+        <v>38.549999237060547</v>
       </c>
       <c r="E5" t="s">
         <v>23</v>
@@ -891,10 +894,10 @@
         <v>17</v>
       </c>
       <c r="G5">
-        <v>29.121493999999998</v>
+        <v>36.028033999999998</v>
       </c>
       <c r="H5">
-        <v>10.421405</v>
+        <v>12.892977</v>
       </c>
       <c r="I5" t="s">
         <v>17</v>
@@ -915,10 +918,10 @@
         <v>2.99</v>
       </c>
       <c r="O5">
-        <v>43.385903025986948</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+        <v>44.94439518501521</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -926,19 +929,19 @@
         <v>25</v>
       </c>
       <c r="D6">
-        <v>29.229999542236332</v>
+        <v>31.760000228881839</v>
       </c>
       <c r="E6" t="s">
         <v>26</v>
       </c>
       <c r="F6">
-        <v>438</v>
+        <v>408</v>
       </c>
       <c r="G6">
-        <v>15.145078</v>
+        <v>16.628273</v>
       </c>
       <c r="H6">
-        <v>7.6518325999999997</v>
+        <v>8.3141365</v>
       </c>
       <c r="I6" t="s">
         <v>17</v>
@@ -953,16 +956,16 @@
         <v>4.8087837924487724</v>
       </c>
       <c r="M6">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="N6">
         <v>3.82</v>
       </c>
       <c r="O6">
-        <v>21.317009154977502</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+        <v>21.602152732406719</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -970,7 +973,7 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>158.08000183105469</v>
+        <v>143.66999816894531</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -979,10 +982,10 @@
         <v>17</v>
       </c>
       <c r="G7">
-        <v>13.419354999999999</v>
+        <v>12.206455999999999</v>
       </c>
       <c r="H7">
-        <v>7.5781400000000003</v>
+        <v>6.8873439999999997</v>
       </c>
       <c r="I7" t="s">
         <v>17</v>
@@ -997,30 +1000,30 @@
         <v>29.716643554944859</v>
       </c>
       <c r="M7">
-        <v>11.78</v>
+        <v>11.77</v>
       </c>
       <c r="N7">
         <v>20.86</v>
       </c>
       <c r="O7">
-        <v>60.408752216552678</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+        <v>62.909307077697058</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
       <c r="C8" t="s">
         <v>29</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8">
+        <v>3387.39990234375</v>
+      </c>
+      <c r="E8" t="s">
         <v>30</v>
       </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
+      <c r="F8" t="s">
+        <v>17</v>
       </c>
       <c r="G8" t="s">
         <v>17</v>
@@ -1046,31 +1049,31 @@
       <c r="N8" t="s">
         <v>17</v>
       </c>
-      <c r="O8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="O8">
+        <v>18.306608171720249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>21</v>
       </c>
       <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9">
+        <v>17.610000610351559</v>
+      </c>
+      <c r="E9" t="s">
         <v>32</v>
       </c>
-      <c r="D9">
-        <v>17.35000038146973</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
       <c r="F9">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G9">
-        <v>19.277778999999999</v>
+        <v>19.566668</v>
       </c>
       <c r="H9">
-        <v>12.392858</v>
+        <v>12.578571999999999</v>
       </c>
       <c r="I9" t="s">
         <v>17</v>
@@ -1091,30 +1094,30 @@
         <v>1.4</v>
       </c>
       <c r="O9">
-        <v>43.59653161446694</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+        <v>43.774884892404998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10">
-        <v>110.0800018310547</v>
+        <v>108</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
       <c r="F10">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G10">
-        <v>23.126048999999998</v>
+        <v>22.689074999999999</v>
       </c>
       <c r="H10">
-        <v>14.815613000000001</v>
+        <v>14.535666000000001</v>
       </c>
       <c r="I10" t="s">
         <v>17</v>
@@ -1135,18 +1138,18 @@
         <v>7.43</v>
       </c>
       <c r="O10">
-        <v>27.404183030306822</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+        <v>26.178633288046029</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11">
-        <v>135.1300048828125</v>
+        <v>145.47999572753909</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -1155,10 +1158,10 @@
         <v>3</v>
       </c>
       <c r="G11">
-        <v>43.731395999999997</v>
+        <v>46.929029999999997</v>
       </c>
       <c r="H11">
-        <v>32.798546000000002</v>
+        <v>35.310679999999998</v>
       </c>
       <c r="I11" t="s">
         <v>17</v>
@@ -1173,36 +1176,36 @@
         <v>51.694442005172633</v>
       </c>
       <c r="M11">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="N11">
         <v>4.12</v>
       </c>
       <c r="O11">
-        <v>59.061403712338908</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+        <v>58.389431514281839</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>24</v>
       </c>
       <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12">
+        <v>71.569999694824219</v>
+      </c>
+      <c r="E12" t="s">
         <v>36</v>
       </c>
-      <c r="D12">
-        <v>70.639999389648438</v>
-      </c>
-      <c r="E12" t="s">
-        <v>37</v>
-      </c>
       <c r="F12">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="G12">
-        <v>26.456928000000001</v>
+        <v>26.805243000000001</v>
       </c>
       <c r="H12">
-        <v>19.195651999999999</v>
+        <v>19.448370000000001</v>
       </c>
       <c r="I12" t="s">
         <v>17</v>
@@ -1223,30 +1226,30 @@
         <v>3.68</v>
       </c>
       <c r="O12">
-        <v>29.629583601540769</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+        <v>28.968142201265241</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D13">
-        <v>22.229999542236332</v>
+        <v>21.090000152587891</v>
       </c>
       <c r="E13" t="s">
         <v>23</v>
       </c>
       <c r="F13">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="G13">
-        <v>13.554878</v>
+        <v>12.859756000000001</v>
       </c>
       <c r="H13">
-        <v>9.7929519999999997</v>
+        <v>9.2907489999999999</v>
       </c>
       <c r="I13" t="s">
         <v>17</v>
@@ -1267,30 +1270,30 @@
         <v>2.27</v>
       </c>
       <c r="O13">
-        <v>24.93436661262972</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+        <v>25.093466891775378</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14">
-        <v>156.75</v>
+        <v>172.8399963378906</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
       </c>
       <c r="F14">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G14">
-        <v>19.092569999999998</v>
+        <v>21.001214999999998</v>
       </c>
       <c r="H14">
-        <v>16.176472</v>
+        <v>17.836946000000001</v>
       </c>
       <c r="I14" t="s">
         <v>17</v>
@@ -1305,36 +1308,36 @@
         <v>24.059240782505299</v>
       </c>
       <c r="M14">
-        <v>8.2100000000000009</v>
+        <v>8.23</v>
       </c>
       <c r="N14">
         <v>9.69</v>
       </c>
       <c r="O14">
-        <v>48.908876698407347</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+        <v>48.643487855208093</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15">
-        <v>200.8500061035156</v>
+        <v>196.58000183105469</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
       </c>
       <c r="F15">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G15">
-        <v>31.236393</v>
+        <v>30.572319</v>
       </c>
       <c r="H15">
-        <v>24.169674000000001</v>
+        <v>23.655836000000001</v>
       </c>
       <c r="I15" t="s">
         <v>17</v>
@@ -1355,30 +1358,30 @@
         <v>8.31</v>
       </c>
       <c r="O15">
-        <v>33.23293560720505</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+        <v>32.254655201655787</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D16">
-        <v>131.44999694824219</v>
+        <v>129.07000732421881</v>
       </c>
       <c r="E16" t="s">
         <v>23</v>
       </c>
       <c r="F16">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="G16">
-        <v>19.330881000000002</v>
+        <v>18.980882999999999</v>
       </c>
       <c r="H16">
-        <v>15.23175</v>
+        <v>14.955968</v>
       </c>
       <c r="I16" t="s">
         <v>17</v>
@@ -1399,30 +1402,30 @@
         <v>8.6300000000000008</v>
       </c>
       <c r="O16">
-        <v>19.582690445835969</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+        <v>19.511122017696149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
         <v>42</v>
       </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
       <c r="D17">
-        <v>365.19000244140619</v>
+        <v>340.3800048828125</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G17">
-        <v>36.776435999999997</v>
+        <v>34.243459999999999</v>
       </c>
       <c r="H17">
-        <v>28.845972</v>
+        <v>26.886257000000001</v>
       </c>
       <c r="I17" t="s">
         <v>17</v>
@@ -1437,36 +1440,36 @@
         <v>52.210202623591513</v>
       </c>
       <c r="M17">
-        <v>9.93</v>
+        <v>9.94</v>
       </c>
       <c r="N17">
         <v>12.66</v>
       </c>
       <c r="O17">
-        <v>22.100144995778599</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+        <v>23.14206432951104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D18">
-        <v>145.19999694824219</v>
+        <v>153.6300048828125</v>
       </c>
       <c r="E18" t="s">
         <v>18</v>
       </c>
       <c r="F18">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="G18">
-        <v>14.816326</v>
+        <v>15.676531000000001</v>
       </c>
       <c r="H18">
-        <v>11.872445000000001</v>
+        <v>12.561734</v>
       </c>
       <c r="I18" t="s">
         <v>17</v>
@@ -1487,30 +1490,30 @@
         <v>12.23</v>
       </c>
       <c r="O18">
-        <v>43.557804880980491</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+        <v>43.139882091532428</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D19">
-        <v>143.94000244140619</v>
+        <v>138.36000061035159</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G19">
-        <v>28.673307000000001</v>
+        <v>27.561751999999998</v>
       </c>
       <c r="H19">
-        <v>23.674343</v>
+        <v>22.756578000000001</v>
       </c>
       <c r="I19" t="s">
         <v>17</v>
@@ -1531,30 +1534,30 @@
         <v>6.08</v>
       </c>
       <c r="O19">
-        <v>22.010444012934261</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+        <v>21.987103006840659</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D20">
-        <v>139.1199951171875</v>
+        <v>136.8999938964844</v>
       </c>
       <c r="E20" t="s">
         <v>23</v>
       </c>
       <c r="F20">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G20">
-        <v>14.690600999999999</v>
+        <v>14.456177</v>
       </c>
       <c r="H20">
-        <v>12.522052</v>
+        <v>12.322232</v>
       </c>
       <c r="I20" t="s">
         <v>17</v>
@@ -1575,30 +1578,30 @@
         <v>11.11</v>
       </c>
       <c r="O20">
-        <v>25.816430111704971</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+        <v>25.75591338359169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21">
-        <v>478.25</v>
+        <v>452.54998779296881</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="G21">
-        <v>19.046195999999998</v>
+        <v>18.0227</v>
       </c>
       <c r="H21">
-        <v>16.440356999999999</v>
+        <v>15.556891</v>
       </c>
       <c r="I21" t="s">
         <v>17</v>
@@ -1619,30 +1622,30 @@
         <v>29.09</v>
       </c>
       <c r="O21">
-        <v>31.908045416524729</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+        <v>31.79772441233456</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D22">
-        <v>460.3599853515625</v>
+        <v>480.239990234375</v>
       </c>
       <c r="E22" t="s">
         <v>18</v>
       </c>
       <c r="F22">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G22">
-        <v>35.576507999999997</v>
+        <v>37.170276999999999</v>
       </c>
       <c r="H22">
-        <v>30.793310000000002</v>
+        <v>32.123077000000002</v>
       </c>
       <c r="I22" t="s">
         <v>17</v>
@@ -1657,36 +1660,36 @@
         <v>35.789415272465227</v>
       </c>
       <c r="M22">
-        <v>12.94</v>
+        <v>12.92</v>
       </c>
       <c r="N22">
         <v>14.95</v>
       </c>
       <c r="O22">
-        <v>25.66652697473976</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+        <v>25.534970140930021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23">
-        <v>585.5999755859375</v>
+        <v>538.72998046875</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23">
-        <v>52</v>
+        <v>56.000000000000007</v>
       </c>
       <c r="G23">
-        <v>40.979706</v>
+        <v>37.726190000000003</v>
       </c>
       <c r="H23">
-        <v>35.750915999999997</v>
+        <v>32.889499999999998</v>
       </c>
       <c r="I23" t="s">
         <v>17</v>
@@ -1701,36 +1704,36 @@
         <v>45.213112751383562</v>
       </c>
       <c r="M23">
-        <v>14.29</v>
+        <v>14.28</v>
       </c>
       <c r="N23">
         <v>16.38</v>
       </c>
       <c r="O23">
-        <v>21.305920868511311</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+        <v>22.524989101788279</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D24">
-        <v>103.4899978637695</v>
+        <v>101.1999969482422</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F24">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="G24">
-        <v>19.978764999999999</v>
+        <v>19.53668</v>
       </c>
       <c r="H24">
-        <v>17.570460000000001</v>
+        <v>17.181664000000001</v>
       </c>
       <c r="I24" t="s">
         <v>17</v>
@@ -1751,36 +1754,36 @@
         <v>5.89</v>
       </c>
       <c r="O24">
-        <v>19.5287722803991</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+        <v>19.532099410079969</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D25">
-        <v>98.720001220703125</v>
+        <v>95.089996337890625</v>
       </c>
       <c r="E25" t="s">
         <v>23</v>
       </c>
       <c r="F25">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G25">
-        <v>42.188037999999999</v>
+        <v>40.636752999999999</v>
       </c>
       <c r="H25">
-        <v>36.294117</v>
+        <v>34.959556999999997</v>
       </c>
       <c r="I25" t="s">
         <v>17</v>
       </c>
       <c r="J25">
-        <v>6.2039999999999997</v>
+        <v>6.2409999999999997</v>
       </c>
       <c r="K25">
         <v>18819000320</v>
@@ -1795,30 +1798,30 @@
         <v>2.72</v>
       </c>
       <c r="O25">
-        <v>24.136404990110162</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+        <v>24.146619281851219</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26">
-        <v>736.77001953125</v>
+        <v>761.6400146484375</v>
       </c>
       <c r="E26" t="s">
         <v>18</v>
       </c>
       <c r="F26">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G26">
-        <v>29.672574999999998</v>
+        <v>29.763190000000002</v>
       </c>
       <c r="H26">
-        <v>27.594380999999998</v>
+        <v>28.525842999999998</v>
       </c>
       <c r="I26" t="s">
         <v>17</v>
@@ -1833,24 +1836,24 @@
         <v>28.33459111814113</v>
       </c>
       <c r="M26">
-        <v>24.83</v>
+        <v>25.59</v>
       </c>
       <c r="N26">
         <v>26.7</v>
       </c>
       <c r="O26">
-        <v>48.639664239828797</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+        <v>47.604728667504432</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>24</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D27">
-        <v>35.380001068115227</v>
+        <v>35.279998779296882</v>
       </c>
       <c r="E27" t="s">
         <v>26</v>
@@ -1859,10 +1862,10 @@
         <v>17</v>
       </c>
       <c r="G27">
-        <v>8.2470870000000005</v>
+        <v>8.2237760000000009</v>
       </c>
       <c r="H27">
-        <v>7.52766</v>
+        <v>7.5063829999999996</v>
       </c>
       <c r="I27" t="s">
         <v>17</v>
@@ -1883,30 +1886,30 @@
         <v>4.7</v>
       </c>
       <c r="O27">
-        <v>48.4992367840483</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+        <v>47.857041571377373</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28">
-        <v>117.7200012207031</v>
+        <v>114.5800018310547</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="G28">
-        <v>19.522387999999999</v>
+        <v>19.001657000000002</v>
       </c>
       <c r="H28">
-        <v>18.567823000000001</v>
+        <v>18.072555999999999</v>
       </c>
       <c r="I28" t="s">
         <v>17</v>
@@ -1927,30 +1930,30 @@
         <v>6.34</v>
       </c>
       <c r="O28">
-        <v>18.408465518113481</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+        <v>18.288821806463691</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>21</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D29">
-        <v>143.75999450683591</v>
+        <v>127.9599990844727</v>
       </c>
       <c r="E29" t="s">
         <v>23</v>
       </c>
       <c r="F29">
-        <v>350</v>
+        <v>394</v>
       </c>
       <c r="G29">
-        <v>19.585830000000001</v>
+        <v>17.433243000000001</v>
       </c>
       <c r="H29">
-        <v>18.841415000000001</v>
+        <v>16.770641000000001</v>
       </c>
       <c r="I29" t="s">
         <v>17</v>
@@ -1971,30 +1974,30 @@
         <v>7.63</v>
       </c>
       <c r="O29">
-        <v>19.410803664500161</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+        <v>19.42880627327235</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30">
-        <v>21.260000228881839</v>
+        <v>20.780000686645511</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="G30">
-        <v>9.6199089999999998</v>
+        <v>9.1140360000000005</v>
       </c>
       <c r="H30">
-        <v>9.7077629999999999</v>
+        <v>9.4885845</v>
       </c>
       <c r="I30" t="s">
         <v>17</v>
@@ -2009,36 +2012,36 @@
         <v>25.984840469640911</v>
       </c>
       <c r="M30">
-        <v>2.21</v>
+        <v>2.2799999999999998</v>
       </c>
       <c r="N30">
         <v>2.19</v>
       </c>
       <c r="O30">
-        <v>27.989167428580419</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+        <v>27.232077610448869</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>18</v>
       </c>
       <c r="C31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31">
+        <v>173.32000732421881</v>
+      </c>
+      <c r="E31" t="s">
         <v>57</v>
       </c>
-      <c r="D31">
-        <v>171.74000549316409</v>
-      </c>
-      <c r="E31" t="s">
-        <v>58</v>
-      </c>
       <c r="F31">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G31">
-        <v>19.167411999999999</v>
+        <v>19.34375</v>
       </c>
       <c r="H31">
-        <v>19.167411999999999</v>
+        <v>19.34375</v>
       </c>
       <c r="I31" t="s">
         <v>17</v>
@@ -2059,30 +2062,30 @@
         <v>8.9600000000000009</v>
       </c>
       <c r="O31">
-        <v>31.4997403111159</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+        <v>31.7764028506854</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>24</v>
       </c>
       <c r="C32" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D32">
-        <v>17.010000228881839</v>
+        <v>20.309999465942379</v>
       </c>
       <c r="E32" t="s">
         <v>26</v>
       </c>
       <c r="F32">
-        <v>588</v>
+        <v>492</v>
       </c>
       <c r="G32">
-        <v>6.0967745999999998</v>
+        <v>7.2795696000000003</v>
       </c>
       <c r="H32">
-        <v>6.1854550000000001</v>
+        <v>7.3854540000000002</v>
       </c>
       <c r="I32" t="s">
         <v>17</v>
@@ -2103,30 +2106,30 @@
         <v>2.75</v>
       </c>
       <c r="O32">
-        <v>51.304260338805967</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+        <v>52.05274095647362</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D33">
-        <v>193.32000732421881</v>
+        <v>213.5</v>
       </c>
       <c r="E33" t="s">
         <v>18</v>
       </c>
       <c r="F33">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="G33">
-        <v>23.207684</v>
+        <v>25</v>
       </c>
       <c r="H33">
-        <v>23.925743000000001</v>
+        <v>26.423266999999999</v>
       </c>
       <c r="I33" t="s">
         <v>17</v>
@@ -2141,36 +2144,36 @@
         <v>41.686769633025442</v>
       </c>
       <c r="M33">
-        <v>8.33</v>
+        <v>8.5399999999999991</v>
       </c>
       <c r="N33">
         <v>8.08</v>
       </c>
       <c r="O33">
-        <v>46.628764253827377</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+        <v>45.846279954867072</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D34">
-        <v>43.819999694824219</v>
+        <v>42.369998931884773</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F34">
-        <v>365</v>
+        <v>378</v>
       </c>
       <c r="G34">
-        <v>16.289963</v>
+        <v>15.750928999999999</v>
       </c>
       <c r="H34">
-        <v>16.661595999999999</v>
+        <v>16.110265999999999</v>
       </c>
       <c r="I34" t="s">
         <v>17</v>
@@ -2191,30 +2194,30 @@
         <v>2.63</v>
       </c>
       <c r="O34">
-        <v>19.608933461138701</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+        <v>19.252426111837181</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D35">
-        <v>41.430000305175781</v>
+        <v>43.209999084472663</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F35">
-        <v>3680</v>
+        <v>3529</v>
       </c>
       <c r="G35">
-        <v>6.5244099999999996</v>
+        <v>6.7621283999999999</v>
       </c>
       <c r="H35">
-        <v>7.0220336999999997</v>
+        <v>7.3237285999999999</v>
       </c>
       <c r="I35" t="s">
         <v>17</v>
@@ -2229,36 +2232,36 @@
         <v>28.104146008031432</v>
       </c>
       <c r="M35">
-        <v>6.35</v>
+        <v>6.39</v>
       </c>
       <c r="N35">
         <v>5.9</v>
       </c>
       <c r="O35">
-        <v>31.46845266789218</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+        <v>31.614182891395409</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D36">
-        <v>60.610000610351563</v>
+        <v>59.490001678466797</v>
       </c>
       <c r="E36" t="s">
         <v>23</v>
       </c>
       <c r="F36">
-        <v>673</v>
+        <v>686</v>
       </c>
       <c r="G36">
-        <v>10.169463</v>
+        <v>9.9815439999999995</v>
       </c>
       <c r="H36">
-        <v>11.328972</v>
+        <v>11.119626999999999</v>
       </c>
       <c r="I36" t="s">
         <v>17</v>
@@ -2279,30 +2282,30 @@
         <v>5.35</v>
       </c>
       <c r="O36">
-        <v>19.37592196843892</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+        <v>19.485964723138071</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D37">
-        <v>13.210000038146971</v>
+        <v>12.840000152587891</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F37">
-        <v>530</v>
+        <v>535</v>
       </c>
       <c r="G37">
-        <v>7.4632769999999997</v>
+        <v>7.2542377</v>
       </c>
       <c r="H37">
-        <v>14.053191</v>
+        <v>13.6595745</v>
       </c>
       <c r="I37" t="s">
         <v>17</v>
@@ -2323,30 +2326,30 @@
         <v>0.94</v>
       </c>
       <c r="O37">
-        <v>30.651188255012919</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+        <v>30.142040184122731</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D38">
-        <v>17.829999923706051</v>
+        <v>17.659999847412109</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F38">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G38">
-        <v>8.8706460000000007</v>
+        <v>8.6995079999999998</v>
       </c>
       <c r="H38">
-        <v>16.980953</v>
+        <v>16.819047999999999</v>
       </c>
       <c r="I38" t="s">
         <v>17</v>
@@ -2361,36 +2364,36 @@
         <v>22.63225720298977</v>
       </c>
       <c r="M38">
-        <v>2.0099999999999998</v>
+        <v>2.0299999999999998</v>
       </c>
       <c r="N38">
         <v>1.05</v>
       </c>
       <c r="O38">
-        <v>35.9546416978243</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+        <v>35.93340686435748</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D39">
-        <v>15.409999847412109</v>
+        <v>14.939999580383301</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F39">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="G39">
-        <v>12.427419</v>
+        <v>11.952</v>
       </c>
       <c r="H39">
-        <v>37.585365000000003</v>
+        <v>36.439022000000001</v>
       </c>
       <c r="I39" t="s">
         <v>17</v>
@@ -2405,24 +2408,24 @@
         <v>22.5677633341305</v>
       </c>
       <c r="M39">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="N39">
         <v>0.41</v>
       </c>
       <c r="O39">
-        <v>36.547889626665622</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+        <v>36.395177989580901</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" t="s">
         <v>67</v>
       </c>
-      <c r="D40" t="s">
-        <v>68</v>
-      </c>
       <c r="E40" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F40">
         <v>0</v>
@@ -2455,18 +2458,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" t="s">
         <v>69</v>
       </c>
-      <c r="C41" t="s">
-        <v>70</v>
-      </c>
       <c r="D41">
-        <v>18.569999694824219</v>
+        <v>22.170000076293949</v>
       </c>
       <c r="E41" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
         <v>17</v>
@@ -2497,18 +2500,18 @@
       </c>
       <c r="O41">
         <f>D41</f>
-        <v>18.569999694824219</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+        <v>22.170000076293949</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D42">
-        <v>3.0499999523162842</v>
+        <v>2.9900000095367432</v>
       </c>
       <c r="E42" t="s">
         <v>18</v>
@@ -2520,7 +2523,7 @@
         <v>17</v>
       </c>
       <c r="H42">
-        <v>-0.55253624999999995</v>
+        <v>-0.54166669999999995</v>
       </c>
       <c r="I42" t="s">
         <v>17</v>
@@ -2541,65 +2544,65 @@
         <v>-5.52</v>
       </c>
       <c r="O42">
-        <v>168.36300614703711</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+        <v>167.24498492839689</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>28</v>
       </c>
       <c r="C43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D43">
+        <v>19.029119491577148</v>
+      </c>
+      <c r="E43" t="s">
+        <v>30</v>
+      </c>
+      <c r="F43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>17</v>
+      </c>
+      <c r="O43">
+        <v>13.649438496972239</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>72</v>
       </c>
-      <c r="D43">
-        <v>19.41500091552734</v>
-      </c>
-      <c r="E43" t="s">
-        <v>31</v>
-      </c>
-      <c r="F43" t="s">
-        <v>17</v>
-      </c>
-      <c r="G43" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" t="s">
-        <v>17</v>
-      </c>
-      <c r="I43" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" t="s">
-        <v>17</v>
-      </c>
-      <c r="K43" t="s">
-        <v>17</v>
-      </c>
-      <c r="L43" t="s">
-        <v>17</v>
-      </c>
-      <c r="M43" t="s">
-        <v>17</v>
-      </c>
-      <c r="N43" t="s">
-        <v>17</v>
-      </c>
-      <c r="O43">
-        <v>14.845675850408311</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
+      <c r="C44" t="s">
         <v>73</v>
       </c>
-      <c r="C44" t="s">
-        <v>74</v>
-      </c>
       <c r="D44">
-        <v>6.0929999351501456</v>
+        <v>6.1149997711181641</v>
       </c>
       <c r="E44" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F44">
         <v>0</v>
@@ -2629,21 +2632,21 @@
         <v>17</v>
       </c>
       <c r="O44">
-        <v>2.6968399079145029</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.6744961612298939</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45">
-        <v>6.2470002174377441</v>
+        <v>6.2610001564025879</v>
       </c>
       <c r="E45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F45">
         <v>0</v>
@@ -2673,27 +2676,27 @@
         <v>17</v>
       </c>
       <c r="O45">
-        <v>2.7216890458586769</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+        <v>2.7157582188855081</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D46">
-        <v>72.772499084472656</v>
+        <v>71.949996948242188</v>
       </c>
       <c r="E46" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F46">
         <v>310</v>
       </c>
       <c r="G46">
-        <v>14.979139</v>
+        <v>14.809839</v>
       </c>
       <c r="H46" t="s">
         <v>17</v>
@@ -2717,74 +2720,74 @@
         <v>17</v>
       </c>
       <c r="O46">
-        <v>13.9713823441376</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+        <v>14.034326054518139</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C47" t="s">
+        <v>76</v>
+      </c>
+      <c r="D47">
+        <v>48.150001525878913</v>
+      </c>
+      <c r="E47" t="s">
+        <v>30</v>
+      </c>
+      <c r="F47">
+        <v>302</v>
+      </c>
+      <c r="G47">
+        <v>15.493598</v>
+      </c>
+      <c r="H47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" t="s">
+        <v>17</v>
+      </c>
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" t="s">
+        <v>17</v>
+      </c>
+      <c r="O47">
+        <v>18.59298580482179</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>77</v>
       </c>
-      <c r="D47">
-        <v>47</v>
-      </c>
-      <c r="E47" t="s">
-        <v>31</v>
-      </c>
-      <c r="F47">
-        <v>313</v>
-      </c>
-      <c r="G47">
-        <v>15.123552</v>
-      </c>
-      <c r="H47" t="s">
-        <v>17</v>
-      </c>
-      <c r="I47" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" t="s">
-        <v>17</v>
-      </c>
-      <c r="K47" t="s">
-        <v>17</v>
-      </c>
-      <c r="L47" t="s">
-        <v>17</v>
-      </c>
-      <c r="M47" t="s">
-        <v>17</v>
-      </c>
-      <c r="N47" t="s">
-        <v>17</v>
-      </c>
-      <c r="O47">
-        <v>18.607037242969241</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A48" t="s">
+      <c r="C48" t="s">
         <v>78</v>
       </c>
-      <c r="C48" t="s">
-        <v>79</v>
-      </c>
       <c r="D48">
-        <v>30.430000305175781</v>
+        <v>33.110000610351563</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F48">
         <v>613</v>
       </c>
       <c r="G48">
-        <v>14.421802</v>
+        <v>15.691943999999999</v>
       </c>
       <c r="H48">
-        <v>7.6457286</v>
+        <v>8.319096</v>
       </c>
       <c r="I48" t="s">
         <v>17</v>
@@ -2805,109 +2808,109 @@
         <v>3.98</v>
       </c>
       <c r="O48">
-        <v>43.37049360710914</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+        <v>43.515408656187979</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49">
+        <v>597.44000244140625</v>
+      </c>
+      <c r="E49" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49">
+        <v>121</v>
+      </c>
+      <c r="G49">
+        <v>25.825686000000001</v>
+      </c>
+      <c r="H49" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49" t="s">
+        <v>17</v>
+      </c>
+      <c r="M49" t="s">
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>17</v>
+      </c>
+      <c r="O49">
+        <v>20.538686659962941</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" t="s">
         <v>80</v>
       </c>
-      <c r="D49">
-        <v>589.3900146484375</v>
-      </c>
-      <c r="E49" t="s">
-        <v>31</v>
-      </c>
-      <c r="F49">
-        <v>129</v>
-      </c>
-      <c r="G49">
-        <v>25.680609</v>
-      </c>
-      <c r="H49" t="s">
-        <v>17</v>
-      </c>
-      <c r="I49" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" t="s">
-        <v>17</v>
-      </c>
-      <c r="K49" t="s">
-        <v>17</v>
-      </c>
-      <c r="L49" t="s">
-        <v>17</v>
-      </c>
-      <c r="M49" t="s">
-        <v>17</v>
-      </c>
-      <c r="N49" t="s">
-        <v>17</v>
-      </c>
-      <c r="O49">
-        <v>20.47577451540911</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>73</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="D50">
+        <v>48.374000549316413</v>
+      </c>
+      <c r="E50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F50" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50" t="s">
+        <v>17</v>
+      </c>
+      <c r="M50" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" t="s">
+        <v>17</v>
+      </c>
+      <c r="O50">
+        <v>48.548662562918622</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" t="s">
         <v>81</v>
       </c>
-      <c r="D50">
-        <v>49.594001770019531</v>
-      </c>
-      <c r="E50" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" t="s">
-        <v>17</v>
-      </c>
-      <c r="G50" t="s">
-        <v>17</v>
-      </c>
-      <c r="H50" t="s">
-        <v>17</v>
-      </c>
-      <c r="I50" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" t="s">
-        <v>17</v>
-      </c>
-      <c r="K50" t="s">
-        <v>17</v>
-      </c>
-      <c r="L50" t="s">
-        <v>17</v>
-      </c>
-      <c r="M50" t="s">
-        <v>17</v>
-      </c>
-      <c r="N50" t="s">
-        <v>17</v>
-      </c>
-      <c r="O50">
-        <v>48.826061606836177</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" t="s">
-        <v>82</v>
-      </c>
       <c r="D51">
-        <v>15.162599563598629</v>
+        <v>14.990200042724609</v>
       </c>
       <c r="E51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F51" t="s">
         <v>17</v>
@@ -2937,21 +2940,21 @@
         <v>17</v>
       </c>
       <c r="O51">
-        <v>25.26302034088506</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+        <v>25.44489083695931</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D52">
-        <v>144.02099609375</v>
+        <v>145.48699951171881</v>
       </c>
       <c r="E52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F52" t="s">
         <v>17</v>
@@ -2981,21 +2984,21 @@
         <v>17</v>
       </c>
       <c r="O52">
-        <v>11.276721655654679</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+        <v>11.419883637983061</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>28</v>
       </c>
       <c r="C53" t="s">
+        <v>83</v>
+      </c>
+      <c r="D53" t="s">
         <v>84</v>
       </c>
-      <c r="D53" t="s">
-        <v>85</v>
-      </c>
       <c r="E53" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F53">
         <v>0</v>
@@ -3028,24 +3031,24 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D54">
-        <v>20.354999542236332</v>
+        <v>20</v>
       </c>
       <c r="E54" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>31.048258000000001</v>
+        <v>30.506762999999999</v>
       </c>
       <c r="H54" t="s">
         <v>17</v>
@@ -3069,65 +3072,65 @@
         <v>17</v>
       </c>
       <c r="O54">
-        <v>26.152699379998602</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+        <v>26.06381059411537</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
+        <v>86</v>
+      </c>
+      <c r="D55">
+        <v>72.830001831054688</v>
+      </c>
+      <c r="E55" t="s">
+        <v>30</v>
+      </c>
+      <c r="F55">
+        <v>375</v>
+      </c>
+      <c r="G55" t="s">
+        <v>17</v>
+      </c>
+      <c r="H55" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55" t="s">
+        <v>17</v>
+      </c>
+      <c r="L55" t="s">
+        <v>17</v>
+      </c>
+      <c r="M55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>17</v>
+      </c>
+      <c r="O55">
+        <v>5.2444131348715466</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" t="s">
         <v>87</v>
       </c>
-      <c r="D55">
-        <v>72.769996643066406</v>
-      </c>
-      <c r="E55" t="s">
-        <v>31</v>
-      </c>
-      <c r="F55">
-        <v>368</v>
-      </c>
-      <c r="G55" t="s">
-        <v>17</v>
-      </c>
-      <c r="H55" t="s">
-        <v>17</v>
-      </c>
-      <c r="I55" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" t="s">
-        <v>17</v>
-      </c>
-      <c r="K55" t="s">
-        <v>17</v>
-      </c>
-      <c r="L55" t="s">
-        <v>17</v>
-      </c>
-      <c r="M55" t="s">
-        <v>17</v>
-      </c>
-      <c r="N55" t="s">
-        <v>17</v>
-      </c>
-      <c r="O55">
-        <v>5.3119995185633773</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" t="s">
-        <v>88</v>
-      </c>
       <c r="D56" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E56" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -3160,15 +3163,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D57">
-        <v>381.3900146484375</v>
+        <v>376.8599853515625</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -3177,10 +3180,10 @@
         <v>76</v>
       </c>
       <c r="G57">
-        <v>16.950665999999998</v>
+        <v>16.719608000000001</v>
       </c>
       <c r="H57">
-        <v>15.535235</v>
+        <v>15.350713000000001</v>
       </c>
       <c r="I57" t="s">
         <v>17</v>
@@ -3195,36 +3198,36 @@
         <v>8.0729203322391978</v>
       </c>
       <c r="M57">
-        <v>22.5</v>
+        <v>22.54</v>
       </c>
       <c r="N57">
         <v>24.55</v>
       </c>
       <c r="O57">
-        <v>28.47876722205304</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+        <v>28.536423323472722</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" t="s">
         <v>90</v>
       </c>
-      <c r="C58" t="s">
-        <v>91</v>
-      </c>
       <c r="D58">
-        <v>148.3500061035156</v>
+        <v>142.50999450683591</v>
       </c>
       <c r="E58" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F58">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="G58">
-        <v>18.474471999999999</v>
+        <v>17.769324999999998</v>
       </c>
       <c r="H58">
-        <v>18.778482</v>
+        <v>18.039239999999999</v>
       </c>
       <c r="I58" t="s">
         <v>17</v>
@@ -3239,24 +3242,24 @@
         <v>18.031248104515921</v>
       </c>
       <c r="M58">
-        <v>8.0299999999999994</v>
+        <v>8.02</v>
       </c>
       <c r="N58">
         <v>7.9</v>
       </c>
       <c r="O58">
-        <v>36.075637474594878</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+        <v>36.232375073884462</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D59">
-        <v>131.7799987792969</v>
+        <v>139.96000671386719</v>
       </c>
       <c r="E59" t="s">
         <v>18</v>
@@ -3265,10 +3268,10 @@
         <v>17</v>
       </c>
       <c r="G59">
-        <v>599</v>
+        <v>636.18179999999995</v>
       </c>
       <c r="H59">
-        <v>280.38297</v>
+        <v>297.78726</v>
       </c>
       <c r="I59" t="s">
         <v>17</v>
@@ -3289,30 +3292,30 @@
         <v>0.47</v>
       </c>
       <c r="O59">
-        <v>72.783241688775817</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+        <v>73.128869039820771</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D60">
-        <v>66.80999755859375</v>
+        <v>67.660003662109375</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F60" t="s">
         <v>17</v>
       </c>
       <c r="G60">
-        <v>10.916665999999999</v>
+        <v>11.055555999999999</v>
       </c>
       <c r="H60">
-        <v>9.5716319999999993</v>
+        <v>9.6934100000000001</v>
       </c>
       <c r="I60" t="s">
         <v>17</v>
@@ -3333,30 +3336,30 @@
         <v>6.98</v>
       </c>
       <c r="O60">
-        <v>40.613994794929283</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+        <v>40.409472648589087</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D61">
-        <v>43.650001525878913</v>
+        <v>42.759998321533203</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F61">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="G61">
-        <v>18.263597000000001</v>
+        <v>17.891211999999999</v>
       </c>
       <c r="H61">
-        <v>16.918606</v>
+        <v>16.573643000000001</v>
       </c>
       <c r="I61" t="s">
         <v>17</v>
@@ -3377,30 +3380,30 @@
         <v>2.58</v>
       </c>
       <c r="O61">
-        <v>41.926996580445383</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+        <v>41.847251822795037</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62">
-        <v>16.879999160766602</v>
+        <v>14.069999694824221</v>
       </c>
       <c r="E62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F62">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="G62">
-        <v>15.486238</v>
+        <v>12.908257000000001</v>
       </c>
       <c r="H62">
-        <v>11.405405</v>
+        <v>9.5067570000000003</v>
       </c>
       <c r="I62" t="s">
         <v>17</v>
@@ -3421,30 +3424,30 @@
         <v>1.48</v>
       </c>
       <c r="O62">
-        <v>26.301098247026331</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+        <v>27.924013917145761</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63">
-        <v>18.079999923706051</v>
+        <v>19.930000305175781</v>
       </c>
       <c r="E63" t="s">
         <v>18</v>
       </c>
       <c r="F63">
-        <v>1659</v>
+        <v>1305</v>
       </c>
       <c r="G63" t="s">
         <v>17</v>
       </c>
       <c r="H63">
-        <v>9.3678760000000008</v>
+        <v>10.326426</v>
       </c>
       <c r="I63" t="s">
         <v>17</v>
@@ -3459,27 +3462,27 @@
         <v>-2.255997845024639</v>
       </c>
       <c r="M63">
-        <v>-5</v>
+        <v>-5.0199999999999996</v>
       </c>
       <c r="N63">
         <v>1.93</v>
       </c>
       <c r="O63">
-        <v>74.536967647107673</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+        <v>74.067519070047666</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -3512,15 +3515,15 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>18</v>
       </c>
       <c r="C65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D65">
-        <v>10.52999973297119</v>
+        <v>10.60000038146973</v>
       </c>
       <c r="E65" t="s">
         <v>18</v>
@@ -3532,7 +3535,7 @@
         <v>17</v>
       </c>
       <c r="H65">
-        <v>3.6435982999999998</v>
+        <v>3.6678199999999999</v>
       </c>
       <c r="I65" t="s">
         <v>17</v>
@@ -3553,7 +3556,95 @@
         <v>2.89</v>
       </c>
       <c r="O65">
-        <v>83.35565568621584</v>
+        <v>83.605752662884157</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" t="s">
+        <v>98</v>
+      </c>
+      <c r="D66">
+        <v>78.349998474121094</v>
+      </c>
+      <c r="E66" t="s">
+        <v>41</v>
+      </c>
+      <c r="F66">
+        <v>286</v>
+      </c>
+      <c r="G66">
+        <v>12.377567000000001</v>
+      </c>
+      <c r="H66">
+        <v>10.897078499999999</v>
+      </c>
+      <c r="I66" t="s">
+        <v>17</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>12163999744</v>
+      </c>
+      <c r="L66">
+        <v>16.9370214423048</v>
+      </c>
+      <c r="M66">
+        <v>6.33</v>
+      </c>
+      <c r="N66">
+        <v>7.19</v>
+      </c>
+      <c r="O66">
+        <v>34.348109558842488</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67" t="s">
+        <v>99</v>
+      </c>
+      <c r="D67">
+        <v>217.77000427246091</v>
+      </c>
+      <c r="E67" t="s">
+        <v>41</v>
+      </c>
+      <c r="F67">
+        <v>505.99999999999989</v>
+      </c>
+      <c r="G67">
+        <v>11.088086000000001</v>
+      </c>
+      <c r="H67">
+        <v>10.530464</v>
+      </c>
+      <c r="I67" t="s">
+        <v>17</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>5767293952</v>
+      </c>
+      <c r="L67">
+        <v>30.76192656777258</v>
+      </c>
+      <c r="M67">
+        <v>19.64</v>
+      </c>
+      <c r="N67">
+        <v>20.68</v>
+      </c>
+      <c r="O67">
+        <v>25.053139405482849</v>
       </c>
     </row>
   </sheetData>

--- a/Stock Selection/tickers_used.xlsx
+++ b/Stock Selection/tickers_used.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/RodWal-Capital-Insights/Stock Selection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_2BB9D44F1E6E680F62355476585DCE3A8747A1ED" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35CA111A-A3C1-4A59-862C-8C7DB03CE62E}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_5D0577719950FC0E62355476585DCE3A8747434D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42F51E4A-5141-42E6-BF1D-D7D63B7DC9FF}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="101">
   <si>
     <t>Chapter</t>
   </si>
@@ -86,6 +86,12 @@
     <t>AGIO</t>
   </si>
   <si>
+    <t>Error: Failed to perform, curl: (6) Could not resolve host: query2.finance.yahoo.com. See https://curl.se/libcurl/c/libcurl-errors.html first for more details.</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -123,9 +129,6 @@
   </si>
   <si>
     <t>GC=F</t>
-  </si>
-  <si>
-    <t>Unknown</t>
   </si>
   <si>
     <t>LEVI</t>
@@ -752,155 +755,155 @@
       <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2">
-        <v>35.5</v>
+      <c r="D2" t="s">
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2">
-        <v>3.0762564999999999</v>
-      </c>
-      <c r="H2">
-        <v>-5.8388156999999996</v>
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>19</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>665985024</v>
-      </c>
-      <c r="L2">
-        <v>1798.258469015796</v>
-      </c>
-      <c r="M2">
-        <v>11.54</v>
-      </c>
-      <c r="N2">
-        <v>-6.08</v>
-      </c>
-      <c r="O2">
-        <v>51.84013469955979</v>
+        <v>19</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" t="s">
+        <v>19</v>
+      </c>
+      <c r="N2" t="s">
+        <v>19</v>
+      </c>
+      <c r="O2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3">
-        <v>199.7799987792969</v>
+        <v>21</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3">
-        <v>114.81609</v>
-      </c>
-      <c r="H3">
-        <v>27.747223000000002</v>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3">
-        <v>14.087</v>
-      </c>
-      <c r="K3">
-        <v>1237799936</v>
-      </c>
-      <c r="L3">
-        <v>13.94751334966173</v>
-      </c>
-      <c r="M3">
-        <v>1.74</v>
-      </c>
-      <c r="N3">
-        <v>7.2</v>
-      </c>
-      <c r="O3">
-        <v>36.182015501162681</v>
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L3" t="s">
+        <v>19</v>
+      </c>
+      <c r="M3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N3" t="s">
+        <v>19</v>
+      </c>
+      <c r="O3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
-      </c>
-      <c r="D4">
-        <v>251.25999450683591</v>
+        <v>22</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4">
-        <v>94</v>
-      </c>
-      <c r="G4">
-        <v>91.700729999999993</v>
-      </c>
-      <c r="H4">
-        <v>40.722850000000001</v>
+        <v>0</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>19</v>
       </c>
       <c r="I4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4">
-        <v>54.54</v>
-      </c>
-      <c r="K4">
-        <v>13240999936</v>
-      </c>
-      <c r="L4">
-        <v>23.211092846353111</v>
-      </c>
-      <c r="M4">
-        <v>2.74</v>
-      </c>
-      <c r="N4">
-        <v>6.17</v>
-      </c>
-      <c r="O4">
-        <v>61.833101755022092</v>
+        <v>19</v>
+      </c>
+      <c r="J4" t="s">
+        <v>19</v>
+      </c>
+      <c r="K4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L4" t="s">
+        <v>19</v>
+      </c>
+      <c r="M4" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" t="s">
+        <v>19</v>
+      </c>
+      <c r="O4" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D5">
-        <v>38.549999237060547</v>
+        <v>38.619998931884773</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5">
-        <v>36.028033999999998</v>
+        <v>36.093456000000003</v>
       </c>
       <c r="H5">
-        <v>12.892977</v>
+        <v>12.916388</v>
       </c>
       <c r="I5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J5">
         <v>14.259</v>
@@ -918,33 +921,33 @@
         <v>2.99</v>
       </c>
       <c r="O5">
-        <v>44.94439518501521</v>
+        <v>44.744106652426638</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D6">
-        <v>31.760000228881839</v>
+        <v>30.420000076293949</v>
       </c>
       <c r="E6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F6">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="G6">
-        <v>16.628273</v>
+        <v>16.010527</v>
       </c>
       <c r="H6">
-        <v>8.3141365</v>
+        <v>7.9633510000000003</v>
       </c>
       <c r="I6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J6">
         <v>18.240998999999999</v>
@@ -956,39 +959,39 @@
         <v>4.8087837924487724</v>
       </c>
       <c r="M6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="N6">
         <v>3.82</v>
       </c>
       <c r="O6">
-        <v>21.602152732406719</v>
+        <v>21.86765100559721</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D7">
-        <v>143.66999816894531</v>
+        <v>151.17999267578119</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G7">
-        <v>12.206455999999999</v>
+        <v>12.833615999999999</v>
       </c>
       <c r="H7">
-        <v>6.8873439999999997</v>
+        <v>7.2473625999999998</v>
       </c>
       <c r="I7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J7">
         <v>43.032002000000013</v>
@@ -1000,83 +1003,83 @@
         <v>29.716643554944859</v>
       </c>
       <c r="M7">
-        <v>11.77</v>
+        <v>11.78</v>
       </c>
       <c r="N7">
         <v>20.86</v>
       </c>
       <c r="O7">
-        <v>62.909307077697058</v>
+        <v>63.062284713438693</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D8">
-        <v>3387.39990234375</v>
+        <v>3340.300048828125</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O8">
-        <v>18.306608171720249</v>
+        <v>18.27796332702945</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>17.610000610351559</v>
+        <v>18.620000839233398</v>
       </c>
       <c r="E9" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F9">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="G9">
-        <v>19.566668</v>
+        <v>20.688890000000001</v>
       </c>
       <c r="H9">
-        <v>12.578571999999999</v>
+        <v>13.300001</v>
       </c>
       <c r="I9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J9">
         <v>14.336</v>
@@ -1094,7 +1097,7 @@
         <v>1.4</v>
       </c>
       <c r="O9">
-        <v>43.774884892404998</v>
+        <v>43.959970189185512</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -1102,25 +1105,25 @@
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10">
-        <v>108</v>
+        <v>107.1999969482422</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
       <c r="F10">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G10">
-        <v>22.689074999999999</v>
+        <v>22.521007999999998</v>
       </c>
       <c r="H10">
-        <v>14.535666000000001</v>
+        <v>14.427994999999999</v>
       </c>
       <c r="I10" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J10">
         <v>47.761001999999998</v>
@@ -1138,33 +1141,33 @@
         <v>7.43</v>
       </c>
       <c r="O10">
-        <v>26.178633288046029</v>
+        <v>26.061675033930541</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D11">
-        <v>145.47999572753909</v>
+        <v>147.8999938964844</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>3</v>
       </c>
       <c r="G11">
-        <v>46.929029999999997</v>
+        <v>47.709679999999999</v>
       </c>
       <c r="H11">
-        <v>35.310679999999998</v>
+        <v>35.898055999999997</v>
       </c>
       <c r="I11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J11">
         <v>59.419995999999998</v>
@@ -1182,33 +1185,33 @@
         <v>4.12</v>
       </c>
       <c r="O11">
-        <v>58.389431514281839</v>
+        <v>57.566996088830372</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12">
-        <v>71.569999694824219</v>
+        <v>71.400001525878906</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="G12">
-        <v>26.805243000000001</v>
+        <v>26.741572999999999</v>
       </c>
       <c r="H12">
-        <v>19.448370000000001</v>
+        <v>19.402173999999999</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J12">
         <v>53.73</v>
@@ -1226,33 +1229,33 @@
         <v>3.68</v>
       </c>
       <c r="O12">
-        <v>28.968142201265241</v>
+        <v>28.942376667943531</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13">
-        <v>21.090000152587891</v>
+        <v>21.690000534057621</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F13">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="G13">
-        <v>12.859756000000001</v>
+        <v>13.22561</v>
       </c>
       <c r="H13">
-        <v>9.2907489999999999</v>
+        <v>9.5550660000000001</v>
       </c>
       <c r="I13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J13">
         <v>4.6609997999999999</v>
@@ -1270,33 +1273,33 @@
         <v>2.27</v>
       </c>
       <c r="O13">
-        <v>25.093466891775378</v>
+        <v>25.36065984558179</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D14">
-        <v>172.8399963378906</v>
+        <v>180.17999267578119</v>
       </c>
       <c r="E14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G14">
-        <v>21.001214999999998</v>
+        <v>21.919706000000001</v>
       </c>
       <c r="H14">
-        <v>17.836946000000001</v>
+        <v>18.594427</v>
       </c>
       <c r="I14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J14">
         <v>31.132999999999999</v>
@@ -1308,39 +1311,39 @@
         <v>24.059240782505299</v>
       </c>
       <c r="M14">
-        <v>8.23</v>
+        <v>8.2200000000000006</v>
       </c>
       <c r="N14">
         <v>9.69</v>
       </c>
       <c r="O14">
-        <v>48.643487855208093</v>
+        <v>48.818593344366519</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D15">
-        <v>196.58000183105469</v>
+        <v>200.30000305175781</v>
       </c>
       <c r="E15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F15">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G15">
-        <v>30.572319</v>
+        <v>31.150856000000001</v>
       </c>
       <c r="H15">
-        <v>23.655836000000001</v>
+        <v>24.103489</v>
       </c>
       <c r="I15" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J15">
         <v>34.685000000000002</v>
@@ -1358,33 +1361,33 @@
         <v>8.31</v>
       </c>
       <c r="O15">
-        <v>32.254655201655787</v>
+        <v>32.318861603294472</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16">
-        <v>129.07000732421881</v>
+        <v>131.05000305175781</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F16">
         <v>441</v>
       </c>
       <c r="G16">
-        <v>18.980882999999999</v>
+        <v>19.272058000000001</v>
       </c>
       <c r="H16">
-        <v>14.955968</v>
+        <v>15.1854</v>
       </c>
       <c r="I16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J16">
         <v>18.905999999999999</v>
@@ -1402,33 +1405,33 @@
         <v>8.6300000000000008</v>
       </c>
       <c r="O16">
-        <v>19.511122017696149</v>
+        <v>19.561471876145148</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17">
+        <v>351.6300048828125</v>
+      </c>
+      <c r="E17" t="s">
         <v>42</v>
-      </c>
-      <c r="D17">
-        <v>340.3800048828125</v>
-      </c>
-      <c r="E17" t="s">
-        <v>41</v>
       </c>
       <c r="F17">
         <v>69</v>
       </c>
       <c r="G17">
-        <v>34.243459999999999</v>
+        <v>35.410876999999999</v>
       </c>
       <c r="H17">
-        <v>26.886257000000001</v>
+        <v>27.774881000000001</v>
       </c>
       <c r="I17" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J17">
         <v>69.707999999999998</v>
@@ -1440,39 +1443,39 @@
         <v>52.210202623591513</v>
       </c>
       <c r="M17">
-        <v>9.94</v>
+        <v>9.93</v>
       </c>
       <c r="N17">
         <v>12.66</v>
       </c>
       <c r="O17">
-        <v>23.14206432951104</v>
+        <v>23.261174566994089</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D18">
-        <v>153.6300048828125</v>
+        <v>155.71000671386719</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F18">
         <v>232</v>
       </c>
       <c r="G18">
-        <v>15.676531000000001</v>
+        <v>15.888776</v>
       </c>
       <c r="H18">
-        <v>12.561734</v>
+        <v>12.731807999999999</v>
       </c>
       <c r="I18" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J18">
         <v>31.573</v>
@@ -1490,33 +1493,33 @@
         <v>12.23</v>
       </c>
       <c r="O18">
-        <v>43.139882091532428</v>
+        <v>42.845680284839453</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D19">
-        <v>138.36000061035159</v>
+        <v>142.69999694824219</v>
       </c>
       <c r="E19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F19">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G19">
-        <v>27.561751999999998</v>
+        <v>28.426293999999999</v>
       </c>
       <c r="H19">
-        <v>22.756578000000001</v>
+        <v>23.470393999999999</v>
       </c>
       <c r="I19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J19">
         <v>35.5</v>
@@ -1534,33 +1537,33 @@
         <v>6.08</v>
       </c>
       <c r="O19">
-        <v>21.987103006840659</v>
+        <v>22.03281874560183</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D20">
-        <v>136.8999938964844</v>
+        <v>137.5</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F20">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G20">
-        <v>14.456177</v>
+        <v>14.50422</v>
       </c>
       <c r="H20">
-        <v>12.322232</v>
+        <v>12.376238000000001</v>
       </c>
       <c r="I20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J20">
         <v>17.510999999999999</v>
@@ -1572,39 +1575,39 @@
         <v>8.5314496054901205</v>
       </c>
       <c r="M20">
-        <v>9.4700000000000006</v>
+        <v>9.48</v>
       </c>
       <c r="N20">
         <v>11.11</v>
       </c>
       <c r="O20">
-        <v>25.75591338359169</v>
+        <v>25.77856046696002</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D21">
-        <v>452.54998779296881</v>
+        <v>453.54998779296881</v>
       </c>
       <c r="E21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F21">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G21">
-        <v>18.0227</v>
+        <v>18.069721000000001</v>
       </c>
       <c r="H21">
-        <v>15.556891</v>
+        <v>15.591267999999999</v>
       </c>
       <c r="I21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J21">
         <v>26.488</v>
@@ -1616,39 +1619,39 @@
         <v>14.81997561254024</v>
       </c>
       <c r="M21">
-        <v>25.11</v>
+        <v>25.1</v>
       </c>
       <c r="N21">
         <v>29.09</v>
       </c>
       <c r="O21">
-        <v>31.79772441233456</v>
+        <v>31.758493277418651</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D22">
-        <v>480.239990234375</v>
+        <v>490.1099853515625</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F22">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G22">
-        <v>37.170276999999999</v>
+        <v>37.904870000000003</v>
       </c>
       <c r="H22">
-        <v>32.123077000000002</v>
+        <v>32.783276000000001</v>
       </c>
       <c r="I22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J22">
         <v>55.247</v>
@@ -1660,39 +1663,39 @@
         <v>35.789415272465227</v>
       </c>
       <c r="M22">
-        <v>12.92</v>
+        <v>12.93</v>
       </c>
       <c r="N22">
         <v>14.95</v>
       </c>
       <c r="O22">
-        <v>25.534970140930021</v>
+        <v>25.587278652876911</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D23">
-        <v>538.72998046875</v>
+        <v>557.530029296875</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F23">
         <v>56.000000000000007</v>
       </c>
       <c r="G23">
-        <v>37.726190000000003</v>
+        <v>39.097476999999998</v>
       </c>
       <c r="H23">
-        <v>32.889499999999998</v>
+        <v>34.037242999999997</v>
       </c>
       <c r="I23" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J23">
         <v>61.845999999999997</v>
@@ -1704,39 +1707,39 @@
         <v>45.213112751383562</v>
       </c>
       <c r="M23">
-        <v>14.28</v>
+        <v>14.26</v>
       </c>
       <c r="N23">
         <v>16.38</v>
       </c>
       <c r="O23">
-        <v>22.524989101788279</v>
+        <v>22.77213014443624</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D24">
-        <v>101.1999969482422</v>
+        <v>103.2799987792969</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F24">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="G24">
-        <v>19.53668</v>
+        <v>19.938224999999999</v>
       </c>
       <c r="H24">
-        <v>17.181664000000001</v>
+        <v>17.534804999999999</v>
       </c>
       <c r="I24" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J24">
         <v>39.542999999999999</v>
@@ -1754,33 +1757,33 @@
         <v>5.89</v>
       </c>
       <c r="O24">
-        <v>19.532099410079969</v>
+        <v>19.470508561942331</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25">
-        <v>95.089996337890625</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F25">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G25">
-        <v>40.636752999999999</v>
+        <v>41.880344000000001</v>
       </c>
       <c r="H25">
-        <v>34.959556999999997</v>
+        <v>36.029409999999999</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J25">
         <v>6.2409999999999997</v>
@@ -1798,33 +1801,33 @@
         <v>2.72</v>
       </c>
       <c r="O25">
-        <v>24.146619281851219</v>
+        <v>24.073290936790361</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D26">
-        <v>761.6400146484375</v>
+        <v>813.3599853515625</v>
       </c>
       <c r="E26" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F26">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G26">
-        <v>29.763190000000002</v>
+        <v>31.896470000000001</v>
       </c>
       <c r="H26">
-        <v>28.525842999999998</v>
+        <v>30.46292</v>
       </c>
       <c r="I26" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J26">
         <v>36.578000000000003</v>
@@ -1836,39 +1839,39 @@
         <v>28.33459111814113</v>
       </c>
       <c r="M26">
-        <v>25.59</v>
+        <v>25.5</v>
       </c>
       <c r="N26">
         <v>26.7</v>
       </c>
       <c r="O26">
-        <v>47.604728667504432</v>
+        <v>47.733915207660623</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D27">
-        <v>35.279998779296882</v>
+        <v>34.349998474121087</v>
       </c>
       <c r="E27" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G27">
-        <v>8.2237760000000009</v>
+        <v>8.0069920000000003</v>
       </c>
       <c r="H27">
-        <v>7.5063829999999996</v>
+        <v>7.3085110000000002</v>
       </c>
       <c r="I27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J27">
         <v>22.016999999999999</v>
@@ -1886,33 +1889,33 @@
         <v>4.7</v>
       </c>
       <c r="O27">
-        <v>47.857041571377373</v>
+        <v>47.892961955687731</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D28">
-        <v>114.5800018310547</v>
+        <v>116.9499969482422</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F28">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="G28">
-        <v>19.001657000000002</v>
+        <v>19.426909999999999</v>
       </c>
       <c r="H28">
-        <v>18.072555999999999</v>
+        <v>18.446370999999999</v>
       </c>
       <c r="I28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28">
         <v>48.826998000000003</v>
@@ -1924,39 +1927,39 @@
         <v>15.220239866756501</v>
       </c>
       <c r="M28">
-        <v>6.03</v>
+        <v>6.02</v>
       </c>
       <c r="N28">
         <v>6.34</v>
       </c>
       <c r="O28">
-        <v>18.288821806463691</v>
+        <v>18.2199154816049</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C29" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D29">
-        <v>127.9599990844727</v>
+        <v>129.94999694824219</v>
       </c>
       <c r="E29" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F29">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="G29">
-        <v>17.433243000000001</v>
+        <v>17.704360000000001</v>
       </c>
       <c r="H29">
-        <v>16.770641000000001</v>
+        <v>17.031454</v>
       </c>
       <c r="I29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J29">
         <v>19.545000999999999</v>
@@ -1974,33 +1977,33 @@
         <v>7.63</v>
       </c>
       <c r="O29">
-        <v>19.42880627327235</v>
+        <v>19.457865499254961</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C30" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D30">
-        <v>20.780000686645511</v>
+        <v>21.360000610351559</v>
       </c>
       <c r="E30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F30">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="G30">
-        <v>9.1140360000000005</v>
+        <v>9.4096919999999997</v>
       </c>
       <c r="H30">
-        <v>9.4885845</v>
+        <v>9.753425</v>
       </c>
       <c r="I30" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J30">
         <v>0</v>
@@ -2012,39 +2015,39 @@
         <v>25.984840469640911</v>
       </c>
       <c r="M30">
-        <v>2.2799999999999998</v>
+        <v>2.27</v>
       </c>
       <c r="N30">
         <v>2.19</v>
       </c>
       <c r="O30">
-        <v>27.232077610448869</v>
+        <v>27.372221883532301</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D31">
-        <v>173.32000732421881</v>
+        <v>166.77000427246091</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F31">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G31">
-        <v>19.34375</v>
+        <v>18.633520000000001</v>
       </c>
       <c r="H31">
-        <v>19.34375</v>
+        <v>18.612724</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J31">
         <v>37.726003000000013</v>
@@ -2056,39 +2059,39 @@
         <v>30.856819860861741</v>
       </c>
       <c r="M31">
-        <v>8.9600000000000009</v>
+        <v>8.9499999999999993</v>
       </c>
       <c r="N31">
         <v>8.9600000000000009</v>
       </c>
       <c r="O31">
-        <v>31.7764028506854</v>
+        <v>31.86715633790724</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D32">
-        <v>20.309999465942379</v>
+        <v>18.180000305175781</v>
       </c>
       <c r="E32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F32">
-        <v>492</v>
+        <v>544</v>
       </c>
       <c r="G32">
-        <v>7.2795696000000003</v>
+        <v>6.5161290000000003</v>
       </c>
       <c r="H32">
-        <v>7.3854540000000002</v>
+        <v>6.6109090000000004</v>
       </c>
       <c r="I32" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J32">
         <v>58.8</v>
@@ -2106,33 +2109,33 @@
         <v>2.75</v>
       </c>
       <c r="O32">
-        <v>52.05274095647362</v>
+        <v>52.467748135245209</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D33">
-        <v>213.5</v>
+        <v>220.0899963378906</v>
       </c>
       <c r="E33" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F33">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G33">
-        <v>25</v>
+        <v>26.107945999999998</v>
       </c>
       <c r="H33">
-        <v>26.423266999999999</v>
+        <v>27.238861</v>
       </c>
       <c r="I33" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J33">
         <v>68.481003999999999</v>
@@ -2144,39 +2147,39 @@
         <v>41.686769633025442</v>
       </c>
       <c r="M33">
-        <v>8.5399999999999991</v>
+        <v>8.43</v>
       </c>
       <c r="N33">
         <v>8.08</v>
       </c>
       <c r="O33">
-        <v>45.846279954867072</v>
+        <v>45.875842776983824</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D34">
-        <v>42.369998931884773</v>
+        <v>43.099998474121087</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F34">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="G34">
-        <v>15.750928999999999</v>
+        <v>16.022304999999999</v>
       </c>
       <c r="H34">
-        <v>16.110265999999999</v>
+        <v>16.387830000000001</v>
       </c>
       <c r="I34" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J34">
         <v>32.266998000000001</v>
@@ -2194,33 +2197,33 @@
         <v>2.63</v>
       </c>
       <c r="O34">
-        <v>19.252426111837181</v>
+        <v>19.176071492506001</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C35" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D35">
-        <v>43.209999084472663</v>
+        <v>44.970001220703118</v>
       </c>
       <c r="E35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F35">
-        <v>3529</v>
+        <v>3578</v>
       </c>
       <c r="G35">
-        <v>6.7621283999999999</v>
+        <v>6.9720936</v>
       </c>
       <c r="H35">
-        <v>7.3237285999999999</v>
+        <v>7.6220340000000002</v>
       </c>
       <c r="I35" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J35">
         <v>0</v>
@@ -2232,39 +2235,39 @@
         <v>28.104146008031432</v>
       </c>
       <c r="M35">
-        <v>6.39</v>
+        <v>6.45</v>
       </c>
       <c r="N35">
         <v>5.9</v>
       </c>
       <c r="O35">
-        <v>31.614182891395409</v>
+        <v>31.858504561556149</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C36" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D36">
-        <v>59.490001678466797</v>
+        <v>59.909999847412109</v>
       </c>
       <c r="E36" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F36">
-        <v>686</v>
+        <v>674</v>
       </c>
       <c r="G36">
-        <v>9.9815439999999995</v>
+        <v>10.052013000000001</v>
       </c>
       <c r="H36">
-        <v>11.119626999999999</v>
+        <v>11.198131</v>
       </c>
       <c r="I36" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J36">
         <v>61.162996</v>
@@ -2282,33 +2285,33 @@
         <v>5.35</v>
       </c>
       <c r="O36">
-        <v>19.485964723138071</v>
+        <v>19.49064194111504</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D37">
-        <v>12.840000152587891</v>
+        <v>13.114999771118161</v>
       </c>
       <c r="E37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F37">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="G37">
-        <v>7.2542377</v>
+        <v>7.4096045000000004</v>
       </c>
       <c r="H37">
-        <v>13.6595745</v>
+        <v>13.952127000000001</v>
       </c>
       <c r="I37" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -2326,33 +2329,33 @@
         <v>0.94</v>
       </c>
       <c r="O37">
-        <v>30.142040184122731</v>
+        <v>30.117069530458139</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D38">
-        <v>17.659999847412109</v>
+        <v>18.260000228881839</v>
       </c>
       <c r="E38" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F38">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G38">
-        <v>8.6995079999999998</v>
+        <v>9.0396040000000006</v>
       </c>
       <c r="H38">
-        <v>16.819047999999999</v>
+        <v>17.390478000000002</v>
       </c>
       <c r="I38" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J38">
         <v>0</v>
@@ -2364,39 +2367,39 @@
         <v>22.63225720298977</v>
       </c>
       <c r="M38">
-        <v>2.0299999999999998</v>
+        <v>2.02</v>
       </c>
       <c r="N38">
         <v>1.05</v>
       </c>
       <c r="O38">
-        <v>35.93340686435748</v>
+        <v>35.94639633092347</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D39">
-        <v>14.939999580383301</v>
+        <v>15.170000076293951</v>
       </c>
       <c r="E39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F39">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="G39">
-        <v>11.952</v>
+        <v>12.2338705</v>
       </c>
       <c r="H39">
-        <v>36.439022000000001</v>
+        <v>37</v>
       </c>
       <c r="I39" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J39">
         <v>0</v>
@@ -2408,125 +2411,125 @@
         <v>22.5677633341305</v>
       </c>
       <c r="M39">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="N39">
         <v>0.41</v>
       </c>
       <c r="O39">
-        <v>36.395177989580901</v>
+        <v>36.396292051920028</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O40" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D41">
-        <v>22.170000076293949</v>
+        <v>17.479999542236332</v>
       </c>
       <c r="E41" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N41" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O41">
         <f>D41</f>
-        <v>22.170000076293949</v>
+        <v>17.479999542236332</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D42">
-        <v>2.9900000095367432</v>
+        <v>2.9200000762939449</v>
       </c>
       <c r="E42" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F42" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G42" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H42">
-        <v>-0.54166669999999995</v>
+        <v>-0.5289855</v>
       </c>
       <c r="I42" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J42">
         <v>-80.991</v>
@@ -2544,253 +2547,253 @@
         <v>-5.52</v>
       </c>
       <c r="O42">
-        <v>167.24498492839689</v>
+        <v>167.69436274647649</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D43">
-        <v>19.029119491577148</v>
+        <v>18.982999801635739</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F43" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G43" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H43" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I43" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J43" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K43" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L43" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M43" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N43" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O43">
-        <v>13.649438496972239</v>
+        <v>13.61405019749199</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C44" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D44">
-        <v>6.1149997711181641</v>
+        <v>6.1319999694824219</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O44">
-        <v>2.6744961612298939</v>
+        <v>2.6712918445884042</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C45" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D45">
-        <v>6.2610001564025879</v>
+        <v>6.2690000534057617</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N45" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O45">
-        <v>2.7157582188855081</v>
+        <v>2.7153145304813111</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D46">
-        <v>71.949996948242188</v>
+        <v>73.264999389648438</v>
       </c>
       <c r="E46" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F46">
         <v>310</v>
       </c>
       <c r="G46">
-        <v>14.809839</v>
+        <v>15.080513</v>
       </c>
       <c r="H46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O46">
-        <v>14.034326054518139</v>
+        <v>13.904027157502201</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D47">
-        <v>48.150001525878913</v>
+        <v>48.990001678466797</v>
       </c>
       <c r="E47" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F47">
         <v>302</v>
       </c>
       <c r="G47">
-        <v>15.493598</v>
+        <v>15.763890999999999</v>
       </c>
       <c r="H47" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I47" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J47" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K47" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L47" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M47" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N47" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O47">
-        <v>18.59298580482179</v>
+        <v>18.748833165197212</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C48" t="s">
+        <v>79</v>
+      </c>
+      <c r="D48">
+        <v>33.950000762939453</v>
+      </c>
+      <c r="E48" t="s">
         <v>78</v>
-      </c>
-      <c r="D48">
-        <v>33.110000610351563</v>
-      </c>
-      <c r="E48" t="s">
-        <v>77</v>
       </c>
       <c r="F48">
         <v>613</v>
       </c>
       <c r="G48">
-        <v>15.691943999999999</v>
+        <v>16.090047999999999</v>
       </c>
       <c r="H48">
-        <v>8.319096</v>
+        <v>8.530151</v>
       </c>
       <c r="I48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J48">
         <v>29.632000000000001</v>
@@ -2808,359 +2811,359 @@
         <v>3.98</v>
       </c>
       <c r="O48">
-        <v>43.515408656187979</v>
+        <v>43.799609558577082</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D49">
-        <v>597.44000244140625</v>
+        <v>606.780029296875</v>
       </c>
       <c r="E49" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F49">
         <v>121</v>
       </c>
       <c r="G49">
-        <v>25.825686000000001</v>
+        <v>26.229430000000001</v>
       </c>
       <c r="H49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N49" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O49">
-        <v>20.538686659962941</v>
+        <v>20.582577824263218</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D50">
-        <v>48.374000549316413</v>
+        <v>48.33599853515625</v>
       </c>
       <c r="E50" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N50" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O50">
-        <v>48.548662562918622</v>
+        <v>48.423981708974331</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D51">
-        <v>14.990200042724609</v>
+        <v>15.20699977874756</v>
       </c>
       <c r="E51" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O51">
-        <v>25.44489083695931</v>
+        <v>25.500153581710549</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C52" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D52">
-        <v>145.48699951171881</v>
+        <v>144.92500305175781</v>
       </c>
       <c r="E52" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N52" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O52">
-        <v>11.419883637983061</v>
+        <v>11.43144535410117</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C53" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E53" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D54">
-        <v>20</v>
+        <v>20.545000076293949</v>
       </c>
       <c r="E54" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>30.506762999999999</v>
+        <v>31.338073999999999</v>
       </c>
       <c r="H54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O54">
-        <v>26.06381059411537</v>
+        <v>26.035363660396289</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C55" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D55">
-        <v>72.830001831054688</v>
+        <v>73.279998779296875</v>
       </c>
       <c r="E55" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F55">
         <v>375</v>
       </c>
       <c r="G55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O55">
-        <v>5.2444131348715466</v>
+        <v>5.2571621197749359</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C56" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D56" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E56" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O56" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
@@ -3168,10 +3171,10 @@
         <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D57">
-        <v>376.8599853515625</v>
+        <v>379.01998901367188</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
@@ -3180,13 +3183,13 @@
         <v>76</v>
       </c>
       <c r="G57">
-        <v>16.719608000000001</v>
+        <v>16.822903</v>
       </c>
       <c r="H57">
-        <v>15.350713000000001</v>
+        <v>15.438696999999999</v>
       </c>
       <c r="I57" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J57">
         <v>19.863</v>
@@ -3198,39 +3201,39 @@
         <v>8.0729203322391978</v>
       </c>
       <c r="M57">
-        <v>22.54</v>
+        <v>22.53</v>
       </c>
       <c r="N57">
         <v>24.55</v>
       </c>
       <c r="O57">
-        <v>28.536423323472722</v>
+        <v>28.52793693975595</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C58" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58">
+        <v>149.8699951171875</v>
+      </c>
+      <c r="E58" t="s">
         <v>90</v>
       </c>
-      <c r="D58">
-        <v>142.50999450683591</v>
-      </c>
-      <c r="E58" t="s">
-        <v>89</v>
-      </c>
       <c r="F58">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="G58">
-        <v>17.769324999999998</v>
+        <v>18.663761000000001</v>
       </c>
       <c r="H58">
-        <v>18.039239999999999</v>
+        <v>18.970884000000002</v>
       </c>
       <c r="I58" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J58">
         <v>21.734999999999999</v>
@@ -3242,39 +3245,39 @@
         <v>18.031248104515921</v>
       </c>
       <c r="M58">
-        <v>8.02</v>
+        <v>8.0299999999999994</v>
       </c>
       <c r="N58">
         <v>7.9</v>
       </c>
       <c r="O58">
-        <v>36.232375073884462</v>
+        <v>36.320386406707762</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C59" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D59">
-        <v>139.96000671386719</v>
+        <v>143.22999572753909</v>
       </c>
       <c r="E59" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F59" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G59">
-        <v>636.18179999999995</v>
+        <v>651.04539999999997</v>
       </c>
       <c r="H59">
-        <v>297.78726</v>
+        <v>304.74466000000001</v>
       </c>
       <c r="I59" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J59">
         <v>13.976000000000001</v>
@@ -3292,33 +3295,33 @@
         <v>0.47</v>
       </c>
       <c r="O59">
-        <v>73.128869039820771</v>
+        <v>72.803425355094788</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C60" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D60">
-        <v>67.660003662109375</v>
+        <v>68.449996948242188</v>
       </c>
       <c r="E60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F60" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G60">
-        <v>11.055555999999999</v>
+        <v>11.18464</v>
       </c>
       <c r="H60">
-        <v>9.6934100000000001</v>
+        <v>9.8065899999999999</v>
       </c>
       <c r="I60" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J60">
         <v>15.811999999999999</v>
@@ -3336,33 +3339,33 @@
         <v>6.98</v>
       </c>
       <c r="O60">
-        <v>40.409472648589087</v>
+        <v>40.265404819872387</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D61">
-        <v>42.759998321533203</v>
+        <v>44.400001525878913</v>
       </c>
       <c r="E61" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F61">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="G61">
-        <v>17.891211999999999</v>
+        <v>18.577406</v>
       </c>
       <c r="H61">
-        <v>16.573643000000001</v>
+        <v>17.209302999999998</v>
       </c>
       <c r="I61" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J61">
         <v>15.000999999999999</v>
@@ -3380,33 +3383,33 @@
         <v>2.58</v>
       </c>
       <c r="O61">
-        <v>41.847251822795037</v>
+        <v>41.88882741313499</v>
       </c>
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C62" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D62">
-        <v>14.069999694824221</v>
+        <v>14.159999847412109</v>
       </c>
       <c r="E62" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F62">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G62">
-        <v>12.908257000000001</v>
+        <v>12.990824999999999</v>
       </c>
       <c r="H62">
-        <v>9.5067570000000003</v>
+        <v>9.5675670000000004</v>
       </c>
       <c r="I62" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J62">
         <v>38.176997999999998</v>
@@ -3424,33 +3427,33 @@
         <v>1.48</v>
       </c>
       <c r="O62">
-        <v>27.924013917145761</v>
+        <v>28.060995978571199</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C63" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D63">
-        <v>19.930000305175781</v>
+        <v>20.440000534057621</v>
       </c>
       <c r="E63" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F63">
-        <v>1305</v>
+        <v>1288</v>
       </c>
       <c r="G63" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H63">
-        <v>10.326426</v>
+        <v>10.590674</v>
       </c>
       <c r="I63" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J63">
         <v>3.5609999999999999</v>
@@ -3462,83 +3465,83 @@
         <v>-2.255997845024639</v>
       </c>
       <c r="M63">
-        <v>-5.0199999999999996</v>
+        <v>-5.01</v>
       </c>
       <c r="N63">
         <v>1.93</v>
       </c>
       <c r="O63">
-        <v>74.067519070047666</v>
+        <v>73.285134463209005</v>
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C64" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D64" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E64" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H64" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I64" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J64" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K64" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L64" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M64" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N64" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="O64" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C65" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D65">
-        <v>10.60000038146973</v>
+        <v>10.60999965667725</v>
       </c>
       <c r="E65" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F65" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G65" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H65">
-        <v>3.6678199999999999</v>
+        <v>3.6712799999999999</v>
       </c>
       <c r="I65" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J65">
         <v>8.8730000000000011</v>
@@ -3556,33 +3559,33 @@
         <v>2.89</v>
       </c>
       <c r="O65">
-        <v>83.605752662884157</v>
+        <v>83.804365951701783</v>
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C66" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D66">
-        <v>78.349998474121094</v>
+        <v>81.139999389648438</v>
       </c>
       <c r="E66" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F66">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="G66">
-        <v>12.377567000000001</v>
+        <v>12.818325</v>
       </c>
       <c r="H66">
-        <v>10.897078499999999</v>
+        <v>11.285118000000001</v>
       </c>
       <c r="I66" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J66">
         <v>0</v>
@@ -3600,33 +3603,33 @@
         <v>7.19</v>
       </c>
       <c r="O66">
-        <v>34.348109558842488</v>
+        <v>34.341302543328503</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C67" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D67">
-        <v>217.77000427246091</v>
+        <v>217.78999328613281</v>
       </c>
       <c r="E67" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F67">
-        <v>505.99999999999989</v>
+        <v>509</v>
       </c>
       <c r="G67">
-        <v>11.088086000000001</v>
+        <v>10.9994955</v>
       </c>
       <c r="H67">
-        <v>10.530464</v>
+        <v>10.531431</v>
       </c>
       <c r="I67" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -3638,13 +3641,13 @@
         <v>30.76192656777258</v>
       </c>
       <c r="M67">
-        <v>19.64</v>
+        <v>19.8</v>
       </c>
       <c r="N67">
         <v>20.68</v>
       </c>
       <c r="O67">
-        <v>25.053139405482849</v>
+        <v>24.990260617528389</v>
       </c>
     </row>
   </sheetData>

--- a/Stock Selection/tickers_used.xlsx
+++ b/Stock Selection/tickers_used.xlsx
@@ -411,6 +411,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/Stock Selection/tickers_used.xlsx
+++ b/Stock Selection/tickers_used.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rodwals-my.sharepoint.com/personal/samuel_rodwal_com/Documents/Professional_WorkTools/Github/RodWal-Capital-Insights/Stock Selection/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_5D0577719950FC0E62355476585DCE3A8747434D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{42F51E4A-5141-42E6-BF1D-D7D63B7DC9FF}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_22B9BC1EDE523A0F62355476585DCE3A87472C50" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29A93EDA-C283-4A11-98FD-91ECC3D9E163}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$69</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="102">
   <si>
     <t>Chapter</t>
   </si>
@@ -86,51 +89,48 @@
     <t>AGIO</t>
   </si>
   <si>
-    <t>Error: Failed to perform, curl: (6) Could not resolve host: query2.finance.yahoo.com. See https://curl.se/libcurl/c/libcurl-errors.html first for more details.</t>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Technology</t>
+  </si>
+  <si>
+    <t>PANW</t>
+  </si>
+  <si>
+    <t>AVGO</t>
+  </si>
+  <si>
+    <t>Consumer Def &amp; Cyclical</t>
+  </si>
+  <si>
+    <t>DAR</t>
+  </si>
+  <si>
+    <t>Consumer Defensive</t>
+  </si>
+  <si>
+    <t>Energy &amp; Utilities</t>
+  </si>
+  <si>
+    <t>SHELL.AS</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>FSLR</t>
+  </si>
+  <si>
+    <t>CFDs</t>
+  </si>
+  <si>
+    <t>GC=F</t>
   </si>
   <si>
     <t>Unknown</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Technology</t>
-  </si>
-  <si>
-    <t>PANW</t>
-  </si>
-  <si>
-    <t>AVGO</t>
-  </si>
-  <si>
-    <t>Consumer Def &amp; Cyclical</t>
-  </si>
-  <si>
-    <t>DAR</t>
-  </si>
-  <si>
-    <t>Consumer Defensive</t>
-  </si>
-  <si>
-    <t>Energy &amp; Utilities</t>
-  </si>
-  <si>
-    <t>SHELL.AS</t>
-  </si>
-  <si>
-    <t>Energy</t>
-  </si>
-  <si>
-    <t>FSLR</t>
-  </si>
-  <si>
-    <t>CFDs</t>
-  </si>
-  <si>
-    <t>GC=F</t>
-  </si>
-  <si>
     <t>LEVI</t>
   </si>
   <si>
@@ -336,6 +336,12 @@
   </si>
   <si>
     <t>BAP</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>GIS</t>
   </si>
 </sst>
 </file>
@@ -702,8 +708,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O67"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -752,426 +766,426 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
-        <v>17</v>
+      <c r="D2">
+        <v>37.009998321533203</v>
       </c>
       <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2">
+        <v>3.2781221999999999</v>
+      </c>
+      <c r="H2">
+        <v>-6.0871709999999997</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>650083008</v>
+      </c>
+      <c r="L2">
+        <v>1590.4171449541279</v>
+      </c>
+      <c r="M2">
+        <v>11.29</v>
+      </c>
+      <c r="N2">
+        <v>-6.08</v>
+      </c>
+      <c r="O2">
+        <v>52.675672722949841</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" t="s">
-        <v>19</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" t="s">
-        <v>19</v>
-      </c>
-      <c r="N2" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
+      <c r="D3">
+        <v>177.0899963378906</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>19</v>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3">
+        <v>101.775856</v>
+      </c>
+      <c r="H3">
+        <v>24.595832999999999</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" t="s">
-        <v>19</v>
-      </c>
-      <c r="M3" t="s">
-        <v>19</v>
-      </c>
-      <c r="N3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="J3">
+        <v>14.087</v>
+      </c>
+      <c r="K3">
+        <v>1237799936</v>
+      </c>
+      <c r="L3">
+        <v>13.94751334966173</v>
+      </c>
+      <c r="M3">
+        <v>1.74</v>
+      </c>
+      <c r="N3">
+        <v>7.2</v>
+      </c>
+      <c r="O3">
+        <v>36.934510992821707</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
+      <c r="D4">
+        <v>306.33999633789063</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
       </c>
       <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s">
-        <v>19</v>
+        <v>77</v>
+      </c>
+      <c r="G4">
+        <v>112.212456</v>
+      </c>
+      <c r="H4">
+        <v>49.649918</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
-      </c>
-      <c r="K4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="M4" t="s">
-        <v>19</v>
-      </c>
-      <c r="N4" t="s">
-        <v>19</v>
-      </c>
-      <c r="O4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="J4">
+        <v>54.54</v>
+      </c>
+      <c r="K4">
+        <v>13240999936</v>
+      </c>
+      <c r="L4">
+        <v>23.211092846353111</v>
+      </c>
+      <c r="M4">
+        <v>2.73</v>
+      </c>
+      <c r="N4">
+        <v>6.17</v>
+      </c>
+      <c r="O4">
+        <v>57.828225738169387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5">
+        <v>31.180000305175781</v>
+      </c>
+      <c r="E5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5">
-        <v>38.619998931884773</v>
-      </c>
-      <c r="E5" t="s">
-        <v>25</v>
-      </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>36.093456000000003</v>
+        <v>47.969234</v>
       </c>
       <c r="H5">
-        <v>12.916388</v>
+        <v>10.428094</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J5">
-        <v>14.259</v>
+        <v>14.28</v>
       </c>
       <c r="K5">
-        <v>171563008</v>
+        <v>105358000</v>
       </c>
       <c r="L5">
-        <v>3.0228864450042048</v>
+        <v>1.847836152611434</v>
       </c>
       <c r="M5">
-        <v>1.07</v>
+        <v>0.65</v>
       </c>
       <c r="N5">
         <v>2.99</v>
       </c>
       <c r="O5">
-        <v>44.744106652426638</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+        <v>42.676039406184621</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6">
+        <v>30.67499923706055</v>
+      </c>
+      <c r="E6" t="s">
         <v>26</v>
       </c>
-      <c r="C6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6">
-        <v>30.420000076293949</v>
-      </c>
-      <c r="E6" t="s">
-        <v>28</v>
-      </c>
       <c r="F6">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="G6">
-        <v>16.010527</v>
+        <v>15.9765625</v>
       </c>
       <c r="H6">
-        <v>7.9633510000000003</v>
+        <v>8.0301050000000007</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J6">
-        <v>18.240998999999999</v>
+        <v>17.751999999999999</v>
       </c>
       <c r="K6">
-        <v>13516000256</v>
+        <v>13601000448</v>
       </c>
       <c r="L6">
-        <v>4.8087837924487724</v>
+        <v>5.0001655650679302</v>
       </c>
       <c r="M6">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="N6">
         <v>3.82</v>
       </c>
       <c r="O6">
-        <v>21.86765100559721</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+        <v>21.62320255684196</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7">
-        <v>151.17999267578119</v>
+        <v>199.94999694824219</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>12.833615999999999</v>
+        <v>17.089742999999999</v>
       </c>
       <c r="H7">
-        <v>7.2473625999999998</v>
+        <v>9.5853300000000008</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J7">
-        <v>43.032002000000013</v>
+        <v>42.540002000000001</v>
       </c>
       <c r="K7">
-        <v>1264962944</v>
+        <v>1257474944</v>
       </c>
       <c r="L7">
-        <v>29.716643554944859</v>
+        <v>28.951150941116499</v>
       </c>
       <c r="M7">
-        <v>11.78</v>
+        <v>11.7</v>
       </c>
       <c r="N7">
         <v>20.86</v>
       </c>
       <c r="O7">
-        <v>63.062284713438693</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+        <v>63.515869616212107</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8">
+        <v>3336</v>
+      </c>
+      <c r="E8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" t="s">
+      <c r="F8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>17</v>
+      </c>
+      <c r="M8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8">
+        <v>18.071577557846432</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
         <v>31</v>
       </c>
-      <c r="D8">
-        <v>3340.300048828125</v>
-      </c>
-      <c r="E8" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G8" t="s">
-        <v>19</v>
-      </c>
-      <c r="H8" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" t="s">
-        <v>19</v>
-      </c>
-      <c r="J8" t="s">
-        <v>19</v>
-      </c>
-      <c r="K8" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" t="s">
-        <v>19</v>
-      </c>
-      <c r="M8" t="s">
-        <v>19</v>
-      </c>
-      <c r="N8" t="s">
-        <v>19</v>
-      </c>
-      <c r="O8">
-        <v>18.27796332702945</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="D9">
+        <v>21.139999389648441</v>
+      </c>
+      <c r="E9" t="s">
         <v>32</v>
       </c>
-      <c r="D9">
-        <v>18.620000839233398</v>
-      </c>
-      <c r="E9" t="s">
-        <v>33</v>
-      </c>
       <c r="F9">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="G9">
-        <v>20.688890000000001</v>
+        <v>20.133333</v>
       </c>
       <c r="H9">
-        <v>13.300001</v>
+        <v>15.099999</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J9">
-        <v>14.336</v>
+        <v>14.885001000000001</v>
       </c>
       <c r="K9">
-        <v>360600000</v>
+        <v>423100000</v>
       </c>
       <c r="L9">
-        <v>5.6327027632036586</v>
+        <v>6.5201648087588282</v>
       </c>
       <c r="M9">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="N9">
         <v>1.4</v>
       </c>
       <c r="O9">
-        <v>43.959970189185512</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+        <v>42.124104664775608</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10">
-        <v>107.1999969482422</v>
+        <v>118.370002746582</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
       </c>
       <c r="F10">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="G10">
-        <v>22.521007999999998</v>
+        <v>23.486113</v>
       </c>
       <c r="H10">
-        <v>14.427994999999999</v>
+        <v>15.93136</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J10">
-        <v>47.761001999999998</v>
+        <v>47.816001999999997</v>
       </c>
       <c r="K10">
-        <v>5965000192</v>
+        <v>6311000064</v>
       </c>
       <c r="L10">
-        <v>20.75865694250961</v>
+        <v>21.865363746164661</v>
       </c>
       <c r="M10">
-        <v>4.76</v>
+        <v>5.04</v>
       </c>
       <c r="N10">
         <v>7.43</v>
       </c>
       <c r="O10">
-        <v>26.061675033930541</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+        <v>27.502078022369361</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11">
-        <v>147.8999938964844</v>
+        <v>180.44999694824219</v>
       </c>
       <c r="E11" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11">
-        <v>47.709679999999999</v>
+        <v>58.209679999999999</v>
       </c>
       <c r="H11">
-        <v>35.898055999999997</v>
+        <v>43.798546000000002</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J11">
         <v>59.419995999999998</v>
@@ -1189,86 +1203,86 @@
         <v>4.12</v>
       </c>
       <c r="O11">
-        <v>57.566996088830372</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+        <v>52.278384578577743</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12">
+        <v>75.410003662109375</v>
+      </c>
+      <c r="E12" t="s">
         <v>36</v>
       </c>
-      <c r="D12">
-        <v>71.400001525878906</v>
-      </c>
-      <c r="E12" t="s">
-        <v>37</v>
-      </c>
       <c r="F12">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="G12">
-        <v>26.741572999999999</v>
+        <v>26.275262999999999</v>
       </c>
       <c r="H12">
-        <v>19.402173999999999</v>
+        <v>20.491848000000001</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J12">
-        <v>53.73</v>
+        <v>56.538999999999987</v>
       </c>
       <c r="K12">
-        <v>5511000064</v>
+        <v>5918000128</v>
       </c>
       <c r="L12">
-        <v>21.809331679631502</v>
+        <v>22.850303764132139</v>
       </c>
       <c r="M12">
-        <v>2.67</v>
+        <v>2.87</v>
       </c>
       <c r="N12">
         <v>3.68</v>
       </c>
       <c r="O12">
-        <v>28.942376667943531</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+        <v>28.707442446844141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13">
+        <v>19.190000534057621</v>
+      </c>
+      <c r="E13" t="s">
         <v>23</v>
       </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13">
-        <v>21.690000534057621</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
       <c r="F13">
-        <v>271</v>
+        <v>313</v>
       </c>
       <c r="G13">
-        <v>13.22561</v>
+        <v>11.701219999999999</v>
       </c>
       <c r="H13">
-        <v>9.5550660000000001</v>
+        <v>8.4537449999999996</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J13">
-        <v>4.6609997999999999</v>
+        <v>4.5310000000000006</v>
       </c>
       <c r="K13">
-        <v>958600000</v>
+        <v>954300032</v>
       </c>
       <c r="L13">
-        <v>1.1924235552220639</v>
+        <v>1.1780566033814761</v>
       </c>
       <c r="M13">
         <v>1.64</v>
@@ -1277,517 +1291,517 @@
         <v>2.27</v>
       </c>
       <c r="O13">
-        <v>25.36065984558179</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+        <v>26.502866067983881</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D14">
-        <v>180.17999267578119</v>
+        <v>161.75999450683591</v>
       </c>
       <c r="E14" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F14">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G14">
-        <v>21.919706000000001</v>
+        <v>19.302505</v>
       </c>
       <c r="H14">
-        <v>18.594427</v>
+        <v>16.692983999999999</v>
       </c>
       <c r="I14" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J14">
-        <v>31.132999999999999</v>
+        <v>31.643000000000001</v>
       </c>
       <c r="K14">
-        <v>6758000128</v>
+        <v>6832000000</v>
       </c>
       <c r="L14">
-        <v>24.059240782505299</v>
+        <v>23.87725928304895</v>
       </c>
       <c r="M14">
-        <v>8.2200000000000006</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="N14">
         <v>9.69</v>
       </c>
       <c r="O14">
-        <v>48.818593344366519</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+        <v>46.12516981128951</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15">
-        <v>200.30000305175781</v>
+        <v>231.5899963378906</v>
       </c>
       <c r="E15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F15">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="G15">
-        <v>31.150856000000001</v>
+        <v>35.089393999999999</v>
       </c>
       <c r="H15">
-        <v>24.103489</v>
+        <v>27.868832000000001</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J15">
-        <v>34.685000000000002</v>
+        <v>34.675997000000002</v>
       </c>
       <c r="K15">
-        <v>97294000128</v>
+        <v>99280003072</v>
       </c>
       <c r="L15">
-        <v>24.301263745783849</v>
+        <v>24.296116475658661</v>
       </c>
       <c r="M15">
-        <v>6.43</v>
+        <v>6.6</v>
       </c>
       <c r="N15">
         <v>8.31</v>
       </c>
       <c r="O15">
-        <v>32.318861603294472</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+        <v>32.144325819597611</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16">
+        <v>150.3999938964844</v>
+      </c>
+      <c r="E16" t="s">
         <v>23</v>
       </c>
-      <c r="C16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16">
-        <v>131.05000305175781</v>
-      </c>
-      <c r="E16" t="s">
-        <v>25</v>
-      </c>
       <c r="F16">
-        <v>441</v>
+        <v>378</v>
       </c>
       <c r="G16">
-        <v>19.272058000000001</v>
+        <v>27.395264000000001</v>
       </c>
       <c r="H16">
-        <v>15.1854</v>
+        <v>17.427578</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J16">
-        <v>18.905999999999999</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="K16">
-        <v>9370000384</v>
+        <v>7550000128</v>
       </c>
       <c r="L16">
-        <v>10.23786431925341</v>
+        <v>8.2290623763639541</v>
       </c>
       <c r="M16">
-        <v>6.8</v>
+        <v>5.49</v>
       </c>
       <c r="N16">
         <v>8.6300000000000008</v>
       </c>
       <c r="O16">
-        <v>19.561471876145148</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+        <v>21.631129642785091</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" t="s">
         <v>42</v>
       </c>
-      <c r="C17" t="s">
-        <v>43</v>
-      </c>
       <c r="D17">
-        <v>351.6300048828125</v>
+        <v>344.47000122070313</v>
       </c>
       <c r="E17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F17">
         <v>69</v>
       </c>
       <c r="G17">
-        <v>35.410876999999999</v>
+        <v>33.672535000000003</v>
       </c>
       <c r="H17">
-        <v>27.774881000000001</v>
+        <v>27.209322</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J17">
-        <v>69.707999999999998</v>
+        <v>70.031000000000006</v>
       </c>
       <c r="K17">
-        <v>19641999360</v>
+        <v>20060000256</v>
       </c>
       <c r="L17">
-        <v>52.210202623591513</v>
+        <v>51.577407114905903</v>
       </c>
       <c r="M17">
-        <v>9.93</v>
+        <v>10.23</v>
       </c>
       <c r="N17">
         <v>12.66</v>
       </c>
       <c r="O17">
-        <v>23.261174566994089</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+        <v>22.61027206439126</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D18">
-        <v>155.71000671386719</v>
+        <v>157.8500061035156</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F18">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="G18">
-        <v>15.888776</v>
+        <v>15.251207000000001</v>
       </c>
       <c r="H18">
-        <v>12.731807999999999</v>
+        <v>12.906788000000001</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J18">
-        <v>31.573</v>
+        <v>32.066001999999997</v>
       </c>
       <c r="K18">
-        <v>11015000064</v>
+        <v>11573000192</v>
       </c>
       <c r="L18">
-        <v>26.04881181510946</v>
+        <v>26.754051850850949</v>
       </c>
       <c r="M18">
-        <v>9.8000000000000007</v>
+        <v>10.35</v>
       </c>
       <c r="N18">
         <v>12.23</v>
       </c>
       <c r="O18">
-        <v>42.845680284839453</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+        <v>38.261570897579141</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D19">
-        <v>142.69999694824219</v>
+        <v>148.17999267578119</v>
       </c>
       <c r="E19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="G19">
-        <v>28.426293999999999</v>
+        <v>29.226821999999999</v>
       </c>
       <c r="H19">
-        <v>23.470393999999999</v>
+        <v>24.37171</v>
       </c>
       <c r="I19" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J19">
-        <v>35.5</v>
+        <v>35.204999999999998</v>
       </c>
       <c r="K19">
-        <v>1424999936</v>
+        <v>1432999936</v>
       </c>
       <c r="L19">
-        <v>18.415610746600951</v>
+        <v>18.120890015041461</v>
       </c>
       <c r="M19">
-        <v>5.0199999999999996</v>
+        <v>5.07</v>
       </c>
       <c r="N19">
         <v>6.08</v>
       </c>
       <c r="O19">
-        <v>22.03281874560183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+        <v>22.834199393923779</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>21</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20">
+        <v>125.9300003051758</v>
+      </c>
+      <c r="E20" t="s">
         <v>23</v>
       </c>
-      <c r="C20" t="s">
-        <v>46</v>
-      </c>
-      <c r="D20">
-        <v>137.5</v>
-      </c>
-      <c r="E20" t="s">
-        <v>25</v>
-      </c>
       <c r="F20">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="G20">
-        <v>14.50422</v>
+        <v>12.297852000000001</v>
       </c>
       <c r="H20">
-        <v>12.376238000000001</v>
+        <v>11.334834000000001</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J20">
-        <v>17.510999999999999</v>
+        <v>17.756</v>
       </c>
       <c r="K20">
-        <v>628000000</v>
+        <v>676000000</v>
       </c>
       <c r="L20">
-        <v>8.5314496054901205</v>
+        <v>9.2400221931992466</v>
       </c>
       <c r="M20">
-        <v>9.48</v>
+        <v>10.24</v>
       </c>
       <c r="N20">
         <v>11.11</v>
       </c>
       <c r="O20">
-        <v>25.77856046696002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+        <v>24.755942019001751</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D21">
-        <v>453.54998779296881</v>
+        <v>476.10000610351563</v>
       </c>
       <c r="E21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F21">
-        <v>289</v>
+        <v>273</v>
       </c>
       <c r="G21">
-        <v>18.069721000000001</v>
+        <v>21.640910000000002</v>
       </c>
       <c r="H21">
-        <v>15.591267999999999</v>
+        <v>16.36645</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J21">
-        <v>26.488</v>
+        <v>24.829000000000001</v>
       </c>
       <c r="K21">
-        <v>12549999616</v>
+        <v>10981000192</v>
       </c>
       <c r="L21">
-        <v>14.81997561254024</v>
+        <v>13.259515301391041</v>
       </c>
       <c r="M21">
-        <v>25.1</v>
+        <v>22</v>
       </c>
       <c r="N21">
         <v>29.09</v>
       </c>
       <c r="O21">
-        <v>31.758493277418651</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>32.896806930622837</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D22">
-        <v>490.1099853515625</v>
+        <v>520.16998291015625</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F22">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G22">
-        <v>37.904870000000003</v>
+        <v>38.163609999999998</v>
       </c>
       <c r="H22">
-        <v>32.783276000000001</v>
+        <v>34.793979999999998</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J22">
-        <v>55.247</v>
+        <v>55.561000000000007</v>
       </c>
       <c r="K22">
-        <v>96635002880</v>
+        <v>101831999488</v>
       </c>
       <c r="L22">
-        <v>35.789415272465227</v>
+        <v>36.146015822676603</v>
       </c>
       <c r="M22">
-        <v>12.93</v>
+        <v>13.63</v>
       </c>
       <c r="N22">
         <v>14.95</v>
       </c>
       <c r="O22">
-        <v>25.587278652876911</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+        <v>24.957353839396021</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23">
-        <v>557.530029296875</v>
+        <v>581.70001220703125</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23">
-        <v>56.000000000000007</v>
+        <v>52</v>
       </c>
       <c r="G23">
-        <v>39.097476999999998</v>
+        <v>39.224544999999999</v>
       </c>
       <c r="H23">
-        <v>34.037242999999997</v>
+        <v>35.512819999999998</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J23">
-        <v>61.845999999999997</v>
+        <v>62.078000000000003</v>
       </c>
       <c r="K23">
-        <v>13143000064</v>
+        <v>13585999872</v>
       </c>
       <c r="L23">
-        <v>45.213112751383562</v>
+        <v>44.925763469370708</v>
       </c>
       <c r="M23">
-        <v>14.26</v>
+        <v>14.83</v>
       </c>
       <c r="N23">
         <v>16.38</v>
       </c>
       <c r="O23">
-        <v>22.77213014443624</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+        <v>21.880006196455859</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D24">
-        <v>103.2799987792969</v>
+        <v>111.9899978637695</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F24">
-        <v>360</v>
+        <v>332</v>
       </c>
       <c r="G24">
-        <v>19.938224999999999</v>
+        <v>16.420819999999999</v>
       </c>
       <c r="H24">
-        <v>17.534804999999999</v>
+        <v>19.013582</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J24">
-        <v>39.542999999999999</v>
+        <v>41.48</v>
       </c>
       <c r="K24">
-        <v>2764199936</v>
+        <v>3649700096</v>
       </c>
       <c r="L24">
-        <v>13.71198897276127</v>
+        <v>17.659810882037171</v>
       </c>
       <c r="M24">
-        <v>5.18</v>
+        <v>6.82</v>
       </c>
       <c r="N24">
         <v>5.89</v>
       </c>
       <c r="O24">
-        <v>19.470508561942331</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+        <v>19.160258325907481</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25">
+        <v>100</v>
+      </c>
+      <c r="E25" t="s">
         <v>23</v>
       </c>
-      <c r="C25" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25">
-        <v>98</v>
-      </c>
-      <c r="E25" t="s">
-        <v>25</v>
-      </c>
       <c r="F25">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G25">
-        <v>41.880344000000001</v>
+        <v>42.735042999999997</v>
       </c>
       <c r="H25">
-        <v>36.029409999999999</v>
+        <v>36.764705999999997</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J25">
         <v>6.2409999999999997</v>
@@ -1805,614 +1819,614 @@
         <v>2.72</v>
       </c>
       <c r="O25">
-        <v>24.073290936790361</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+        <v>23.533480414029849</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D26">
-        <v>813.3599853515625</v>
+        <v>742.15997314453125</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F26">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="G26">
-        <v>31.896470000000001</v>
+        <v>26.317727999999999</v>
       </c>
       <c r="H26">
-        <v>30.46292</v>
+        <v>27.796253</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J26">
-        <v>36.578000000000003</v>
+        <v>37.594999999999999</v>
       </c>
       <c r="K26">
-        <v>8702799872</v>
+        <v>9415199744</v>
       </c>
       <c r="L26">
-        <v>28.33459111814113</v>
+        <v>29.273115447467571</v>
       </c>
       <c r="M26">
-        <v>25.5</v>
+        <v>28.2</v>
       </c>
       <c r="N26">
         <v>26.7</v>
       </c>
       <c r="O26">
-        <v>47.733915207660623</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+        <v>43.270417253024199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="C27" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27">
+        <v>32.970001220703118</v>
+      </c>
+      <c r="E27" t="s">
         <v>26</v>
       </c>
-      <c r="C27" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27">
-        <v>34.349998474121087</v>
-      </c>
-      <c r="E27" t="s">
-        <v>28</v>
-      </c>
       <c r="F27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G27">
-        <v>8.0069920000000003</v>
+        <v>10.635484999999999</v>
       </c>
       <c r="H27">
-        <v>7.3085110000000002</v>
+        <v>7.014894</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J27">
-        <v>22.016999999999999</v>
+        <v>22.035</v>
       </c>
       <c r="K27">
-        <v>1520527998976</v>
+        <v>1127194951680</v>
       </c>
       <c r="L27">
-        <v>7.9344361198138351</v>
+        <v>5.5838348244311069</v>
       </c>
       <c r="M27">
-        <v>4.29</v>
+        <v>3.1</v>
       </c>
       <c r="N27">
         <v>4.7</v>
       </c>
       <c r="O27">
-        <v>47.892961955687731</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+        <v>48.247457859823257</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D28">
-        <v>116.9499969482422</v>
+        <v>122.4499969482422</v>
       </c>
       <c r="E28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F28">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="G28">
-        <v>19.426909999999999</v>
+        <v>20.040915999999999</v>
       </c>
       <c r="H28">
-        <v>18.446370999999999</v>
+        <v>19.313879</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J28">
-        <v>48.826998000000003</v>
+        <v>49.838000000000001</v>
       </c>
       <c r="K28">
-        <v>4643999744</v>
+        <v>4729999872</v>
       </c>
       <c r="L28">
-        <v>15.220239866756501</v>
+        <v>15.33324647302905</v>
       </c>
       <c r="M28">
-        <v>6.02</v>
+        <v>6.11</v>
       </c>
       <c r="N28">
         <v>6.34</v>
       </c>
       <c r="O28">
-        <v>18.2199154816049</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+        <v>17.913676432310869</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>21</v>
+      </c>
+      <c r="C29" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29">
+        <v>132.94000244140619</v>
+      </c>
+      <c r="E29" t="s">
         <v>23</v>
       </c>
-      <c r="C29" t="s">
-        <v>55</v>
-      </c>
-      <c r="D29">
-        <v>129.94999694824219</v>
-      </c>
-      <c r="E29" t="s">
-        <v>25</v>
-      </c>
       <c r="F29">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="G29">
-        <v>17.704360000000001</v>
+        <v>18.186046999999999</v>
       </c>
       <c r="H29">
-        <v>17.031454</v>
+        <v>17.423328000000001</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J29">
-        <v>19.545000999999999</v>
+        <v>19.409001</v>
       </c>
       <c r="K29">
-        <v>2464999936</v>
+        <v>2449999872</v>
       </c>
       <c r="L29">
-        <v>12.48164484200357</v>
+        <v>12.42519420062256</v>
       </c>
       <c r="M29">
-        <v>7.34</v>
+        <v>7.31</v>
       </c>
       <c r="N29">
         <v>7.63</v>
       </c>
       <c r="O29">
-        <v>19.457865499254961</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+        <v>18.94113927707048</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30">
-        <v>21.360000610351559</v>
+        <v>24.879999160766602</v>
       </c>
       <c r="E30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F30">
-        <v>554</v>
+        <v>471</v>
       </c>
       <c r="G30">
-        <v>9.4096919999999997</v>
+        <v>10.678112</v>
       </c>
       <c r="H30">
-        <v>9.753425</v>
+        <v>11.36073</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>5210999808</v>
+        <v>4792999936</v>
       </c>
       <c r="L30">
-        <v>25.984840469640911</v>
+        <v>24.461569062302619</v>
       </c>
       <c r="M30">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="N30">
         <v>2.19</v>
       </c>
       <c r="O30">
-        <v>27.372221883532301</v>
-      </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+        <v>27.33551834987211</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C31" t="s">
+        <v>56</v>
+      </c>
+      <c r="D31">
+        <v>203.8999938964844</v>
+      </c>
+      <c r="E31" t="s">
         <v>57</v>
       </c>
-      <c r="D31">
-        <v>166.77000427246091</v>
-      </c>
-      <c r="E31" t="s">
-        <v>58</v>
-      </c>
       <c r="F31">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G31">
-        <v>18.633520000000001</v>
+        <v>21.737739999999999</v>
       </c>
       <c r="H31">
-        <v>18.612724</v>
+        <v>22.756695000000001</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J31">
-        <v>37.726003000000013</v>
+        <v>37.921999999999997</v>
       </c>
       <c r="K31">
-        <v>110995996672</v>
+        <v>115572998144</v>
       </c>
       <c r="L31">
-        <v>30.856819860861741</v>
+        <v>31.118284681456949</v>
       </c>
       <c r="M31">
-        <v>8.9499999999999993</v>
+        <v>9.3800000000000008</v>
       </c>
       <c r="N31">
         <v>8.9600000000000009</v>
       </c>
       <c r="O31">
-        <v>31.86715633790724</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+        <v>31.103518754216541</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" t="s">
+        <v>58</v>
+      </c>
+      <c r="D32">
+        <v>20.479999542236332</v>
+      </c>
+      <c r="E32" t="s">
         <v>26</v>
       </c>
-      <c r="C32" t="s">
-        <v>59</v>
-      </c>
-      <c r="D32">
-        <v>18.180000305175781</v>
-      </c>
-      <c r="E32" t="s">
-        <v>28</v>
-      </c>
       <c r="F32">
-        <v>544</v>
+        <v>488</v>
       </c>
       <c r="G32">
-        <v>6.5161290000000003</v>
+        <v>7.0865049999999998</v>
       </c>
       <c r="H32">
-        <v>6.6109090000000004</v>
+        <v>7.447273</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J32">
-        <v>58.8</v>
+        <v>59.68</v>
       </c>
       <c r="K32">
-        <v>1019000000</v>
+        <v>1080999936</v>
       </c>
       <c r="L32">
-        <v>10.041387718820969</v>
+        <v>11.026110850399389</v>
       </c>
       <c r="M32">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="N32">
         <v>2.75</v>
       </c>
       <c r="O32">
-        <v>52.467748135245209</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+        <v>53.000983884134811</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D33">
-        <v>220.0899963378906</v>
+        <v>238.8800048828125</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F33">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="G33">
-        <v>26.107945999999998</v>
+        <v>25.71367</v>
       </c>
       <c r="H33">
-        <v>27.238861</v>
+        <v>29.564357999999999</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J33">
-        <v>68.481003999999999</v>
+        <v>69.115995999999996</v>
       </c>
       <c r="K33">
-        <v>1309346889728</v>
+        <v>1444887003136</v>
       </c>
       <c r="L33">
-        <v>41.686769633025442</v>
+        <v>42.481697237297887</v>
       </c>
       <c r="M33">
-        <v>8.43</v>
+        <v>9.2899999999999991</v>
       </c>
       <c r="N33">
         <v>8.08</v>
       </c>
       <c r="O33">
-        <v>45.875842776983824</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+        <v>43.050835739781448</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D34">
-        <v>43.099998474121087</v>
+        <v>44.580001831054688</v>
       </c>
       <c r="E34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F34">
-        <v>370</v>
+        <v>359</v>
       </c>
       <c r="G34">
-        <v>16.022304999999999</v>
+        <v>16.950571</v>
       </c>
       <c r="H34">
-        <v>16.387830000000001</v>
+        <v>16.950571</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J34">
-        <v>32.266998000000001</v>
+        <v>32.450000000000003</v>
       </c>
       <c r="K34">
-        <v>2710000128</v>
+        <v>2654000128</v>
       </c>
       <c r="L34">
-        <v>11.435082528811259</v>
+        <v>11.16721438560171</v>
       </c>
       <c r="M34">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="N34">
         <v>2.63</v>
       </c>
       <c r="O34">
-        <v>19.176071492506001</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+        <v>19.05130104963688</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D35">
-        <v>44.970001220703118</v>
+        <v>49.529998779296882</v>
       </c>
       <c r="E35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F35">
-        <v>3578</v>
+        <v>3078</v>
       </c>
       <c r="G35">
-        <v>6.9720936</v>
+        <v>7.1678724000000003</v>
       </c>
       <c r="H35">
-        <v>7.6220340000000002</v>
+        <v>8.3949149999999992</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J35">
         <v>0</v>
       </c>
       <c r="K35">
-        <v>6341936021504</v>
+        <v>6693464834048</v>
       </c>
       <c r="L35">
-        <v>28.104146008031432</v>
+        <v>28.72103458590216</v>
       </c>
       <c r="M35">
-        <v>6.45</v>
+        <v>6.91</v>
       </c>
       <c r="N35">
         <v>5.9</v>
       </c>
       <c r="O35">
-        <v>31.858504561556149</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+        <v>29.69022721756469</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36">
+        <v>65.819999694824219</v>
+      </c>
+      <c r="E36" t="s">
         <v>23</v>
       </c>
-      <c r="C36" t="s">
-        <v>63</v>
-      </c>
-      <c r="D36">
-        <v>59.909999847412109</v>
-      </c>
-      <c r="E36" t="s">
-        <v>25</v>
-      </c>
       <c r="F36">
-        <v>674</v>
+        <v>620</v>
       </c>
       <c r="G36">
-        <v>10.052013000000001</v>
+        <v>12.731140999999999</v>
       </c>
       <c r="H36">
-        <v>11.198131</v>
+        <v>12.302804</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J36">
-        <v>61.162996</v>
+        <v>62.061</v>
       </c>
       <c r="K36">
-        <v>10183999488</v>
+        <v>8762999808</v>
       </c>
       <c r="L36">
-        <v>50.301292507937191</v>
+        <v>43.25484806547454</v>
       </c>
       <c r="M36">
-        <v>5.96</v>
+        <v>5.17</v>
       </c>
       <c r="N36">
         <v>5.35</v>
       </c>
       <c r="O36">
-        <v>19.49064194111504</v>
-      </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+        <v>19.503102663931191</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D37">
-        <v>13.114999771118161</v>
+        <v>16.479999542236332</v>
       </c>
       <c r="E37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F37">
-        <v>547</v>
+        <v>425</v>
       </c>
       <c r="G37">
-        <v>7.4096045000000004</v>
+        <v>9.3636359999999996</v>
       </c>
       <c r="H37">
-        <v>13.952127000000001</v>
+        <v>17.531914</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J37">
         <v>0</v>
       </c>
       <c r="K37">
-        <v>10151000064</v>
+        <v>10119000064</v>
       </c>
       <c r="L37">
-        <v>31.698101116992639</v>
+        <v>32.249736812063553</v>
       </c>
       <c r="M37">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="N37">
         <v>0.94</v>
       </c>
       <c r="O37">
-        <v>30.117069530458139</v>
-      </c>
-    </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+        <v>30.89016806516544</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D38">
-        <v>18.260000228881839</v>
+        <v>20.270000457763668</v>
       </c>
       <c r="E38" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F38">
-        <v>240</v>
+        <v>214</v>
       </c>
       <c r="G38">
-        <v>9.0396040000000006</v>
+        <v>9.2136359999999993</v>
       </c>
       <c r="H38">
-        <v>17.390478000000002</v>
+        <v>19.304763999999999</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J38">
         <v>0</v>
       </c>
       <c r="K38">
-        <v>5630000128</v>
+        <v>6051999744</v>
       </c>
       <c r="L38">
-        <v>22.63225720298977</v>
+        <v>23.59086237853322</v>
       </c>
       <c r="M38">
-        <v>2.02</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N38">
         <v>1.05</v>
       </c>
       <c r="O38">
-        <v>35.94639633092347</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+        <v>35.140934831594002</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D39">
-        <v>15.170000076293951</v>
+        <v>17.129999160766602</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F39">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="G39">
-        <v>12.2338705</v>
+        <v>13.814515</v>
       </c>
       <c r="H39">
-        <v>37</v>
+        <v>41.780487000000001</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J39">
         <v>0</v>
       </c>
       <c r="K39">
-        <v>1177995968512</v>
+        <v>483675013120</v>
       </c>
       <c r="L39">
-        <v>22.5677633341305</v>
+        <v>14.45341900173403</v>
       </c>
       <c r="M39">
         <v>1.24</v>
@@ -2421,119 +2435,119 @@
         <v>0.41</v>
       </c>
       <c r="O39">
-        <v>36.396292051920028</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+        <v>33.717713686896509</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>66</v>
+      </c>
+      <c r="D40" t="s">
         <v>67</v>
       </c>
-      <c r="D40" t="s">
-        <v>68</v>
-      </c>
       <c r="E40" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F40">
         <v>0</v>
       </c>
       <c r="G40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O40" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" t="s">
         <v>69</v>
       </c>
-      <c r="C41" t="s">
-        <v>70</v>
-      </c>
       <c r="D41">
-        <v>17.479999542236332</v>
+        <v>15.090000152587891</v>
       </c>
       <c r="E41" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O41">
         <f>D41</f>
-        <v>17.479999542236332</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+        <v>15.090000152587891</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D42">
-        <v>2.9200000762939449</v>
+        <v>3.9900000095367432</v>
       </c>
       <c r="E42" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>19</v>
-      </c>
-      <c r="G42" t="s">
-        <v>19</v>
+        <v>17</v>
+      </c>
+      <c r="G42">
+        <v>0.115118295</v>
       </c>
       <c r="H42">
-        <v>-0.5289855</v>
+        <v>-0.72282606000000005</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J42">
         <v>-80.991</v>
@@ -2545,262 +2559,262 @@
         <v>-120.67624899812979</v>
       </c>
       <c r="M42">
-        <v>-96</v>
+        <v>34.659999999999997</v>
       </c>
       <c r="N42">
         <v>-5.52</v>
       </c>
       <c r="O42">
-        <v>167.69436274647649</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+        <v>138.73604265756191</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>28</v>
+      </c>
+      <c r="C43" t="s">
+        <v>71</v>
+      </c>
+      <c r="D43">
+        <v>18.72599983215332</v>
+      </c>
+      <c r="E43" t="s">
         <v>30</v>
       </c>
-      <c r="C43" t="s">
+      <c r="F43" t="s">
+        <v>17</v>
+      </c>
+      <c r="G43" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43" t="s">
+        <v>17</v>
+      </c>
+      <c r="M43" t="s">
+        <v>17</v>
+      </c>
+      <c r="N43" t="s">
+        <v>17</v>
+      </c>
+      <c r="O43">
+        <v>12.24047549670594</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>72</v>
       </c>
-      <c r="D43">
-        <v>18.982999801635739</v>
-      </c>
-      <c r="E43" t="s">
-        <v>18</v>
-      </c>
-      <c r="F43" t="s">
-        <v>19</v>
-      </c>
-      <c r="G43" t="s">
-        <v>19</v>
-      </c>
-      <c r="H43" t="s">
-        <v>19</v>
-      </c>
-      <c r="I43" t="s">
-        <v>19</v>
-      </c>
-      <c r="J43" t="s">
-        <v>19</v>
-      </c>
-      <c r="K43" t="s">
-        <v>19</v>
-      </c>
-      <c r="L43" t="s">
-        <v>19</v>
-      </c>
-      <c r="M43" t="s">
-        <v>19</v>
-      </c>
-      <c r="N43" t="s">
-        <v>19</v>
-      </c>
-      <c r="O43">
-        <v>13.61405019749199</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
+      <c r="C44" t="s">
         <v>73</v>
       </c>
-      <c r="C44" t="s">
-        <v>74</v>
-      </c>
       <c r="D44">
-        <v>6.1319999694824219</v>
+        <v>6.1979999542236328</v>
       </c>
       <c r="E44" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F44">
         <v>0</v>
       </c>
       <c r="G44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O44">
-        <v>2.6712918445884042</v>
-      </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.5679790859345881</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D45">
-        <v>6.2690000534057617</v>
+        <v>6.3249998092651367</v>
       </c>
       <c r="E45" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F45">
         <v>0</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O45">
-        <v>2.7153145304813111</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+        <v>2.603494122551655</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C46" t="s">
+        <v>75</v>
+      </c>
+      <c r="D46">
+        <v>76.830001831054688</v>
+      </c>
+      <c r="E46" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46">
+        <v>304</v>
+      </c>
+      <c r="G46">
+        <v>15.814316</v>
+      </c>
+      <c r="H46" t="s">
+        <v>17</v>
+      </c>
+      <c r="I46" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46" t="s">
+        <v>17</v>
+      </c>
+      <c r="M46" t="s">
+        <v>17</v>
+      </c>
+      <c r="N46" t="s">
+        <v>17</v>
+      </c>
+      <c r="O46">
+        <v>13.470578337591551</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>72</v>
+      </c>
+      <c r="C47" t="s">
         <v>76</v>
       </c>
-      <c r="D46">
-        <v>73.264999389648438</v>
-      </c>
-      <c r="E46" t="s">
-        <v>18</v>
-      </c>
-      <c r="F46">
-        <v>310</v>
-      </c>
-      <c r="G46">
-        <v>15.080513</v>
-      </c>
-      <c r="H46" t="s">
-        <v>19</v>
-      </c>
-      <c r="I46" t="s">
-        <v>19</v>
-      </c>
-      <c r="J46" t="s">
-        <v>19</v>
-      </c>
-      <c r="K46" t="s">
-        <v>19</v>
-      </c>
-      <c r="L46" t="s">
-        <v>19</v>
-      </c>
-      <c r="M46" t="s">
-        <v>19</v>
-      </c>
-      <c r="N46" t="s">
-        <v>19</v>
-      </c>
-      <c r="O46">
-        <v>13.904027157502201</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>73</v>
-      </c>
-      <c r="C47" t="s">
+      <c r="D47">
+        <v>51.360000610351563</v>
+      </c>
+      <c r="E47" t="s">
+        <v>30</v>
+      </c>
+      <c r="F47">
+        <v>278</v>
+      </c>
+      <c r="G47">
+        <v>15.669456500000001</v>
+      </c>
+      <c r="H47" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" t="s">
+        <v>17</v>
+      </c>
+      <c r="M47" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" t="s">
+        <v>17</v>
+      </c>
+      <c r="O47">
+        <v>18.045205964160129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>77</v>
       </c>
-      <c r="D47">
-        <v>48.990001678466797</v>
-      </c>
-      <c r="E47" t="s">
-        <v>18</v>
-      </c>
-      <c r="F47">
-        <v>302</v>
-      </c>
-      <c r="G47">
-        <v>15.763890999999999</v>
-      </c>
-      <c r="H47" t="s">
-        <v>19</v>
-      </c>
-      <c r="I47" t="s">
-        <v>19</v>
-      </c>
-      <c r="J47" t="s">
-        <v>19</v>
-      </c>
-      <c r="K47" t="s">
-        <v>19</v>
-      </c>
-      <c r="L47" t="s">
-        <v>19</v>
-      </c>
-      <c r="M47" t="s">
-        <v>19</v>
-      </c>
-      <c r="N47" t="s">
-        <v>19</v>
-      </c>
-      <c r="O47">
-        <v>18.748833165197212</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
+      <c r="C48" t="s">
         <v>78</v>
       </c>
-      <c r="C48" t="s">
-        <v>79</v>
-      </c>
       <c r="D48">
-        <v>33.950000762939453</v>
+        <v>45.080001831054688</v>
       </c>
       <c r="E48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F48">
         <v>613</v>
       </c>
       <c r="G48">
-        <v>16.090047999999999</v>
+        <v>21.364930999999999</v>
       </c>
       <c r="H48">
-        <v>8.530151</v>
+        <v>11.326632999999999</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J48">
-        <v>29.632000000000001</v>
+        <v>29.631</v>
       </c>
       <c r="K48">
         <v>602676992</v>
@@ -2815,649 +2829,649 @@
         <v>3.98</v>
       </c>
       <c r="O48">
-        <v>43.799609558577082</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+        <v>46.728514728461469</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C49" t="s">
+        <v>79</v>
+      </c>
+      <c r="D49">
+        <v>643.44000244140625</v>
+      </c>
+      <c r="E49" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49">
+        <v>113</v>
+      </c>
+      <c r="G49">
+        <v>27.320784</v>
+      </c>
+      <c r="H49" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49" t="s">
+        <v>17</v>
+      </c>
+      <c r="M49" t="s">
+        <v>17</v>
+      </c>
+      <c r="N49" t="s">
+        <v>17</v>
+      </c>
+      <c r="O49">
+        <v>19.781457726672151</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" t="s">
         <v>80</v>
       </c>
-      <c r="D49">
-        <v>606.780029296875</v>
-      </c>
-      <c r="E49" t="s">
-        <v>18</v>
-      </c>
-      <c r="F49">
-        <v>121</v>
-      </c>
-      <c r="G49">
-        <v>26.229430000000001</v>
-      </c>
-      <c r="H49" t="s">
-        <v>19</v>
-      </c>
-      <c r="I49" t="s">
-        <v>19</v>
-      </c>
-      <c r="J49" t="s">
-        <v>19</v>
-      </c>
-      <c r="K49" t="s">
-        <v>19</v>
-      </c>
-      <c r="L49" t="s">
-        <v>19</v>
-      </c>
-      <c r="M49" t="s">
-        <v>19</v>
-      </c>
-      <c r="N49" t="s">
-        <v>19</v>
-      </c>
-      <c r="O49">
-        <v>20.582577824263218</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>73</v>
-      </c>
-      <c r="C50" t="s">
+      <c r="D50">
+        <v>53.220001220703118</v>
+      </c>
+      <c r="E50" t="s">
+        <v>30</v>
+      </c>
+      <c r="F50" t="s">
+        <v>17</v>
+      </c>
+      <c r="G50" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" t="s">
+        <v>17</v>
+      </c>
+      <c r="I50" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50" t="s">
+        <v>17</v>
+      </c>
+      <c r="M50" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" t="s">
+        <v>17</v>
+      </c>
+      <c r="O50">
+        <v>44.805026182776693</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" t="s">
         <v>81</v>
       </c>
-      <c r="D50">
-        <v>48.33599853515625</v>
-      </c>
-      <c r="E50" t="s">
-        <v>18</v>
-      </c>
-      <c r="F50" t="s">
-        <v>19</v>
-      </c>
-      <c r="G50" t="s">
-        <v>19</v>
-      </c>
-      <c r="H50" t="s">
-        <v>19</v>
-      </c>
-      <c r="I50" t="s">
-        <v>19</v>
-      </c>
-      <c r="J50" t="s">
-        <v>19</v>
-      </c>
-      <c r="K50" t="s">
-        <v>19</v>
-      </c>
-      <c r="L50" t="s">
-        <v>19</v>
-      </c>
-      <c r="M50" t="s">
-        <v>19</v>
-      </c>
-      <c r="N50" t="s">
-        <v>19</v>
-      </c>
-      <c r="O50">
-        <v>48.423981708974331</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>73</v>
-      </c>
-      <c r="C51" t="s">
+      <c r="D51">
+        <v>18.271299362182621</v>
+      </c>
+      <c r="E51" t="s">
+        <v>30</v>
+      </c>
+      <c r="F51" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" t="s">
+        <v>17</v>
+      </c>
+      <c r="L51" t="s">
+        <v>17</v>
+      </c>
+      <c r="M51" t="s">
+        <v>17</v>
+      </c>
+      <c r="N51" t="s">
+        <v>17</v>
+      </c>
+      <c r="O51">
+        <v>25.112411570309352</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" t="s">
         <v>82</v>
       </c>
-      <c r="D51">
-        <v>15.20699977874756</v>
-      </c>
-      <c r="E51" t="s">
-        <v>18</v>
-      </c>
-      <c r="F51" t="s">
-        <v>19</v>
-      </c>
-      <c r="G51" t="s">
-        <v>19</v>
-      </c>
-      <c r="H51" t="s">
-        <v>19</v>
-      </c>
-      <c r="I51" t="s">
-        <v>19</v>
-      </c>
-      <c r="J51" t="s">
-        <v>19</v>
-      </c>
-      <c r="K51" t="s">
-        <v>19</v>
-      </c>
-      <c r="L51" t="s">
-        <v>19</v>
-      </c>
-      <c r="M51" t="s">
-        <v>19</v>
-      </c>
-      <c r="N51" t="s">
-        <v>19</v>
-      </c>
-      <c r="O51">
-        <v>25.500153581710549</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="D52">
+        <v>147.177001953125</v>
+      </c>
+      <c r="E52" t="s">
         <v>30</v>
       </c>
-      <c r="C52" t="s">
+      <c r="F52" t="s">
+        <v>17</v>
+      </c>
+      <c r="G52" t="s">
+        <v>17</v>
+      </c>
+      <c r="H52" t="s">
+        <v>17</v>
+      </c>
+      <c r="I52" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52" t="s">
+        <v>17</v>
+      </c>
+      <c r="M52" t="s">
+        <v>17</v>
+      </c>
+      <c r="N52" t="s">
+        <v>17</v>
+      </c>
+      <c r="O52">
+        <v>10.954418454178921</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>28</v>
+      </c>
+      <c r="C53" t="s">
         <v>83</v>
       </c>
-      <c r="D52">
-        <v>144.92500305175781</v>
-      </c>
-      <c r="E52" t="s">
-        <v>18</v>
-      </c>
-      <c r="F52" t="s">
-        <v>19</v>
-      </c>
-      <c r="G52" t="s">
-        <v>19</v>
-      </c>
-      <c r="H52" t="s">
-        <v>19</v>
-      </c>
-      <c r="I52" t="s">
-        <v>19</v>
-      </c>
-      <c r="J52" t="s">
-        <v>19</v>
-      </c>
-      <c r="K52" t="s">
-        <v>19</v>
-      </c>
-      <c r="L52" t="s">
-        <v>19</v>
-      </c>
-      <c r="M52" t="s">
-        <v>19</v>
-      </c>
-      <c r="N52" t="s">
-        <v>19</v>
-      </c>
-      <c r="O52">
-        <v>11.43144535410117</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
+      <c r="D53" t="s">
+        <v>84</v>
+      </c>
+      <c r="E53" t="s">
         <v>30</v>
-      </c>
-      <c r="C53" t="s">
-        <v>84</v>
-      </c>
-      <c r="D53" t="s">
-        <v>85</v>
-      </c>
-      <c r="E53" t="s">
-        <v>18</v>
       </c>
       <c r="F53">
         <v>0</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O53" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C54" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D54">
-        <v>20.545000076293949</v>
+        <v>22.440000534057621</v>
       </c>
       <c r="E54" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F54">
         <v>0</v>
       </c>
       <c r="G54">
-        <v>31.338073999999999</v>
+        <v>34.010292</v>
       </c>
       <c r="H54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O54">
-        <v>26.035363660396289</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.25">
+        <v>25.393508186371779</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C55" t="s">
+        <v>86</v>
+      </c>
+      <c r="D55">
+        <v>73.44000244140625</v>
+      </c>
+      <c r="E55" t="s">
+        <v>30</v>
+      </c>
+      <c r="F55">
+        <v>377</v>
+      </c>
+      <c r="G55" t="s">
+        <v>17</v>
+      </c>
+      <c r="H55" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55" t="s">
+        <v>17</v>
+      </c>
+      <c r="L55" t="s">
+        <v>17</v>
+      </c>
+      <c r="M55" t="s">
+        <v>17</v>
+      </c>
+      <c r="N55" t="s">
+        <v>17</v>
+      </c>
+      <c r="O55">
+        <v>5.0084612475789312</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>66</v>
+      </c>
+      <c r="C56" t="s">
         <v>87</v>
       </c>
-      <c r="D55">
-        <v>73.279998779296875</v>
-      </c>
-      <c r="E55" t="s">
-        <v>18</v>
-      </c>
-      <c r="F55">
-        <v>375</v>
-      </c>
-      <c r="G55" t="s">
-        <v>19</v>
-      </c>
-      <c r="H55" t="s">
-        <v>19</v>
-      </c>
-      <c r="I55" t="s">
-        <v>19</v>
-      </c>
-      <c r="J55" t="s">
-        <v>19</v>
-      </c>
-      <c r="K55" t="s">
-        <v>19</v>
-      </c>
-      <c r="L55" t="s">
-        <v>19</v>
-      </c>
-      <c r="M55" t="s">
-        <v>19</v>
-      </c>
-      <c r="N55" t="s">
-        <v>19</v>
-      </c>
-      <c r="O55">
-        <v>5.2571621197749359</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" t="s">
-        <v>88</v>
-      </c>
       <c r="D56" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E56" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F56">
         <v>0</v>
       </c>
       <c r="G56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O56" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>15</v>
       </c>
       <c r="C57" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D57">
-        <v>379.01998901367188</v>
+        <v>395.79000854492188</v>
       </c>
       <c r="E57" t="s">
         <v>15</v>
       </c>
       <c r="F57">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G57">
-        <v>16.822903</v>
+        <v>16.608896000000001</v>
       </c>
       <c r="H57">
-        <v>15.438696999999999</v>
+        <v>16.121794000000001</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J57">
-        <v>19.863</v>
+        <v>19.943999999999999</v>
       </c>
       <c r="K57">
-        <v>5778999808</v>
+        <v>5970999808</v>
       </c>
       <c r="L57">
-        <v>8.0729203322391978</v>
+        <v>8.213430251373973</v>
       </c>
       <c r="M57">
-        <v>22.53</v>
+        <v>23.83</v>
       </c>
       <c r="N57">
         <v>24.55</v>
       </c>
       <c r="O57">
-        <v>28.52793693975595</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.25">
+        <v>28.036629270798201</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>89</v>
+      </c>
+      <c r="C58" t="s">
         <v>90</v>
       </c>
-      <c r="C58" t="s">
-        <v>91</v>
-      </c>
       <c r="D58">
-        <v>149.8699951171875</v>
+        <v>152.38999938964841</v>
       </c>
       <c r="E58" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F58">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G58">
-        <v>18.663761000000001</v>
+        <v>21.194714999999999</v>
       </c>
       <c r="H58">
-        <v>18.970884000000002</v>
+        <v>19.289873</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J58">
-        <v>21.734999999999999</v>
+        <v>23.555</v>
       </c>
       <c r="K58">
-        <v>4419999744</v>
+        <v>3939000064</v>
       </c>
       <c r="L58">
-        <v>18.031248104515921</v>
+        <v>16.010894099950089</v>
       </c>
       <c r="M58">
-        <v>8.0299999999999994</v>
+        <v>7.19</v>
       </c>
       <c r="N58">
         <v>7.9</v>
       </c>
       <c r="O58">
-        <v>36.320386406707762</v>
-      </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.25">
+        <v>28.943574193976151</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C59" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D59">
-        <v>143.22999572753909</v>
+        <v>177.16999816894531</v>
       </c>
       <c r="E59" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G59">
-        <v>651.04539999999997</v>
+        <v>590.56664999999998</v>
       </c>
       <c r="H59">
-        <v>304.74466000000001</v>
+        <v>376.95746000000003</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J59">
-        <v>13.976000000000001</v>
+        <v>17.375</v>
       </c>
       <c r="K59">
-        <v>570691008</v>
+        <v>763292032</v>
       </c>
       <c r="L59">
-        <v>18.32059821851664</v>
+        <v>22.184936181680779</v>
       </c>
       <c r="M59">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="N59">
         <v>0.47</v>
       </c>
       <c r="O59">
-        <v>72.803425355094788</v>
-      </c>
-    </row>
-    <row r="60" spans="1:15" x14ac:dyDescent="0.25">
+        <v>71.826711160229777</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C60" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D60">
-        <v>68.449996948242188</v>
+        <v>74.180000305175781</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G60">
-        <v>11.18464</v>
+        <v>16.782803999999999</v>
       </c>
       <c r="H60">
-        <v>9.8065899999999999</v>
+        <v>10.627507</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J60">
-        <v>15.811999999999999</v>
+        <v>15.827999999999999</v>
       </c>
       <c r="K60">
-        <v>1558000000</v>
+        <v>1013000000</v>
       </c>
       <c r="L60">
-        <v>7.9340020612451809</v>
+        <v>5.1177124712067892</v>
       </c>
       <c r="M60">
-        <v>6.12</v>
+        <v>4.42</v>
       </c>
       <c r="N60">
         <v>6.98</v>
       </c>
       <c r="O60">
-        <v>40.265404819872387</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.25">
+        <v>39.929992492705523</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C61" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D61">
-        <v>44.400001525878913</v>
+        <v>44.75</v>
       </c>
       <c r="E61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F61">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G61">
-        <v>18.577406</v>
+        <v>18.491734999999998</v>
       </c>
       <c r="H61">
-        <v>17.209302999999998</v>
+        <v>17.344961000000001</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J61">
-        <v>15.000999999999999</v>
+        <v>15.113</v>
       </c>
       <c r="K61">
-        <v>916000000</v>
+        <v>919000000</v>
       </c>
       <c r="L61">
-        <v>8.087585993712608</v>
+        <v>8.0374319497661482</v>
       </c>
       <c r="M61">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="N61">
         <v>2.58</v>
       </c>
       <c r="O61">
-        <v>41.88882741313499</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.25">
+        <v>40.35149285636885</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C62" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D62">
-        <v>14.159999847412109</v>
+        <v>15.02000045776367</v>
       </c>
       <c r="E62" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F62">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G62">
-        <v>12.990824999999999</v>
+        <v>13.907406999999999</v>
       </c>
       <c r="H62">
-        <v>9.5675670000000004</v>
+        <v>10.148649000000001</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J62">
-        <v>38.176997999999998</v>
+        <v>38.534999999999997</v>
       </c>
       <c r="K62">
-        <v>2350000128</v>
+        <v>2351000064</v>
       </c>
       <c r="L62">
-        <v>9.5758125530442939</v>
+        <v>9.614362834791228</v>
       </c>
       <c r="M62">
-        <v>1.0900000000000001</v>
+        <v>1.08</v>
       </c>
       <c r="N62">
         <v>1.48</v>
       </c>
       <c r="O62">
-        <v>28.060995978571199</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.25">
+        <v>29.074871319927791</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C63" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D63">
-        <v>20.440000534057621</v>
+        <v>23.139999389648441</v>
       </c>
       <c r="E63" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F63">
-        <v>1288</v>
+        <v>562</v>
       </c>
       <c r="G63" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H63">
-        <v>10.590674</v>
+        <v>11.989637</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J63">
         <v>3.5609999999999999</v>
@@ -3469,83 +3483,83 @@
         <v>-2.255997845024639</v>
       </c>
       <c r="M63">
-        <v>-5.01</v>
+        <v>-5.0199999999999996</v>
       </c>
       <c r="N63">
         <v>1.93</v>
       </c>
       <c r="O63">
-        <v>73.285134463209005</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.25">
+        <v>72.65798250054317</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C64" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E64" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F64">
         <v>0</v>
       </c>
       <c r="G64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N64" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="O64" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C65" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D65">
-        <v>10.60999965667725</v>
+        <v>12.55000019073486</v>
       </c>
       <c r="E65" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G65" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H65">
-        <v>3.6712799999999999</v>
+        <v>4.3425602999999997</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J65">
         <v>8.8730000000000011</v>
@@ -3563,77 +3577,77 @@
         <v>2.89</v>
       </c>
       <c r="O65">
-        <v>83.804365951701783</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.25">
+        <v>82.172415526498753</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D66">
-        <v>81.139999389648438</v>
+        <v>93.69000244140625</v>
       </c>
       <c r="E66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F66">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="G66">
-        <v>12.818325</v>
+        <v>13.838996</v>
       </c>
       <c r="H66">
-        <v>11.285118000000001</v>
+        <v>13.030599</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66">
-        <v>12163999744</v>
+        <v>12903999488</v>
       </c>
       <c r="L66">
-        <v>16.9370214423048</v>
+        <v>17.719188154565511</v>
       </c>
       <c r="M66">
-        <v>6.33</v>
+        <v>6.77</v>
       </c>
       <c r="N66">
         <v>7.19</v>
       </c>
       <c r="O66">
-        <v>34.341302543328503</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.25">
+        <v>33.222800825878238</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C67" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D67">
-        <v>217.78999328613281</v>
+        <v>251.8800048828125</v>
       </c>
       <c r="E67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F67">
-        <v>509</v>
+        <v>437</v>
       </c>
       <c r="G67">
-        <v>10.9994955</v>
+        <v>12.500249</v>
       </c>
       <c r="H67">
-        <v>10.531431</v>
+        <v>12.179883999999999</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J67">
         <v>0</v>
@@ -3645,16 +3659,111 @@
         <v>30.76192656777258</v>
       </c>
       <c r="M67">
-        <v>19.8</v>
+        <v>20.149999999999999</v>
       </c>
       <c r="N67">
         <v>20.68</v>
       </c>
       <c r="O67">
-        <v>24.990260617528389</v>
+        <v>23.099991624605771</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" t="s">
+        <v>100</v>
+      </c>
+      <c r="D68">
+        <v>317.54998779296881</v>
+      </c>
+      <c r="E68" t="s">
+        <v>41</v>
+      </c>
+      <c r="F68" t="s">
+        <v>17</v>
+      </c>
+      <c r="G68">
+        <v>30.592483999999999</v>
+      </c>
+      <c r="H68">
+        <v>88.949579999999997</v>
+      </c>
+      <c r="I68" t="s">
+        <v>17</v>
+      </c>
+      <c r="J68">
+        <v>30.122</v>
+      </c>
+      <c r="K68">
+        <v>2860652032</v>
+      </c>
+      <c r="L68">
+        <v>42.657831451507121</v>
+      </c>
+      <c r="M68">
+        <v>10.38</v>
+      </c>
+      <c r="N68">
+        <v>3.57</v>
+      </c>
+      <c r="O68">
+        <v>86.667457095501092</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>21</v>
+      </c>
+      <c r="C69" t="s">
+        <v>101</v>
+      </c>
+      <c r="D69">
+        <v>49.650001525878913</v>
+      </c>
+      <c r="E69" t="s">
+        <v>23</v>
+      </c>
+      <c r="F69">
+        <v>491</v>
+      </c>
+      <c r="G69">
+        <v>12.109756000000001</v>
+      </c>
+      <c r="H69">
+        <v>10.563829999999999</v>
+      </c>
+      <c r="I69" t="s">
+        <v>17</v>
+      </c>
+      <c r="J69">
+        <v>20.035</v>
+      </c>
+      <c r="K69">
+        <v>2284699904</v>
+      </c>
+      <c r="L69">
+        <v>11.724467077620339</v>
+      </c>
+      <c r="M69">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="N69">
+        <v>4.7</v>
+      </c>
+      <c r="O69">
+        <v>21.722377935742522</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:O69" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="^VIX"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Stock Selection/tickers_used.xlsx
+++ b/Stock Selection/tickers_used.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36.41999816894531</v>
+        <v>37.95000076293945</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3.2258635</v>
+        <v>3.3613818</v>
       </c>
       <c r="H2" t="n">
-        <v>-5.9901314</v>
+        <v>-6.2417765</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -558,10 +558,10 @@
         <v>11.29</v>
       </c>
       <c r="N2" t="n">
-        <v>-6.079999875953525</v>
+        <v>-6.079999942795045</v>
       </c>
       <c r="O2" t="n">
-        <v>53.99747189777327</v>
+        <v>54.01001382992659</v>
       </c>
     </row>
     <row r="3">
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>203.1199951171875</v>
+        <v>205.6799926757812</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>127.74842</v>
+        <v>128.54999</v>
       </c>
       <c r="H3" t="n">
-        <v>28.211111</v>
+        <v>28.566666</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -614,13 +614,13 @@
         <v>12.29626464029078</v>
       </c>
       <c r="M3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="N3" t="n">
-        <v>7.199999855276437</v>
+        <v>7.199999911637614</v>
       </c>
       <c r="O3" t="n">
-        <v>35.70169778808636</v>
+        <v>35.70461520547995</v>
       </c>
     </row>
     <row r="4">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>346.1700134277344</v>
+        <v>345.3500061035156</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -648,13 +648,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G4" t="n">
-        <v>88.989716</v>
+        <v>88.32481</v>
       </c>
       <c r="H4" t="n">
-        <v>56.10535</v>
+        <v>55.972446</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -671,13 +671,13 @@
         <v>31.39371858717731</v>
       </c>
       <c r="M4" t="n">
-        <v>3.89</v>
+        <v>3.91</v>
       </c>
       <c r="N4" t="n">
-        <v>6.170000070006414</v>
+        <v>6.170000255188341</v>
       </c>
       <c r="O4" t="n">
-        <v>57.44734040964799</v>
+        <v>57.34017744620709</v>
       </c>
     </row>
     <row r="5">
@@ -697,7 +697,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33.11999893188477</v>
+        <v>32.45000076293945</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>50.953846</v>
+        <v>49.92308</v>
       </c>
       <c r="H5" t="n">
-        <v>11.076922</v>
+        <v>10.852843</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -733,10 +733,10 @@
         <v>0.65</v>
       </c>
       <c r="N5" t="n">
-        <v>2.990000194267393</v>
+        <v>2.99000001777778</v>
       </c>
       <c r="O5" t="n">
-        <v>44.00755691068372</v>
+        <v>43.93167631734155</v>
       </c>
     </row>
     <row r="6">
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.20499992370605</v>
+        <v>30.30999946594238</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -764,13 +764,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>401.9999999999999</v>
+        <v>407</v>
       </c>
       <c r="G6" t="n">
-        <v>15.897368</v>
+        <v>16.037037</v>
       </c>
       <c r="H6" t="n">
-        <v>7.9070683</v>
+        <v>7.934555</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -787,13 +787,13 @@
         <v>5.00016556506793</v>
       </c>
       <c r="M6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="N6" t="n">
-        <v>3.819999875770145</v>
+        <v>3.819999920089077</v>
       </c>
       <c r="O6" t="n">
-        <v>21.17852781617214</v>
+        <v>21.18096499995337</v>
       </c>
     </row>
     <row r="7">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>210.7100067138672</v>
+        <v>209.6300048828125</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>18.009403</v>
+        <v>17.932423</v>
       </c>
       <c r="H7" t="n">
-        <v>10.1011505</v>
+        <v>10.0493765</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -846,13 +846,13 @@
         <v>28.9511509411165</v>
       </c>
       <c r="M7" t="n">
-        <v>11.7</v>
+        <v>11.69</v>
       </c>
       <c r="N7" t="n">
-        <v>20.86000072109283</v>
+        <v>20.86000110383092</v>
       </c>
       <c r="O7" t="n">
-        <v>62.3511976728598</v>
+        <v>62.3507437554203</v>
       </c>
     </row>
     <row r="8">
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3698</v>
+        <v>3675.60009765625</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -921,7 +921,7 @@
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>18.0759090914343</v>
+        <v>18.08145297329331</v>
       </c>
     </row>
     <row r="9">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>22.70000076293945</v>
+        <v>23.03000068664551</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G9" t="n">
-        <v>21.61905</v>
+        <v>21.933334</v>
       </c>
       <c r="H9" t="n">
-        <v>16.214287</v>
+        <v>16.45</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -975,10 +975,10 @@
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>1.399999936040324</v>
+        <v>1.400000041741368</v>
       </c>
       <c r="O9" t="n">
-        <v>41.72925501469297</v>
+        <v>41.74702021309368</v>
       </c>
     </row>
     <row r="10">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>112.2600021362305</v>
+        <v>113.620002746582</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="G10" t="n">
-        <v>22.27381</v>
+        <v>22.543652</v>
       </c>
       <c r="H10" t="n">
-        <v>15.109018</v>
+        <v>15.29206</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1032,10 +1032,10 @@
         <v>5.04</v>
       </c>
       <c r="N10" t="n">
-        <v>7.429999893853489</v>
+        <v>7.429999800326577</v>
       </c>
       <c r="O10" t="n">
-        <v>27.68971548505991</v>
+        <v>27.71019464372183</v>
       </c>
     </row>
     <row r="11">
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>170.2899932861328</v>
+        <v>176.2400054931641</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1066,10 +1066,10 @@
         <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>48.37784</v>
+        <v>50.210827</v>
       </c>
       <c r="H11" t="n">
-        <v>41.332523</v>
+        <v>42.776703</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1086,13 +1086,13 @@
         <v>52.41378363138983</v>
       </c>
       <c r="M11" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="N11" t="n">
-        <v>4.119999964341224</v>
+        <v>4.119999745963686</v>
       </c>
       <c r="O11" t="n">
-        <v>49.78603761816388</v>
+        <v>49.75188948083932</v>
       </c>
     </row>
     <row r="12">
@@ -1112,7 +1112,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>70.30999755859375</v>
+        <v>70.79000091552734</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="G12" t="n">
-        <v>24.498259</v>
+        <v>24.665506</v>
       </c>
       <c r="H12" t="n">
-        <v>19.105978</v>
+        <v>19.236412</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
         <v>2.87</v>
       </c>
       <c r="N12" t="n">
-        <v>3.679999922463731</v>
+        <v>3.680000247214883</v>
       </c>
       <c r="O12" t="n">
-        <v>28.72386789013239</v>
+        <v>28.63745033459384</v>
       </c>
     </row>
     <row r="13">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.38999938964844</v>
+        <v>18.32999992370605</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="G13" t="n">
-        <v>11.213414</v>
+        <v>11.176829</v>
       </c>
       <c r="H13" t="n">
-        <v>8.101321</v>
+        <v>8.07489</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1203,10 +1203,10 @@
         <v>1.64</v>
       </c>
       <c r="N13" t="n">
-        <v>2.270000088830999</v>
+        <v>2.269999953399496</v>
       </c>
       <c r="O13" t="n">
-        <v>25.84166483457696</v>
+        <v>25.8432806792828</v>
       </c>
     </row>
     <row r="14">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>178.1300048828125</v>
+        <v>189.7599945068359</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1234,13 +1234,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="G14" t="n">
-        <v>21.256563</v>
+        <v>22.671446</v>
       </c>
       <c r="H14" t="n">
-        <v>18.38287</v>
+        <v>19.583076</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1257,13 +1257,13 @@
         <v>23.87725928304895</v>
       </c>
       <c r="M14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>9.689999705313289</v>
+        <v>9.689999390638935</v>
       </c>
       <c r="O14" t="n">
-        <v>45.26959854984195</v>
+        <v>45.38540031405748</v>
       </c>
     </row>
     <row r="15">
@@ -1283,7 +1283,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>238.9900054931641</v>
+        <v>237.8800048828125</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
         <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>36.210606</v>
+        <v>36.042427</v>
       </c>
       <c r="H15" t="n">
-        <v>28.759325</v>
+        <v>28.625751</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1317,10 +1317,10 @@
         <v>6.6</v>
       </c>
       <c r="N15" t="n">
-        <v>8.310000512639434</v>
+        <v>8.310000491613739</v>
       </c>
       <c r="O15" t="n">
-        <v>32.41387224248927</v>
+        <v>32.20725544916472</v>
       </c>
     </row>
     <row r="16">
@@ -1340,7 +1340,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>141.2299957275391</v>
+        <v>140.7299957275391</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1348,13 +1348,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>405.9999999999999</v>
+        <v>403</v>
       </c>
       <c r="G16" t="n">
-        <v>25.724955</v>
+        <v>25.63388</v>
       </c>
       <c r="H16" t="n">
-        <v>16.365005</v>
+        <v>16.307068</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1374,10 +1374,10 @@
         <v>5.49</v>
       </c>
       <c r="N16" t="n">
-        <v>8.630000157503103</v>
+        <v>8.629999931780443</v>
       </c>
       <c r="O16" t="n">
-        <v>21.98042117923055</v>
+        <v>21.98092298714878</v>
       </c>
     </row>
     <row r="17">
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>346.2000122070312</v>
+        <v>338.1799926757812</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G17" t="n">
-        <v>33.841644</v>
+        <v>32.99317</v>
       </c>
       <c r="H17" t="n">
-        <v>27.345972</v>
+        <v>26.71248</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1428,13 +1428,13 @@
         <v>51.5774071149059</v>
       </c>
       <c r="M17" t="n">
-        <v>10.23</v>
+        <v>10.25</v>
       </c>
       <c r="N17" t="n">
-        <v>12.66000024453441</v>
+        <v>12.65999984560704</v>
       </c>
       <c r="O17" t="n">
-        <v>22.7439173900362</v>
+        <v>22.83990030182712</v>
       </c>
     </row>
     <row r="18">
@@ -1454,7 +1454,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>165.2599945068359</v>
+        <v>168.1300048828125</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G18" t="n">
-        <v>15.951737</v>
+        <v>16.228765</v>
       </c>
       <c r="H18" t="n">
-        <v>13.512673</v>
+        <v>13.747343</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1488,10 +1488,10 @@
         <v>10.36</v>
       </c>
       <c r="N18" t="n">
-        <v>12.23000027506297</v>
+        <v>12.22999999947717</v>
       </c>
       <c r="O18" t="n">
-        <v>36.95493219345893</v>
+        <v>36.84403152732129</v>
       </c>
     </row>
     <row r="19">
@@ -1511,7 +1511,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>148.2599945068359</v>
+        <v>145.2599945068359</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1522,10 +1522,10 @@
         <v>192</v>
       </c>
       <c r="G19" t="n">
-        <v>29.18504</v>
+        <v>28.650885</v>
       </c>
       <c r="H19" t="n">
-        <v>24.384869</v>
+        <v>23.891447</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1542,13 +1542,13 @@
         <v>18.12089001504146</v>
       </c>
       <c r="M19" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="N19" t="n">
-        <v>6.07999963037882</v>
+        <v>6.079999863835621</v>
       </c>
       <c r="O19" t="n">
-        <v>23.11351002235296</v>
+        <v>23.20702050706216</v>
       </c>
     </row>
     <row r="20">
@@ -1568,7 +1568,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>123.9300003051758</v>
+        <v>124.0400009155273</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G20" t="n">
-        <v>12.102539</v>
+        <v>12.113281</v>
       </c>
       <c r="H20" t="n">
-        <v>11.154816</v>
+        <v>11.164717</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1602,10 +1602,10 @@
         <v>10.24</v>
       </c>
       <c r="N20" t="n">
-        <v>11.10999951098932</v>
+        <v>11.1099995562384</v>
       </c>
       <c r="O20" t="n">
-        <v>24.97747982141185</v>
+        <v>24.97514503631669</v>
       </c>
     </row>
     <row r="21">
@@ -1625,7 +1625,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>511.2999877929688</v>
+        <v>517.5999755859375</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1633,13 +1633,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G21" t="n">
-        <v>23.262056</v>
+        <v>23.537971</v>
       </c>
       <c r="H21" t="n">
-        <v>17.576487</v>
+        <v>17.793055</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1656,13 +1656,13 @@
         <v>13.25951530139104</v>
       </c>
       <c r="M21" t="n">
-        <v>21.98</v>
+        <v>21.99</v>
       </c>
       <c r="N21" t="n">
-        <v>29.08999891690352</v>
+        <v>29.09000031674929</v>
       </c>
       <c r="O21" t="n">
-        <v>33.26046516822021</v>
+        <v>33.22972117950654</v>
       </c>
     </row>
     <row r="22">
@@ -1682,7 +1682,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>510.0199890136719</v>
+        <v>508.4500122070312</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1690,13 +1690,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G22" t="n">
-        <v>37.391495</v>
+        <v>37.33113</v>
       </c>
       <c r="H22" t="n">
-        <v>34.11505</v>
+        <v>34.010036</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1713,13 +1713,13 @@
         <v>36.1460158226766</v>
       </c>
       <c r="M22" t="n">
-        <v>13.64</v>
+        <v>13.62</v>
       </c>
       <c r="N22" t="n">
-        <v>14.94999975124386</v>
+        <v>14.94999923572652</v>
       </c>
       <c r="O22" t="n">
-        <v>24.79939496703536</v>
+        <v>24.73960008382995</v>
       </c>
     </row>
     <row r="23">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>598.6300048828125</v>
+        <v>586.0499877929688</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1747,13 +1747,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G23" t="n">
-        <v>40.338947</v>
+        <v>39.464645</v>
       </c>
       <c r="H23" t="n">
-        <v>36.546402</v>
+        <v>35.77839</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1770,13 +1770,13 @@
         <v>44.92576346937071</v>
       </c>
       <c r="M23" t="n">
-        <v>14.84</v>
+        <v>14.85</v>
       </c>
       <c r="N23" t="n">
-        <v>16.37999836161197</v>
+        <v>16.37999887063025</v>
       </c>
       <c r="O23" t="n">
-        <v>21.93641278850285</v>
+        <v>22.04241757165076</v>
       </c>
     </row>
     <row r="24">
@@ -1796,7 +1796,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>107.5199966430664</v>
+        <v>106.4400024414062</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1804,13 +1804,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G24" t="n">
-        <v>15.765395</v>
+        <v>15.6070385</v>
       </c>
       <c r="H24" t="n">
-        <v>18.25467</v>
+        <v>18.071308</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
         <v>6.82</v>
       </c>
       <c r="N24" t="n">
-        <v>5.889999470988323</v>
+        <v>5.88999990711277</v>
       </c>
       <c r="O24" t="n">
-        <v>19.29526882246841</v>
+        <v>19.26680359544233</v>
       </c>
     </row>
     <row r="25">
@@ -1853,7 +1853,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>104.2699966430664</v>
+        <v>103.5999984741211</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1861,13 +1861,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G25" t="n">
-        <v>39.347168</v>
+        <v>39.094337</v>
       </c>
       <c r="H25" t="n">
-        <v>38.334557</v>
+        <v>38.088234</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1887,10 +1887,10 @@
         <v>2.65</v>
       </c>
       <c r="N25" t="n">
-        <v>2.720000041817789</v>
+        <v>2.720000052355305</v>
       </c>
       <c r="O25" t="n">
-        <v>24.11957295831651</v>
+        <v>24.091917189888</v>
       </c>
     </row>
     <row r="26">
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>872.27001953125</v>
+        <v>927.7999877929688</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G26" t="n">
-        <v>30.93156</v>
+        <v>32.830856</v>
       </c>
       <c r="H26" t="n">
-        <v>32.66929</v>
+        <v>34.74906</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1941,13 +1941,13 @@
         <v>29.27311544746757</v>
       </c>
       <c r="M26" t="n">
-        <v>28.2</v>
+        <v>28.26</v>
       </c>
       <c r="N26" t="n">
-        <v>26.69999928162657</v>
+        <v>26.7000024689292</v>
       </c>
       <c r="O26" t="n">
-        <v>42.39859158144832</v>
+        <v>42.57642578176039</v>
       </c>
     </row>
     <row r="27">
@@ -1967,7 +1967,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>27.23999977111816</v>
+        <v>24.40999984741211</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>8.787096999999999</v>
+        <v>7.8741937</v>
       </c>
       <c r="H27" t="n">
-        <v>5.795745</v>
+        <v>5.1936173</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2003,10 +2003,10 @@
         <v>3.1</v>
       </c>
       <c r="N27" t="n">
-        <v>4.699999701698085</v>
+        <v>4.699999718387435</v>
       </c>
       <c r="O27" t="n">
-        <v>51.68916239411227</v>
+        <v>52.67605770492458</v>
       </c>
     </row>
     <row r="28">
@@ -2026,7 +2026,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>121.0999984741211</v>
+        <v>120.3899993896484</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G28" t="n">
-        <v>19.819967</v>
+        <v>19.67157</v>
       </c>
       <c r="H28" t="n">
-        <v>19.100946</v>
+        <v>18.988958</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2057,13 +2057,13 @@
         <v>15.33324647302905</v>
       </c>
       <c r="M28" t="n">
-        <v>6.11</v>
+        <v>6.12</v>
       </c>
       <c r="N28" t="n">
-        <v>6.340000043669098</v>
+        <v>6.34000029857607</v>
       </c>
       <c r="O28" t="n">
-        <v>17.98019302927061</v>
+        <v>17.9782663392021</v>
       </c>
     </row>
     <row r="29">
@@ -2083,7 +2083,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>125.5899963378906</v>
+        <v>125.5100021362305</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="G29" t="n">
-        <v>17.180574</v>
+        <v>17.169632</v>
       </c>
       <c r="H29" t="n">
-        <v>16.460026</v>
+        <v>16.449541</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2117,10 +2117,10 @@
         <v>7.31</v>
       </c>
       <c r="N29" t="n">
-        <v>7.629999875935228</v>
+        <v>7.630000261784232</v>
       </c>
       <c r="O29" t="n">
-        <v>19.20081523067931</v>
+        <v>19.18738206151678</v>
       </c>
     </row>
     <row r="30">
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>25.34000015258789</v>
+        <v>25.31999969482422</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2148,13 +2148,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>461.0000000000001</v>
+        <v>463</v>
       </c>
       <c r="G30" t="n">
-        <v>10.875537</v>
+        <v>10.820513</v>
       </c>
       <c r="H30" t="n">
-        <v>11.570776</v>
+        <v>11.561644</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2171,13 +2171,13 @@
         <v>24.46156906230262</v>
       </c>
       <c r="M30" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="N30" t="n">
-        <v>2.190000061585143</v>
+        <v>2.189999942467025</v>
       </c>
       <c r="O30" t="n">
-        <v>27.31731288542093</v>
+        <v>27.29634875926489</v>
       </c>
     </row>
     <row r="31">
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>249.5299987792969</v>
+        <v>252.0299987792969</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2205,13 +2205,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>26.630737</v>
+        <v>26.86887</v>
       </c>
       <c r="H31" t="n">
-        <v>27.84933</v>
+        <v>28.128347</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2228,13 +2228,13 @@
         <v>31.11828468145695</v>
       </c>
       <c r="M31" t="n">
-        <v>9.369999999999999</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>8.960000071071615</v>
+        <v>8.9600003434008</v>
       </c>
       <c r="O31" t="n">
-        <v>32.18561064428849</v>
+        <v>32.1707923695234</v>
       </c>
     </row>
     <row r="32">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>24.15999984741211</v>
+        <v>23.89999961853027</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2262,13 +2262,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>408</v>
+        <v>413.9999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>8.358131</v>
+        <v>8.269895999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>8.783637000000001</v>
+        <v>8.690909</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         <v>2.89</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75056902367574</v>
+        <v>2.74999998487273</v>
       </c>
       <c r="O32" t="n">
-        <v>53.83176110693063</v>
+        <v>53.83562399023739</v>
       </c>
     </row>
     <row r="33">
@@ -2311,7 +2311,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>262.7900085449219</v>
+        <v>268.6400146484375</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2322,10 +2322,10 @@
         <v>127</v>
       </c>
       <c r="G33" t="n">
-        <v>28.564133</v>
+        <v>29.13666</v>
       </c>
       <c r="H33" t="n">
-        <v>32.523518</v>
+        <v>33.247528</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2342,13 +2342,13 @@
         <v>42.48169723729789</v>
       </c>
       <c r="M33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>8.079999480527349</v>
+        <v>8.079999651355658</v>
       </c>
       <c r="O33" t="n">
-        <v>42.28319898970346</v>
+        <v>42.01481172219495</v>
       </c>
     </row>
     <row r="34">
@@ -2368,7 +2368,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>43.22999954223633</v>
+        <v>43.11000061035156</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2376,13 +2376,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G34" t="n">
-        <v>16.437262</v>
+        <v>16.391634</v>
       </c>
       <c r="H34" t="n">
-        <v>16.437262</v>
+        <v>16.391634</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
         <v>2.63</v>
       </c>
       <c r="N34" t="n">
-        <v>2.630000029337996</v>
+        <v>2.630000194632919</v>
       </c>
       <c r="O34" t="n">
-        <v>19.0464707838143</v>
+        <v>19.04018944596649</v>
       </c>
     </row>
     <row r="35">
@@ -2425,7 +2425,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>52.02999877929688</v>
+        <v>51.56000137329102</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2948</v>
+        <v>2931</v>
       </c>
       <c r="G35" t="n">
-        <v>7.297335</v>
+        <v>7.2314167</v>
       </c>
       <c r="H35" t="n">
-        <v>8.818644000000001</v>
+        <v>8.738982999999999</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2459,10 +2459,10 @@
         <v>7.13</v>
       </c>
       <c r="N35" t="n">
-        <v>5.899999906935451</v>
+        <v>5.900000191474342</v>
       </c>
       <c r="O35" t="n">
-        <v>29.33651164626945</v>
+        <v>29.33413053198274</v>
       </c>
     </row>
     <row r="36">
@@ -2482,7 +2482,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>65.51000213623047</v>
+        <v>63.93999862670898</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2490,13 +2490,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>654</v>
+        <v>647</v>
       </c>
       <c r="G36" t="n">
-        <v>12.67118</v>
+        <v>12.367504</v>
       </c>
       <c r="H36" t="n">
-        <v>12.244861</v>
+        <v>11.951402</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2516,10 +2516,10 @@
         <v>5.17</v>
       </c>
       <c r="N36" t="n">
-        <v>5.349999655874449</v>
+        <v>5.349999826523197</v>
       </c>
       <c r="O36" t="n">
-        <v>19.33581076283902</v>
+        <v>19.4812678650334</v>
       </c>
     </row>
     <row r="37">
@@ -2539,7 +2539,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>16.05500030517578</v>
+        <v>16.21999931335449</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2547,13 +2547,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>432</v>
+        <v>436.0000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>9.122159</v>
+        <v>9.215909</v>
       </c>
       <c r="H37" t="n">
-        <v>17.079788</v>
+        <v>17.255318</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2573,10 +2573,10 @@
         <v>1.76</v>
       </c>
       <c r="N37" t="n">
-        <v>0.9399999757125662</v>
+        <v>0.9400000227961312</v>
       </c>
       <c r="O37" t="n">
-        <v>30.7863730194871</v>
+        <v>30.79454077711425</v>
       </c>
     </row>
     <row r="38">
@@ -2596,7 +2596,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>20.77000045776367</v>
+        <v>21.01000022888184</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2604,13 +2604,13 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G38" t="n">
-        <v>9.440909</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>19.780954</v>
+        <v>20.009525</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2630,10 +2630,10 @@
         <v>2.2</v>
       </c>
       <c r="N38" t="n">
-        <v>1.049999937200383</v>
+        <v>1.049999948968396</v>
       </c>
       <c r="O38" t="n">
-        <v>34.16470674439753</v>
+        <v>34.10097374356364</v>
       </c>
     </row>
     <row r="39">
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>16.61000061035156</v>
+        <v>16.71999931335449</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         <v>296</v>
       </c>
       <c r="G39" t="n">
-        <v>13.395162</v>
+        <v>13.4838705</v>
       </c>
       <c r="H39" t="n">
-        <v>40.512196</v>
+        <v>40.780487</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2687,10 +2687,10 @@
         <v>1.24</v>
       </c>
       <c r="N39" t="n">
-        <v>0.4100000061796591</v>
+        <v>0.4099999912545059</v>
       </c>
       <c r="O39" t="n">
-        <v>33.35813300506702</v>
+        <v>33.34281477989967</v>
       </c>
     </row>
     <row r="40">
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>15.72000026702881</v>
+        <v>15.69999980926514</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="n">
-        <v>155.1714376815827</v>
+        <v>155.1400388080655</v>
       </c>
     </row>
     <row r="42">
@@ -2846,7 +2846,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>3.799999952316284</v>
+        <v>3.730000019073486</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2859,10 +2859,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>0.10963647</v>
+        <v>0.10761685</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.6884058</v>
+        <v>-0.6757246</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2882,10 +2882,10 @@
         <v>34.66</v>
       </c>
       <c r="N42" t="n">
-        <v>-5.519999907491024</v>
+        <v>-5.520000336044427</v>
       </c>
       <c r="O42" t="n">
-        <v>123.7634489996687</v>
+        <v>122.7891339009234</v>
       </c>
     </row>
     <row r="43">
@@ -2905,7 +2905,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>18.30100059509277</v>
+        <v>18.35000038146973</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="n">
-        <v>11.26724307437371</v>
+        <v>11.27262764472069</v>
       </c>
     </row>
     <row r="44">
@@ -2974,7 +2974,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.242000102996826</v>
+        <v>6.238999843597412</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="n">
-        <v>2.550955770125057</v>
+        <v>2.546121982578514</v>
       </c>
     </row>
     <row r="45">
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6.35099983215332</v>
+        <v>6.355000019073486</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>2.585325521591403</v>
+        <v>2.585395565692625</v>
       </c>
     </row>
     <row r="46">
@@ -3108,7 +3108,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>78.52249908447266</v>
+        <v>77.83499908447266</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>292</v>
       </c>
       <c r="G46" t="n">
-        <v>16.066492</v>
+        <v>15.925823</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>13.33831749155971</v>
+        <v>13.33130425497159</v>
       </c>
     </row>
     <row r="47">
@@ -3173,7 +3173,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>54.52000045776367</v>
+        <v>54.27000045776367</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>270</v>
       </c>
       <c r="G47" t="n">
-        <v>16.93132</v>
+        <v>16.853682</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3218,7 +3218,7 @@
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="n">
-        <v>17.95406675732121</v>
+        <v>17.84992835573419</v>
       </c>
     </row>
     <row r="48">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>43.34999847412109</v>
+        <v>43.11999893188477</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
         <v>613</v>
       </c>
       <c r="G48" t="n">
-        <v>25.958084</v>
+        <v>25.82036</v>
       </c>
       <c r="H48" t="n">
-        <v>10.891959</v>
+        <v>10.83417</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3272,10 +3272,10 @@
         <v>1.67</v>
       </c>
       <c r="N48" t="n">
-        <v>3.980000151866261</v>
+        <v>3.980000215234279</v>
       </c>
       <c r="O48" t="n">
-        <v>46.32510420628786</v>
+        <v>46.30644117730371</v>
       </c>
     </row>
     <row r="49">
@@ -3295,7 +3295,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>659.1799926757812</v>
+        <v>662.260009765625</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         <v>111</v>
       </c>
       <c r="G49" t="n">
-        <v>27.843939</v>
+        <v>27.97404</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="n">
-        <v>19.56368891954483</v>
+        <v>19.49841889413724</v>
       </c>
     </row>
     <row r="50">
@@ -3360,7 +3360,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>51.88000106811523</v>
+        <v>52.93000030517578</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
-        <v>43.65107776659897</v>
+        <v>43.59455104643413</v>
       </c>
     </row>
     <row r="51">
@@ -3429,7 +3429,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>19.51779937744141</v>
+        <v>19.70310020446777</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="n">
-        <v>24.73200727911984</v>
+        <v>24.74558984769503</v>
       </c>
     </row>
     <row r="52">
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>146.97900390625</v>
+        <v>147.9049987792969</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="N52" t="inlineStr"/>
       <c r="O52" t="n">
-        <v>10.51303988917713</v>
+        <v>10.55407046701334</v>
       </c>
     </row>
     <row r="53">
@@ -3638,7 +3638,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>22.59749984741211</v>
+        <v>23</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3649,7 +3649,7 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>33.914364</v>
+        <v>34.518436</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="n">
-        <v>25.18932084671675</v>
+        <v>25.21446084981468</v>
       </c>
     </row>
     <row r="55">
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>74.58999633789062</v>
+        <v>74.40000152587891</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="n">
-        <v>4.993243305356508</v>
+        <v>5.000440855014763</v>
       </c>
     </row>
     <row r="56">
@@ -3841,7 +3841,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>399.3900146484375</v>
+        <v>401.0599975585938</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3852,10 +3852,10 @@
         <v>72</v>
       </c>
       <c r="G57" t="n">
-        <v>16.759968</v>
+        <v>16.851261</v>
       </c>
       <c r="H57" t="n">
-        <v>16.268433</v>
+        <v>16.336456</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3872,13 +3872,13 @@
         <v>8.213430251373973</v>
       </c>
       <c r="M57" t="n">
-        <v>23.83</v>
+        <v>23.8</v>
       </c>
       <c r="N57" t="n">
-        <v>24.54999904713856</v>
+        <v>24.55000016886121</v>
       </c>
       <c r="O57" t="n">
-        <v>28.47443983555831</v>
+        <v>28.46316380708747</v>
       </c>
     </row>
     <row r="58">
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>155.1600036621094</v>
+        <v>155.3999938964844</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G58" t="n">
-        <v>21.550001</v>
+        <v>21.583334</v>
       </c>
       <c r="H58" t="n">
-        <v>19.640507</v>
+        <v>19.670885</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3932,10 +3932,10 @@
         <v>7.2</v>
       </c>
       <c r="N58" t="n">
-        <v>7.8999999166065</v>
+        <v>7.900000121829007</v>
       </c>
       <c r="O58" t="n">
-        <v>29.1304656687993</v>
+        <v>29.12923261725295</v>
       </c>
     </row>
     <row r="59">
@@ -3955,7 +3955,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>168.3300018310547</v>
+        <v>176.9700012207031</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3968,10 +3968,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>543</v>
+        <v>589.89996</v>
       </c>
       <c r="H59" t="n">
-        <v>358.14893</v>
+        <v>376.53192</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3988,13 +3988,13 @@
         <v>22.18493618168078</v>
       </c>
       <c r="M59" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="N59" t="n">
-        <v>0.4700000132097412</v>
+        <v>0.4699999968680029</v>
       </c>
       <c r="O59" t="n">
-        <v>71.46859099965052</v>
+        <v>71.60482855405809</v>
       </c>
     </row>
     <row r="60">
@@ -4014,7 +4014,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>82.87999725341797</v>
+        <v>85.37000274658203</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -4027,10 +4027,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>18.751131</v>
+        <v>19.31448</v>
       </c>
       <c r="H60" t="n">
-        <v>11.873925</v>
+        <v>12.2306595</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4050,10 +4050,10 @@
         <v>4.42</v>
       </c>
       <c r="N60" t="n">
-        <v>6.980000063451468</v>
+        <v>6.979999953933967</v>
       </c>
       <c r="O60" t="n">
-        <v>39.37491400801107</v>
+        <v>39.46724159365311</v>
       </c>
     </row>
     <row r="61">
@@ -4073,7 +4073,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>44.68999862670898</v>
+        <v>43.83000183105469</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -4081,13 +4081,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G61" t="n">
-        <v>18.466942</v>
+        <v>18.11157</v>
       </c>
       <c r="H61" t="n">
-        <v>17.321705</v>
+        <v>16.988373</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4107,10 +4107,10 @@
         <v>2.42</v>
       </c>
       <c r="N61" t="n">
-        <v>2.579999984222626</v>
+        <v>2.579999970041551</v>
       </c>
       <c r="O61" t="n">
-        <v>40.74083054372721</v>
+        <v>40.76072528750323</v>
       </c>
     </row>
     <row r="62">
@@ -4130,7 +4130,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>15.09000015258789</v>
+        <v>14.89999961853027</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -4138,13 +4138,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G62" t="n">
-        <v>13.972221</v>
+        <v>13.796295</v>
       </c>
       <c r="H62" t="n">
-        <v>10.195946</v>
+        <v>10.067567</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4164,10 +4164,10 @@
         <v>1.08</v>
       </c>
       <c r="N62" t="n">
-        <v>1.48000000711929</v>
+        <v>1.480000045545292</v>
       </c>
       <c r="O62" t="n">
-        <v>30.11513334973534</v>
+        <v>30.13326794084924</v>
       </c>
     </row>
     <row r="63">
@@ -4187,7 +4187,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>25.34000015258789</v>
+        <v>24.09000015258789</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4203,7 +4203,7 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>13.129534</v>
+        <v>12.481866</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -4223,10 +4223,10 @@
         <v>-5.06</v>
       </c>
       <c r="N63" t="n">
-        <v>1.929999964399947</v>
+        <v>1.929999901664374</v>
       </c>
       <c r="O63" t="n">
-        <v>72.16652700148759</v>
+        <v>72.31308291683214</v>
       </c>
     </row>
     <row r="64">
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.31999969482422</v>
+        <v>11.77000045776367</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -4335,7 +4335,7 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>4.2629757</v>
+        <v>4.0726643</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -4355,10 +4355,10 @@
         <v>-0.44</v>
       </c>
       <c r="N65" t="n">
-        <v>2.889999981661687</v>
+        <v>2.890000154877404</v>
       </c>
       <c r="O65" t="n">
-        <v>84.02787568831472</v>
+        <v>84.12308983123386</v>
       </c>
     </row>
     <row r="66">
@@ -4378,7 +4378,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>101.7600021362305</v>
+        <v>102.4100036621094</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -4386,13 +4386,13 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G66" t="n">
-        <v>15.031019</v>
+        <v>15.127031</v>
       </c>
       <c r="H66" t="n">
-        <v>14.15299</v>
+        <v>14.243394</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -4412,10 +4412,10 @@
         <v>6.77</v>
       </c>
       <c r="N66" t="n">
-        <v>7.190000285185707</v>
+        <v>7.190000056314483</v>
       </c>
       <c r="O66" t="n">
-        <v>33.0170559462393</v>
+        <v>32.63710014620076</v>
       </c>
     </row>
     <row r="67">
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>278.2900085449219</v>
+        <v>261.9100036621094</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="G67" t="n">
-        <v>12.672587</v>
+        <v>11.943001</v>
       </c>
       <c r="H67" t="n">
-        <v>13.456964</v>
+        <v>12.664893</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4466,13 +4466,13 @@
         <v>31.66420631970241</v>
       </c>
       <c r="M67" t="n">
-        <v>21.96</v>
+        <v>21.93</v>
       </c>
       <c r="N67" t="n">
-        <v>20.6799994816752</v>
+        <v>20.68000129666389</v>
       </c>
       <c r="O67" t="n">
-        <v>22.58063500738485</v>
+        <v>23.39634073161628</v>
       </c>
     </row>
     <row r="68">
@@ -4492,7 +4492,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>320.5599975585938</v>
+        <v>343.1300048828125</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -4505,10 +4505,10 @@
         </is>
       </c>
       <c r="G68" t="n">
-        <v>30.852741</v>
+        <v>33.025024</v>
       </c>
       <c r="H68" t="n">
-        <v>89.79272</v>
+        <v>96.11485</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4528,10 +4528,10 @@
         <v>10.39</v>
       </c>
       <c r="N68" t="n">
-        <v>3.569999856988336</v>
+        <v>3.56999989994067</v>
       </c>
       <c r="O68" t="n">
-        <v>85.60418427121573</v>
+        <v>85.80983966530586</v>
       </c>
     </row>
     <row r="69">
@@ -4551,7 +4551,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>49.18000030517578</v>
+        <v>49.84999847412109</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -4559,13 +4559,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="G69" t="n">
-        <v>11.995122</v>
+        <v>9.423439999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>10.46383</v>
+        <v>10.606383</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4573,22 +4573,22 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>20.035</v>
+        <v>19.627</v>
       </c>
       <c r="K69" t="n">
-        <v>2284699904</v>
+        <v>2908999936</v>
       </c>
       <c r="L69" t="n">
-        <v>11.72446707762034</v>
+        <v>15.1858416129293</v>
       </c>
       <c r="M69" t="n">
-        <v>4.1</v>
+        <v>5.29</v>
       </c>
       <c r="N69" t="n">
-        <v>4.699999933597525</v>
+        <v>4.699999846707506</v>
       </c>
       <c r="O69" t="n">
-        <v>21.87823812534869</v>
+        <v>21.9306329041664</v>
       </c>
     </row>
     <row r="70">
@@ -4608,7 +4608,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>37.79000091552734</v>
+        <v>37.9900016784668</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
       </c>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
-        <v>26.23708103558965</v>
+        <v>26.06745164119132</v>
       </c>
     </row>
     <row r="71">
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>19.01000022888184</v>
+        <v>19.1200008392334</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -4683,13 +4683,13 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="G71" t="n">
-        <v>9.228156</v>
+        <v>9.236715</v>
       </c>
       <c r="H71" t="n">
-        <v>11.88125</v>
+        <v>11.950001</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4706,13 +4706,13 @@
         <v>32.24973681206355</v>
       </c>
       <c r="M71" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="N71" t="n">
-        <v>1.600000019264121</v>
+        <v>1.599999936337528</v>
       </c>
       <c r="O71" t="n">
-        <v>33.11103954552237</v>
+        <v>32.9223572390386</v>
       </c>
     </row>
     <row r="72">
@@ -4732,7 +4732,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>8.890000343322754</v>
+        <v>8.310000419616699</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -4740,13 +4740,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="G72" t="n">
-        <v>9.260417</v>
+        <v>8.656250999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>6.5851855</v>
+        <v>6.1555557</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4766,10 +4766,10 @@
         <v>0.96</v>
       </c>
       <c r="N72" t="n">
-        <v>1.349999987596819</v>
+        <v>1.350000036490077</v>
       </c>
       <c r="O72" t="n">
-        <v>66.6950819914433</v>
+        <v>66.96679247442412</v>
       </c>
     </row>
     <row r="73">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>87.80000305175781</v>
+        <v>89.58999633789062</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
-        <v>43.46227969834302</v>
+        <v>43.43016497156809</v>
       </c>
     </row>
     <row r="74">
@@ -4858,7 +4858,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>61.18999862670898</v>
+        <v>61.38000106811523</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -4866,13 +4866,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>624</v>
+        <v>633</v>
       </c>
       <c r="G74" t="n">
-        <v>11.085145</v>
+        <v>11.119565</v>
       </c>
       <c r="H74" t="n">
-        <v>7.526445</v>
+        <v>7.5498157</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4892,10 +4892,10 @@
         <v>5.52</v>
       </c>
       <c r="N74" t="n">
-        <v>8.130000103197323</v>
+        <v>8.129999924119371</v>
       </c>
       <c r="O74" t="n">
-        <v>23.30652834536934</v>
+        <v>23.2509329693794</v>
       </c>
     </row>
     <row r="75">
@@ -4915,7 +4915,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>24.68000030517578</v>
+        <v>24.56999969482422</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -4923,13 +4923,13 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G75" t="n">
-        <v>8.172186</v>
+        <v>8.135761</v>
       </c>
       <c r="H75" t="n">
-        <v>8.599303000000001</v>
+        <v>8.560976</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4949,10 +4949,10 @@
         <v>3.02</v>
       </c>
       <c r="N75" t="n">
-        <v>2.870000080840945</v>
+        <v>2.869999833526483</v>
       </c>
       <c r="O75" t="n">
-        <v>32.97063706452909</v>
+        <v>32.95646340049621</v>
       </c>
     </row>
     <row r="76">
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>25113</v>
+        <v>24985</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
-        <v>15.66360662571528</v>
+        <v>15.67566973818042</v>
       </c>
     </row>
   </sheetData>

--- a/Stock Selection/tickers_used.xlsx
+++ b/Stock Selection/tickers_used.xlsx
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.25</v>
+        <v>27.68000030517578</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>-5.6420455</v>
+        <v>-5.596159</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -557,13 +557,13 @@
         <v>-764.0130895091434</v>
       </c>
       <c r="M2" t="n">
-        <v>-7.12</v>
+        <v>-6.99</v>
       </c>
       <c r="N2" t="n">
-        <v>-5.184289988444793</v>
+        <v>-4.946249794756686</v>
       </c>
       <c r="O2" t="n">
-        <v>70.59404465080874</v>
+        <v>70.36452720384661</v>
       </c>
     </row>
     <row r="3">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>148.6999969482422</v>
+        <v>163.1600036621094</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -596,10 +596,10 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>94.11391999999999</v>
+        <v>87.72042999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>37.21063</v>
+        <v>41.029613</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -616,13 +616,13 @@
         <v>12.95699241359188</v>
       </c>
       <c r="M3" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="N3" t="n">
-        <v>3.996169829649274</v>
+        <v>3.976640083398042</v>
       </c>
       <c r="O3" t="n">
-        <v>36.13526280668989</v>
+        <v>36.55402793250116</v>
       </c>
     </row>
     <row r="4">
@@ -642,7 +642,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>51.59999847412109</v>
+        <v>53.20000076293945</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -655,10 +655,10 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>132.3077</v>
+        <v>136.41026</v>
       </c>
       <c r="H4" t="n">
-        <v>13.5967655</v>
+        <v>13.934508</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14.761</v>
+        <v>14.919</v>
       </c>
       <c r="K4" t="n">
         <v>62804000</v>
@@ -678,10 +678,10 @@
         <v>0.39</v>
       </c>
       <c r="N4" t="n">
-        <v>3.795020107842641</v>
+        <v>3.817860003592481</v>
       </c>
       <c r="O4" t="n">
-        <v>43.05151426484986</v>
+        <v>42.29373878869562</v>
       </c>
     </row>
     <row r="5">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>241.8800048828125</v>
+        <v>191.8000030517578</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>18.54908</v>
+        <v>13.888487</v>
       </c>
       <c r="H5" t="n">
-        <v>10.424856</v>
+        <v>7.53254</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>39.970002</v>
+        <v>40.734002</v>
       </c>
       <c r="K5" t="n">
-        <v>1400461952</v>
+        <v>1528228992</v>
       </c>
       <c r="L5" t="n">
-        <v>27.72848796624502</v>
+        <v>29.2799168812844</v>
       </c>
       <c r="M5" t="n">
-        <v>13.04</v>
+        <v>13.81</v>
       </c>
       <c r="N5" t="n">
-        <v>23.20223942496784</v>
+        <v>25.46285888315997</v>
       </c>
       <c r="O5" t="n">
-        <v>64.08489078848542</v>
+        <v>64.15205636759323</v>
       </c>
     </row>
     <row r="6">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>38.5099983215332</v>
+        <v>35.97999954223633</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>11.378778</v>
+        <v>6.726139</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>23.020001</v>
+        <v>22.488001</v>
       </c>
       <c r="K6" t="n">
-        <v>-523917000704</v>
+        <v>-826000000</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.440746953402847</v>
+        <v>-4.477450378626907</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.18</v>
+        <v>-1.21</v>
       </c>
       <c r="N6" t="n">
-        <v>3.384370300706561</v>
+        <v>5.349279808555298</v>
       </c>
       <c r="O6" t="n">
-        <v>58.88609256164607</v>
+        <v>58.81433911720559</v>
       </c>
     </row>
     <row r="7">
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.09000015258789</v>
+        <v>23.75</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>141.2462221282146</v>
+        <v>140.6988447621899</v>
       </c>
     </row>
     <row r="8">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.609999895095825</v>
+        <v>2.309999942779541</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.07530294</v>
+        <v>0.06564365</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.47282606</v>
+        <v>-0.41847825</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -923,13 +923,13 @@
         <v>-346.4997018377226</v>
       </c>
       <c r="M8" t="n">
-        <v>34.66</v>
+        <v>35.19</v>
       </c>
       <c r="N8" t="n">
-        <v>-5.520000092837153</v>
+        <v>-5.520000006642021</v>
       </c>
       <c r="O8" t="n">
-        <v>95.20802218634955</v>
+        <v>92.99814081721834</v>
       </c>
     </row>
     <row r="9">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.16200065612793</v>
+        <v>17.67140007019043</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>8.579329734960631</v>
+        <v>8.812671882330616</v>
       </c>
     </row>
     <row r="10">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>30.27799987792969</v>
+        <v>32.55599975585938</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>42.2994361812405</v>
+        <v>41.14878026553125</v>
       </c>
     </row>
     <row r="11">
@@ -1087,7 +1087,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>27.82699966430664</v>
+        <v>26.57250022888184</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>28.39112417340644</v>
+        <v>29.04924302959466</v>
       </c>
     </row>
     <row r="12">
@@ -1156,7 +1156,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>155.1600036621094</v>
+        <v>157.5160064697266</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>9.959782764391424</v>
+        <v>9.845020278283462</v>
       </c>
     </row>
     <row r="13">
@@ -1225,7 +1225,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>135.2400054931641</v>
+        <v>152.6699981689453</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -1238,10 +1238,10 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>211.31252</v>
+        <v>242.33333</v>
       </c>
       <c r="H13" t="n">
-        <v>73.99585999999999</v>
+        <v>82.60783000000001</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1258,13 +1258,13 @@
         <v>36.3099688197316</v>
       </c>
       <c r="M13" t="n">
-        <v>0.64</v>
+        <v>0.63</v>
       </c>
       <c r="N13" t="n">
-        <v>1.827669892520529</v>
+        <v>1.848129870606035</v>
       </c>
       <c r="O13" t="n">
-        <v>61.78781477163975</v>
+        <v>59.73190552490613</v>
       </c>
     </row>
     <row r="14">
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>79.56999969482422</v>
+        <v>72.20999908447266</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>106.09333</v>
+        <v>97.58108</v>
       </c>
       <c r="H14" t="n">
-        <v>8.412414999999999</v>
+        <v>7.6338296</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1317,13 +1317,13 @@
         <v>0.8089028285351719</v>
       </c>
       <c r="M14" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="N14" t="n">
-        <v>9.45863936750912</v>
+        <v>9.459210234987777</v>
       </c>
       <c r="O14" t="n">
-        <v>37.86743356967614</v>
+        <v>38.26831446901861</v>
       </c>
     </row>
     <row r="15">
@@ -1343,7 +1343,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20.04999923706055</v>
+        <v>16.63999938964844</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>-23.36258</v>
+        <v>-19.389193</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         <v>-0.19</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8582099766832493</v>
+        <v>-0.8582100033584914</v>
       </c>
       <c r="O15" t="n">
-        <v>95.92145901757243</v>
+        <v>95.93408719469861</v>
       </c>
     </row>
     <row r="16">
@@ -1404,7 +1404,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>171.3500061035156</v>
+        <v>205.7100067138672</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>38.419285</v>
+        <v>46.33108</v>
       </c>
       <c r="H16" t="n">
-        <v>27.879423</v>
+        <v>34.468834</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1437,13 +1437,13 @@
         <v>18.30955730773422</v>
       </c>
       <c r="M16" t="n">
-        <v>4.46</v>
+        <v>4.44</v>
       </c>
       <c r="N16" t="n">
-        <v>6.146110201187293</v>
+        <v>5.968000156717433</v>
       </c>
       <c r="O16" t="n">
-        <v>75.16681718303221</v>
+        <v>77.43564003918426</v>
       </c>
     </row>
     <row r="17">
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>51.09000015258789</v>
+        <v>54.77999877929688</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="n">
-        <v>42.40436248482072</v>
+        <v>41.33186903664492</v>
       </c>
     </row>
     <row r="18">
@@ -1532,7 +1532,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>34800.5</v>
+        <v>35321</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>21.28533389781008</v>
+        <v>21.81721187709065</v>
       </c>
     </row>
     <row r="19">
@@ -1600,18 +1600,18 @@
           <t>IAPD.AS</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>23.46999931335449</v>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Error: single positional indexer is out-of-bounds</t>
+        </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="F19" t="n">
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1648,9 +1648,15 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="n">
-        <v>12.98623063367854</v>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1670,7 +1676,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>79.55999755859375</v>
+        <v>65.11000061035156</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1678,13 +1684,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>779</v>
+        <v>925</v>
       </c>
       <c r="G20" t="n">
-        <v>9.574006000000001</v>
+        <v>8.906976999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>10.025151</v>
+        <v>7.680131</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1705,13 +1711,13 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>8.31</v>
+        <v>7.31</v>
       </c>
       <c r="N20" t="n">
-        <v>7.936039822102805</v>
+        <v>8.477720055862532</v>
       </c>
       <c r="O20" t="n">
-        <v>31.95599597606035</v>
+        <v>33.30170864823912</v>
       </c>
     </row>
     <row r="21">
@@ -1731,7 +1737,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16.70999908447266</v>
+        <v>15.42000007629395</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1739,13 +1745,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>747</v>
+        <v>777</v>
       </c>
       <c r="G21" t="n">
-        <v>30.381815</v>
+        <v>29.094341</v>
       </c>
       <c r="H21" t="n">
-        <v>7.776795</v>
+        <v>7.178437</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1753,22 +1759,22 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>35.143003</v>
+        <v>35.986</v>
       </c>
       <c r="K21" t="n">
-        <v>30185000960</v>
+        <v>13813999616</v>
       </c>
       <c r="L21" t="n">
-        <v>14.15010307203829</v>
+        <v>6.467379773447542</v>
       </c>
       <c r="M21" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="N21" t="n">
-        <v>2.148699957305376</v>
+        <v>2.148099938230836</v>
       </c>
       <c r="O21" t="n">
-        <v>31.33768258465192</v>
+        <v>31.68006418254064</v>
       </c>
     </row>
     <row r="22">
@@ -1788,7 +1794,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>67.56999969482422</v>
+        <v>66.98000335693359</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1796,13 +1802,13 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="G22" t="n">
-        <v>16.400486</v>
+        <v>16.257282</v>
       </c>
       <c r="H22" t="n">
-        <v>11.633813</v>
+        <v>11.519557</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1810,22 +1816,22 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>62.106997</v>
+        <v>62.47600300000001</v>
       </c>
       <c r="K22" t="n">
-        <v>6946999808</v>
+        <v>6927000064</v>
       </c>
       <c r="L22" t="n">
-        <v>34.49525733269226</v>
+        <v>34.39594880599941</v>
       </c>
       <c r="M22" t="n">
         <v>4.12</v>
       </c>
       <c r="N22" t="n">
-        <v>5.808069950481774</v>
+        <v>5.814459996763208</v>
       </c>
       <c r="O22" t="n">
-        <v>21.37021990845621</v>
+        <v>21.09740159101063</v>
       </c>
     </row>
     <row r="23">
@@ -1845,7 +1851,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>77.87999725341797</v>
+        <v>77.02999877929688</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1853,13 +1859,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>501.9999999999999</v>
+        <v>508</v>
       </c>
       <c r="G23" t="n">
-        <v>13.474048</v>
+        <v>13.326989</v>
       </c>
       <c r="H23" t="n">
-        <v>10.773855</v>
+        <v>10.664706</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1879,10 +1885,10 @@
         <v>5.78</v>
       </c>
       <c r="N23" t="n">
-        <v>7.228610117123162</v>
+        <v>7.222890043035117</v>
       </c>
       <c r="O23" t="n">
-        <v>23.67967859488886</v>
+        <v>24.06064046157138</v>
       </c>
     </row>
     <row r="24">
@@ -1902,7 +1908,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28.81999969482422</v>
+        <v>31.76000022888184</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1910,13 +1916,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>541</v>
+        <v>494.0000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>14.85567</v>
+        <v>16.28718</v>
       </c>
       <c r="H24" t="n">
-        <v>10.19816</v>
+        <v>11.2385</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1933,13 +1939,13 @@
         <v>4.765279340249381</v>
       </c>
       <c r="M24" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="N24" t="n">
-        <v>2.825999954386303</v>
+        <v>2.825999931386024</v>
       </c>
       <c r="O24" t="n">
-        <v>31.23239004777362</v>
+        <v>32.00016770688306</v>
       </c>
     </row>
     <row r="25">
@@ -1959,7 +1965,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>71.86000061035156</v>
+        <v>70.62000274658203</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1977,7 +1983,7 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>17.882296</v>
+        <v>13.195462</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1985,22 +1991,22 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>29.843</v>
+        <v>32.279</v>
       </c>
       <c r="K25" t="n">
-        <v>524497984</v>
+        <v>588137984</v>
       </c>
       <c r="L25" t="n">
-        <v>12.12400596915581</v>
+        <v>12.85203589463252</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.84</v>
+        <v>-1.8</v>
       </c>
       <c r="N25" t="n">
-        <v>4.018499671985721</v>
+        <v>5.351840105831992</v>
       </c>
       <c r="O25" t="n">
-        <v>49.71231236032548</v>
+        <v>50.52340580548695</v>
       </c>
     </row>
     <row r="26">
@@ -2020,7 +2026,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>26.43000030517578</v>
+        <v>23.79999923706055</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2028,7 +2034,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>492</v>
+        <v>539</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2036,7 +2042,7 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>13.694301</v>
+        <v>12.331606</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -2053,13 +2059,13 @@
         <v>-4.985057763658522</v>
       </c>
       <c r="M26" t="n">
-        <v>-9.52</v>
+        <v>-9.4</v>
       </c>
       <c r="N26" t="n">
-        <v>1.929999954373413</v>
+        <v>1.929999972190203</v>
       </c>
       <c r="O26" t="n">
-        <v>61.15248191603343</v>
+        <v>60.74446077455457</v>
       </c>
     </row>
     <row r="27">
@@ -2079,7 +2085,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>49.88000106811523</v>
+        <v>48.43999862670898</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2087,13 +2093,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="G27" t="n">
-        <v>8.163665999999999</v>
+        <v>7.9279866</v>
       </c>
       <c r="H27" t="n">
-        <v>7.095306</v>
+        <v>6.890469</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2113,10 +2119,10 @@
         <v>6.11</v>
       </c>
       <c r="N27" t="n">
-        <v>7.029999984231157</v>
+        <v>7.030000225922064</v>
       </c>
       <c r="O27" t="n">
-        <v>27.0019676961784</v>
+        <v>24.53960840747772</v>
       </c>
     </row>
     <row r="28">
@@ -2136,7 +2142,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>97.08999633789062</v>
+        <v>93.37000274658203</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2144,13 +2150,13 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>413.9999999999999</v>
+        <v>418</v>
       </c>
       <c r="G28" t="n">
-        <v>15.46019</v>
+        <v>15.825424</v>
       </c>
       <c r="H28" t="n">
-        <v>11.069887</v>
+        <v>10.346669</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2167,13 +2173,13 @@
         <v>17.29067693440566</v>
       </c>
       <c r="M28" t="n">
-        <v>6.28</v>
+        <v>5.9</v>
       </c>
       <c r="N28" t="n">
-        <v>8.770640236697144</v>
+        <v>9.024160601501993</v>
       </c>
       <c r="O28" t="n">
-        <v>26.6972151488009</v>
+        <v>27.17395293175811</v>
       </c>
     </row>
     <row r="29">
@@ -2193,7 +2199,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>44.61999893188477</v>
+        <v>43.56999969482422</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2201,13 +2207,13 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>547</v>
+        <v>560</v>
       </c>
       <c r="G29" t="n">
-        <v>9.595698000000001</v>
+        <v>9.369892</v>
       </c>
       <c r="H29" t="n">
-        <v>12.6513</v>
+        <v>12.516051</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2227,10 +2233,10 @@
         <v>4.65</v>
       </c>
       <c r="N29" t="n">
-        <v>3.526910193567836</v>
+        <v>3.481129926270213</v>
       </c>
       <c r="O29" t="n">
-        <v>24.47509169020723</v>
+        <v>24.14787216305325</v>
       </c>
     </row>
     <row r="30">
@@ -2250,7 +2256,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>29.79999923706055</v>
+        <v>26.85000038146973</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2258,13 +2264,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>430.9999999999999</v>
+        <v>471</v>
       </c>
       <c r="G30" t="n">
-        <v>11.825397</v>
+        <v>11.095041</v>
       </c>
       <c r="H30" t="n">
-        <v>9.786759999999999</v>
+        <v>8.817937000000001</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2275,19 +2281,19 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>6327000064</v>
+        <v>8323999744</v>
       </c>
       <c r="L30" t="n">
-        <v>29.11642799409482</v>
+        <v>34.03246170874658</v>
       </c>
       <c r="M30" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="N30" t="n">
-        <v>3.044930011266298</v>
+        <v>3.044929940128822</v>
       </c>
       <c r="O30" t="n">
-        <v>27.97926687611319</v>
+        <v>27.89100659114464</v>
       </c>
     </row>
     <row r="31">
@@ -2307,7 +2313,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>29.05999946594238</v>
+        <v>32.38000106811523</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2315,13 +2321,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="G31" t="n">
-        <v>6.952153</v>
+        <v>7.4436784</v>
       </c>
       <c r="H31" t="n">
-        <v>13.486546</v>
+        <v>13.135957</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2329,22 +2335,22 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>62.19100400000001</v>
+        <v>59.252</v>
       </c>
       <c r="K31" t="n">
-        <v>1508999936</v>
+        <v>1434000000</v>
       </c>
       <c r="L31" t="n">
-        <v>16.09428259385665</v>
+        <v>16.51122686051728</v>
       </c>
       <c r="M31" t="n">
-        <v>4.18</v>
+        <v>4.35</v>
       </c>
       <c r="N31" t="n">
-        <v>2.154739950906806</v>
+        <v>2.464989879923879</v>
       </c>
       <c r="O31" t="n">
-        <v>55.05998091416151</v>
+        <v>54.44673905205934</v>
       </c>
     </row>
     <row r="32">
@@ -2364,7 +2370,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>19.85499954223633</v>
+        <v>18.54999923706055</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -2372,13 +2378,13 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>463</v>
+        <v>488</v>
       </c>
       <c r="G32" t="n">
-        <v>11.28125</v>
+        <v>10.539772</v>
       </c>
       <c r="H32" t="n">
-        <v>8.992706999999999</v>
+        <v>8.405379</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2398,10 +2404,10 @@
         <v>1.76</v>
       </c>
       <c r="N32" t="n">
-        <v>2.207900195373465</v>
+        <v>2.206920025505161</v>
       </c>
       <c r="O32" t="n">
-        <v>30.96456995544901</v>
+        <v>31.12496858406112</v>
       </c>
     </row>
     <row r="33">
@@ -2421,7 +2427,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>350.25</v>
+        <v>334.1799926757812</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2429,13 +2435,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="G33" t="n">
-        <v>14.747369</v>
+        <v>13.3672</v>
       </c>
       <c r="H33" t="n">
-        <v>11.138918</v>
+        <v>10.387271</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2449,16 +2455,16 @@
         <v>6925377024</v>
       </c>
       <c r="L33" t="n">
-        <v>33.07984665338594</v>
+        <v>33.45617549293598</v>
       </c>
       <c r="M33" t="n">
-        <v>23.75</v>
+        <v>25</v>
       </c>
       <c r="N33" t="n">
-        <v>31.44380809698033</v>
+        <v>32.17206835903109</v>
       </c>
       <c r="O33" t="n">
-        <v>24.23063859490438</v>
+        <v>25.34666552819715</v>
       </c>
     </row>
     <row r="34">
@@ -2478,7 +2484,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>23.51000022888184</v>
+        <v>21.53000068664551</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2486,13 +2492,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>352</v>
+        <v>488.9999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>11.248804</v>
+        <v>10.765</v>
       </c>
       <c r="H34" t="n">
-        <v>11.308321</v>
+        <v>10.416062</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2509,13 +2515,13 @@
         <v>31.95778523761375</v>
       </c>
       <c r="M34" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
-        <v>2.079000076924049</v>
+        <v>2.067000051136937</v>
       </c>
       <c r="O34" t="n">
-        <v>32.99189189474258</v>
+        <v>33.92425177440695</v>
       </c>
     </row>
     <row r="35">
@@ -2535,7 +2541,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>109.0199966430664</v>
+        <v>104.9100036621094</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2543,13 +2549,13 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>470</v>
+        <v>488.9999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>22.432098</v>
+        <v>21.542095</v>
       </c>
       <c r="H35" t="n">
-        <v>14.175673</v>
+        <v>13.602788</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2566,13 +2572,13 @@
         <v>9.855900651513558</v>
       </c>
       <c r="M35" t="n">
-        <v>4.86</v>
+        <v>4.87</v>
       </c>
       <c r="N35" t="n">
-        <v>7.690639918335194</v>
+        <v>7.712389817595435</v>
       </c>
       <c r="O35" t="n">
-        <v>24.69850443239818</v>
+        <v>25.12906253855759</v>
       </c>
     </row>
     <row r="36">
@@ -2592,7 +2598,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>76.81999969482422</v>
+        <v>75.59999847412109</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -2600,13 +2606,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="G36" t="n">
-        <v>21.639437</v>
+        <v>18.759304</v>
       </c>
       <c r="H36" t="n">
-        <v>16.208803</v>
+        <v>14.543328</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2623,13 +2629,13 @@
         <v>18.97273536447026</v>
       </c>
       <c r="M36" t="n">
-        <v>3.55</v>
+        <v>4.03</v>
       </c>
       <c r="N36" t="n">
-        <v>4.739399923290092</v>
+        <v>5.198259880690382</v>
       </c>
       <c r="O36" t="n">
-        <v>30.43719185421022</v>
+        <v>31.11624509954891</v>
       </c>
     </row>
     <row r="37">
@@ -2649,7 +2655,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>33.66999816894531</v>
+        <v>35.7599983215332</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -2657,13 +2663,13 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="G37" t="n">
-        <v>13.3083</v>
+        <v>13.860465</v>
       </c>
       <c r="H37" t="n">
-        <v>10.859618</v>
+        <v>11.5405445</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2680,13 +2686,13 @@
         <v>6.683752542830076</v>
       </c>
       <c r="M37" t="n">
-        <v>2.53</v>
+        <v>2.58</v>
       </c>
       <c r="N37" t="n">
-        <v>3.100477214663105</v>
+        <v>3.098640477625055</v>
       </c>
       <c r="O37" t="n">
-        <v>21.77670582172541</v>
+        <v>21.52208714806119</v>
       </c>
     </row>
     <row r="38">
@@ -2706,7 +2712,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>74.80999755859375</v>
+        <v>74.33999633789062</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2714,7 +2720,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2753,7 +2759,7 @@
       </c>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="n">
-        <v>4.220575757890895</v>
+        <v>4.182491436690196</v>
       </c>
     </row>
     <row r="39">
@@ -2773,7 +2779,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>164.9400024414062</v>
+        <v>160.6999969482422</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2781,13 +2787,13 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="G39" t="n">
-        <v>27.49</v>
+        <v>27.329931</v>
       </c>
       <c r="H39" t="n">
-        <v>18.067163</v>
+        <v>17.59769</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2804,13 +2810,13 @@
         <v>8.772957224371577</v>
       </c>
       <c r="M39" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="N39" t="n">
-        <v>9.129269628076431</v>
+        <v>9.131880204063272</v>
       </c>
       <c r="O39" t="n">
-        <v>22.74489529417205</v>
+        <v>22.69928464996319</v>
       </c>
     </row>
     <row r="40">
@@ -2830,7 +2836,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>47.79000091552734</v>
+        <v>48.77000045776367</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -2838,13 +2844,13 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="G40" t="n">
-        <v>17.505495</v>
+        <v>18.062963</v>
       </c>
       <c r="H40" t="n">
-        <v>15.7423</v>
+        <v>16.051422</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2861,13 +2867,13 @@
         <v>11.41066822392783</v>
       </c>
       <c r="M40" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="N40" t="n">
-        <v>3.035769926600773</v>
+        <v>3.038360118982834</v>
       </c>
       <c r="O40" t="n">
-        <v>19.33058887669577</v>
+        <v>19.16777523218412</v>
       </c>
     </row>
     <row r="41">
@@ -2887,7 +2893,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>126.7799987792969</v>
+        <v>131.6100006103516</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -2895,13 +2901,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="G41" t="n">
-        <v>20.091917</v>
+        <v>20.923689</v>
       </c>
       <c r="H41" t="n">
-        <v>17.710192</v>
+        <v>18.384907</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2909,22 +2915,22 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>46.223</v>
+        <v>51.214004</v>
       </c>
       <c r="K41" t="n">
-        <v>4911000064</v>
+        <v>4904999936</v>
       </c>
       <c r="L41" t="n">
-        <v>15.23404769907964</v>
+        <v>15.42938004482665</v>
       </c>
       <c r="M41" t="n">
-        <v>6.31</v>
+        <v>6.29</v>
       </c>
       <c r="N41" t="n">
-        <v>7.158589741957449</v>
+        <v>7.158589413063203</v>
       </c>
       <c r="O41" t="n">
-        <v>16.47982795858777</v>
+        <v>16.2520361262849</v>
       </c>
     </row>
     <row r="42">
@@ -2944,7 +2950,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>129.3699951171875</v>
+        <v>132.0399932861328</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -2952,13 +2958,13 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="G42" t="n">
-        <v>19.424925</v>
+        <v>20.036417</v>
       </c>
       <c r="H42" t="n">
-        <v>18.965788</v>
+        <v>19.250423</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,13 +2981,13 @@
         <v>16.36496559845065</v>
       </c>
       <c r="M42" t="n">
-        <v>6.66</v>
+        <v>6.59</v>
       </c>
       <c r="N42" t="n">
-        <v>6.8212296329152</v>
+        <v>6.859069709072513</v>
       </c>
       <c r="O42" t="n">
-        <v>19.16097964609009</v>
+        <v>18.93133572149846</v>
       </c>
     </row>
     <row r="43">
@@ -3001,7 +3007,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>23.3799991607666</v>
+        <v>20.29999923706055</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -3009,13 +3015,13 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="G43" t="n">
-        <v>15.904761</v>
+        <v>14.604316</v>
       </c>
       <c r="H43" t="n">
-        <v>57.024387</v>
+        <v>49.512196</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3032,13 +3038,13 @@
         <v>19.87709011258726</v>
       </c>
       <c r="M43" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="N43" t="n">
-        <v>0.4100000086062583</v>
+        <v>0.4099999773199425</v>
       </c>
       <c r="O43" t="n">
-        <v>31.78805194408695</v>
+        <v>32.57791205451376</v>
       </c>
     </row>
     <row r="44">
@@ -3058,7 +3064,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>17.89999961853027</v>
+        <v>17.29999923706055</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -3066,13 +3072,13 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="G44" t="n">
-        <v>11.623377</v>
+        <v>11.233766</v>
       </c>
       <c r="H44" t="n">
-        <v>7.784199</v>
+        <v>7.523276</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3092,10 +3098,10 @@
         <v>1.54</v>
       </c>
       <c r="N44" t="n">
-        <v>2.299530063212705</v>
+        <v>2.299530050081978</v>
       </c>
       <c r="O44" t="n">
-        <v>30.00071832204404</v>
+        <v>29.89907526110384</v>
       </c>
     </row>
     <row r="45">
@@ -3115,7 +3121,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>89.79499816894531</v>
+        <v>86.36000061035156</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3126,7 +3132,7 @@
         <v>264</v>
       </c>
       <c r="G45" t="n">
-        <v>18.213263</v>
+        <v>17.344433</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3160,7 +3166,7 @@
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>13.12363926663064</v>
+        <v>13.36924640344535</v>
       </c>
     </row>
     <row r="46">
@@ -3180,7 +3186,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>58.52999877929688</v>
+        <v>54.84999847412109</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3188,10 +3194,10 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="G46" t="n">
-        <v>17.579369</v>
+        <v>16.474087</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3225,7 +3231,7 @@
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="n">
-        <v>16.82089033227414</v>
+        <v>16.90175399346569</v>
       </c>
     </row>
     <row r="47">
@@ -3245,7 +3251,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>117.1600036621094</v>
+        <v>112.8000030517578</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3253,13 +3259,13 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="G47" t="n">
-        <v>10.479427</v>
+        <v>10.171326</v>
       </c>
       <c r="H47" t="n">
-        <v>9.737617999999999</v>
+        <v>9.375242</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3267,7 +3273,7 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>17.399</v>
+        <v>17.482</v>
       </c>
       <c r="K47" t="n">
         <v>729000000</v>
@@ -3276,13 +3282,13 @@
         <v>10.09835184082055</v>
       </c>
       <c r="M47" t="n">
-        <v>11.18</v>
+        <v>11.09</v>
       </c>
       <c r="N47" t="n">
-        <v>12.03169026163374</v>
+        <v>12.03168974750282</v>
       </c>
       <c r="O47" t="n">
-        <v>19.01172043149329</v>
+        <v>18.97785215991588</v>
       </c>
     </row>
     <row r="48">
@@ -3302,7 +3308,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>22.8799991607666</v>
+        <v>20.28000068664551</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3310,13 +3316,13 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="G48" t="n">
-        <v>18.15873</v>
+        <v>16.09524</v>
       </c>
       <c r="H48" t="n">
-        <v>13.894624</v>
+        <v>12.31569</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3336,10 +3342,10 @@
         <v>1.26</v>
       </c>
       <c r="N48" t="n">
-        <v>1.646679979304701</v>
+        <v>1.646680022527809</v>
       </c>
       <c r="O48" t="n">
-        <v>43.81739107242661</v>
+        <v>43.67635950829639</v>
       </c>
     </row>
     <row r="49">
@@ -3359,7 +3365,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>92.18000030517578</v>
+        <v>91.12999725341797</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3367,13 +3373,13 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G49" t="n">
-        <v>27.933334</v>
+        <v>28.126543</v>
       </c>
       <c r="H49" t="n">
-        <v>21.034761</v>
+        <v>20.797152</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3390,13 +3396,13 @@
         <v>24.93433392858717</v>
       </c>
       <c r="M49" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="N49" t="n">
-        <v>4.3822699152691</v>
+        <v>4.381849844316085</v>
       </c>
       <c r="O49" t="n">
-        <v>26.5085740709486</v>
+        <v>26.72957423061913</v>
       </c>
     </row>
     <row r="50">
@@ -3416,7 +3422,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>151.3999938964844</v>
+        <v>145.1399993896484</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3424,13 +3430,13 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="G50" t="n">
-        <v>22.330381</v>
+        <v>21.40708</v>
       </c>
       <c r="H50" t="n">
-        <v>15.69011</v>
+        <v>15.072418</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3438,7 +3444,7 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>49.523</v>
+        <v>49.508998</v>
       </c>
       <c r="K50" t="n">
         <v>8510000128</v>
@@ -3450,10 +3456,10 @@
         <v>6.78</v>
       </c>
       <c r="N50" t="n">
-        <v>9.649390214376085</v>
+        <v>9.629509969113677</v>
       </c>
       <c r="O50" t="n">
-        <v>28.67655366480765</v>
+        <v>29.00813799653272</v>
       </c>
     </row>
     <row r="51">
@@ -3473,7 +3479,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>116</v>
+        <v>108.9499969482422</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3481,13 +3487,13 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="G51" t="n">
-        <v>16.595137</v>
+        <v>15.586553</v>
       </c>
       <c r="H51" t="n">
-        <v>9.602649</v>
+        <v>9.019038999999999</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3507,10 +3513,10 @@
         <v>6.99</v>
       </c>
       <c r="N51" t="n">
-        <v>12.08000000833104</v>
+        <v>12.08000064621543</v>
       </c>
       <c r="O51" t="n">
-        <v>32.55049490979646</v>
+        <v>32.63783342051859</v>
       </c>
     </row>
     <row r="52">
@@ -3530,7 +3536,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>201.0099945068359</v>
+        <v>191.8699951171875</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3538,13 +3544,13 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="G52" t="n">
-        <v>38.730247</v>
+        <v>39.807053</v>
       </c>
       <c r="H52" t="n">
-        <v>35.280632</v>
+        <v>33.676407</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3552,7 +3558,7 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>58.645</v>
+        <v>58.89100000000001</v>
       </c>
       <c r="K52" t="n">
         <v>4334900224</v>
@@ -3561,13 +3567,13 @@
         <v>32.30178942852026</v>
       </c>
       <c r="M52" t="n">
-        <v>5.19</v>
+        <v>4.82</v>
       </c>
       <c r="N52" t="n">
-        <v>5.697460139229817</v>
+        <v>5.697460394667029</v>
       </c>
       <c r="O52" t="n">
-        <v>44.97310493028372</v>
+        <v>45.61026636009843</v>
       </c>
     </row>
     <row r="53">
@@ -3587,7 +3593,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>51.84000015258789</v>
+        <v>53.2400016784668</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3595,13 +3601,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G53" t="n">
-        <v>38.117645</v>
+        <v>39.731342</v>
       </c>
       <c r="H53" t="n">
-        <v>28.062576</v>
+        <v>24.929878</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3618,13 +3624,13 @@
         <v>6.252026138106316</v>
       </c>
       <c r="M53" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="N53" t="n">
-        <v>1.847300124998785</v>
+        <v>2.13559014121396</v>
       </c>
       <c r="O53" t="n">
-        <v>38.39322182106407</v>
+        <v>38.21628797521188</v>
       </c>
     </row>
     <row r="54">
@@ -3644,7 +3650,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>25.98999977111816</v>
+        <v>22.43000030517578</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3652,13 +3658,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="G54" t="n">
-        <v>11.3</v>
+        <v>10.288991</v>
       </c>
       <c r="H54" t="n">
-        <v>7.3150277</v>
+        <v>6.3130465</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3675,13 +3681,13 @@
         <v>23.02557930379152</v>
       </c>
       <c r="M54" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="N54" t="n">
-        <v>3.552959857023941</v>
+        <v>3.552959780222715</v>
       </c>
       <c r="O54" t="n">
-        <v>31.05410020544356</v>
+        <v>31.69576100303146</v>
       </c>
     </row>
     <row r="55">
@@ -3701,7 +3707,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>53.61999893188477</v>
+        <v>52.38000106811523</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3709,13 +3715,13 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="G55" t="n">
-        <v>21.362549</v>
+        <v>20.868526</v>
       </c>
       <c r="H55" t="n">
-        <v>16.452799</v>
+        <v>16.077496</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3735,10 +3741,10 @@
         <v>2.51</v>
       </c>
       <c r="N55" t="n">
-        <v>3.259019874483653</v>
+        <v>3.257970088632909</v>
       </c>
       <c r="O55" t="n">
-        <v>31.7570552164466</v>
+        <v>31.64522682631186</v>
       </c>
     </row>
     <row r="56">
@@ -3758,7 +3764,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>142.8800048828125</v>
+        <v>137</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -3766,13 +3772,13 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="G56" t="n">
-        <v>28.806452</v>
+        <v>27.620968</v>
       </c>
       <c r="H56" t="n">
-        <v>12.6381645</v>
+        <v>12.180593</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3792,10 +3798,10 @@
         <v>4.96</v>
       </c>
       <c r="N56" t="n">
-        <v>11.3054395583166</v>
+        <v>11.24739985976052</v>
       </c>
       <c r="O56" t="n">
-        <v>39.35595125772326</v>
+        <v>39.1194486617608</v>
       </c>
     </row>
     <row r="57">
@@ -3815,7 +3821,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>554.7000122070312</v>
+        <v>505.7999877929688</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -3823,13 +3829,13 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>234</v>
+        <v>256</v>
       </c>
       <c r="G57" t="n">
-        <v>25.375114</v>
+        <v>23.127571</v>
       </c>
       <c r="H57" t="n">
-        <v>20.611885</v>
+        <v>18.794827</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3846,13 +3852,13 @@
         <v>13.46170485686734</v>
       </c>
       <c r="M57" t="n">
-        <v>21.86</v>
+        <v>21.87</v>
       </c>
       <c r="N57" t="n">
-        <v>26.91165859925141</v>
+        <v>26.91165967066197</v>
       </c>
       <c r="O57" t="n">
-        <v>32.04741487484393</v>
+        <v>32.2598649281532</v>
       </c>
     </row>
     <row r="58">
@@ -3872,7 +3878,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>163.3300018310547</v>
+        <v>158.6199951171875</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -3880,13 +3886,13 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G58" t="n">
-        <v>29.428827</v>
+        <v>28.63177</v>
       </c>
       <c r="H58" t="n">
-        <v>21.896156</v>
+        <v>21.264303</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -3903,13 +3909,13 @@
         <v>18.97979108480482</v>
       </c>
       <c r="M58" t="n">
-        <v>5.55</v>
+        <v>5.54</v>
       </c>
       <c r="N58" t="n">
-        <v>7.459300245716859</v>
+        <v>7.45944953461148</v>
       </c>
       <c r="O58" t="n">
-        <v>22.92211367696139</v>
+        <v>22.97727012672365</v>
       </c>
     </row>
     <row r="59">
@@ -3929,7 +3935,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>167.0599975585938</v>
+        <v>156.2100067138672</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -3937,13 +3943,13 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="G59" t="n">
-        <v>27.843332</v>
+        <v>26.035002</v>
       </c>
       <c r="H59" t="n">
-        <v>17.769808</v>
+        <v>16.619888</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -3963,10 +3969,10 @@
         <v>6</v>
       </c>
       <c r="N59" t="n">
-        <v>9.401339483161198</v>
+        <v>9.398980709970319</v>
       </c>
       <c r="O59" t="n">
-        <v>31.15018059058458</v>
+        <v>30.81941553864065</v>
       </c>
     </row>
     <row r="60">
@@ -3986,7 +3992,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>64.33999633789062</v>
+        <v>62.65999984741211</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -3994,13 +4000,13 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="G60" t="n">
-        <v>42.328945</v>
+        <v>41.223686</v>
       </c>
       <c r="H60" t="n">
-        <v>18.290722</v>
+        <v>17.513556</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -4020,10 +4026,10 @@
         <v>1.52</v>
       </c>
       <c r="N60" t="n">
-        <v>3.517630213716584</v>
+        <v>3.577799953785063</v>
       </c>
       <c r="O60" t="n">
-        <v>50.7282659732462</v>
+        <v>50.13506673463911</v>
       </c>
     </row>
     <row r="61">
@@ -4043,7 +4049,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>370.5400085449219</v>
+        <v>353.8599853515625</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -4051,13 +4057,13 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="G61" t="n">
-        <v>35.22243</v>
+        <v>34.025</v>
       </c>
       <c r="H61" t="n">
-        <v>20.615908</v>
+        <v>19.687874</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -4065,22 +4071,22 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>68.893</v>
+        <v>68.633</v>
       </c>
       <c r="K61" t="n">
-        <v>1717882978304</v>
+        <v>1717882585088</v>
       </c>
       <c r="L61" t="n">
-        <v>45.09998975939252</v>
+        <v>45.09997633236109</v>
       </c>
       <c r="M61" t="n">
-        <v>10.52</v>
+        <v>10.4</v>
       </c>
       <c r="N61" t="n">
-        <v>17.97349932609914</v>
+        <v>17.97349908636973</v>
       </c>
       <c r="O61" t="n">
-        <v>38.60220831805844</v>
+        <v>37.49267264648747</v>
       </c>
     </row>
     <row r="62">
@@ -4100,7 +4106,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3992</v>
+        <v>3857</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -4108,13 +4114,13 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G62" t="n">
-        <v>49.283947</v>
+        <v>38.188118</v>
       </c>
       <c r="H62" t="n">
-        <v>30.931362</v>
+        <v>29.46963</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -4131,13 +4137,13 @@
         <v>15.41593591408773</v>
       </c>
       <c r="M62" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>129.0599489282108</v>
+        <v>130.8805030806291</v>
       </c>
       <c r="O62" t="n">
-        <v>41.71851973586736</v>
+        <v>42.36792457170424</v>
       </c>
     </row>
     <row r="63">
@@ -4157,7 +4163,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>689.4299926757812</v>
+        <v>681.3099975585938</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -4165,10 +4171,10 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G63" t="n">
-        <v>27.760637</v>
+        <v>27.421848</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4202,7 +4208,7 @@
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="n">
-        <v>19.38921069140605</v>
+        <v>19.11814478705992</v>
       </c>
     </row>
     <row r="64">
@@ -4222,7 +4228,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>17.13999938964844</v>
+        <v>14.27000045776367</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -4230,13 +4236,13 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="G64" t="n">
-        <v>26.36923</v>
+        <v>21.621212</v>
       </c>
       <c r="H64" t="n">
-        <v>25.021896</v>
+        <v>12.650709</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -4253,13 +4259,13 @@
         <v>8.500735439787386</v>
       </c>
       <c r="M64" t="n">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="N64" t="n">
-        <v>0.6850000251638979</v>
+        <v>1.128000055788468</v>
       </c>
       <c r="O64" t="n">
-        <v>80.45086479640956</v>
+        <v>80.91697969272178</v>
       </c>
     </row>
     <row r="65">
@@ -4279,7 +4285,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>122.9899978637695</v>
+        <v>123.3099975585938</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -4287,13 +4293,13 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G65" t="n">
-        <v>45.05128</v>
+        <v>46.708332</v>
       </c>
       <c r="H65" t="n">
-        <v>37.44592</v>
+        <v>37.465324</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -4310,13 +4316,13 @@
         <v>3.069845005111191</v>
       </c>
       <c r="M65" t="n">
-        <v>2.73</v>
+        <v>2.64</v>
       </c>
       <c r="N65" t="n">
-        <v>3.284469919921036</v>
+        <v>3.291310054027392</v>
       </c>
       <c r="O65" t="n">
-        <v>25.5166359682107</v>
+        <v>25.34512838756209</v>
       </c>
     </row>
     <row r="66">
@@ -4336,7 +4342,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3617</v>
+        <v>3379</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -4344,7 +4350,7 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4352,7 +4358,7 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>21.131216</v>
+        <v>19.709566</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -4360,22 +4366,22 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>26.009</v>
+        <v>32.217</v>
       </c>
       <c r="K66" t="n">
-        <v>-1523000064</v>
+        <v>-1275000064</v>
       </c>
       <c r="L66" t="n">
-        <v>-5.712678464457828</v>
+        <v>-6.874798192600785</v>
       </c>
       <c r="M66" t="n">
-        <v>-1.17</v>
+        <v>-0.79</v>
       </c>
       <c r="N66" t="n">
-        <v>171.1685688130773</v>
+        <v>171.4395943573796</v>
       </c>
       <c r="O66" t="n">
-        <v>36.74363771842292</v>
+        <v>37.01857233223282</v>
       </c>
     </row>
     <row r="67">
@@ -4395,7 +4401,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>375.3800048828125</v>
+        <v>346.5299987792969</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -4403,13 +4409,13 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G67" t="n">
-        <v>38.461063</v>
+        <v>35.57803</v>
       </c>
       <c r="H67" t="n">
-        <v>27.242867</v>
+        <v>25.049263</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -4426,13 +4432,13 @@
         <v>27.7840794311011</v>
       </c>
       <c r="M67" t="n">
-        <v>9.76</v>
+        <v>9.74</v>
       </c>
       <c r="N67" t="n">
-        <v>13.7790198396818</v>
+        <v>13.83393989592815</v>
       </c>
       <c r="O67" t="n">
-        <v>47.53700337820005</v>
+        <v>47.5785466340779</v>
       </c>
     </row>
     <row r="68">
@@ -4452,7 +4458,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1255.599975585938</v>
+        <v>1186</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -4460,13 +4466,13 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G68" t="n">
-        <v>50.75182</v>
+        <v>47.97735</v>
       </c>
       <c r="H68" t="n">
-        <v>33.63592</v>
+        <v>31.723621</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -4474,7 +4480,7 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>37.736</v>
+        <v>37.549</v>
       </c>
       <c r="K68" t="n">
         <v>9609400320</v>
@@ -4483,13 +4489,13 @@
         <v>29.41596142645869</v>
       </c>
       <c r="M68" t="n">
-        <v>24.74</v>
+        <v>24.72</v>
       </c>
       <c r="N68" t="n">
-        <v>37.32914026391838</v>
+        <v>37.38539178740031</v>
       </c>
       <c r="O68" t="n">
-        <v>37.31963012228753</v>
+        <v>37.41344610197102</v>
       </c>
     </row>
     <row r="69">
@@ -4509,7 +4515,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1469.589965820312</v>
+        <v>1368.359985351562</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -4517,13 +4523,13 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G69" t="n">
-        <v>50.003063</v>
+        <v>48.78289</v>
       </c>
       <c r="H69" t="n">
-        <v>33.391384</v>
+        <v>31.460503</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -4531,7 +4537,7 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>37.736</v>
+        <v>37.549</v>
       </c>
       <c r="K69" t="n">
         <v>9609400320</v>
@@ -4540,13 +4546,13 @@
         <v>29.41596142645869</v>
       </c>
       <c r="M69" t="n">
-        <v>29.39</v>
+        <v>28.05</v>
       </c>
       <c r="N69" t="n">
-        <v>44.01105284585726</v>
+        <v>43.49453616019942</v>
       </c>
       <c r="O69" t="n">
-        <v>41.29011791955085</v>
+        <v>40.98527955719306</v>
       </c>
     </row>
     <row r="70">
@@ -4566,7 +4572,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>397.2300109863281</v>
+        <v>410.6799926757812</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -4574,13 +4580,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="G70" t="n">
-        <v>24.873512</v>
+        <v>25.381952</v>
       </c>
       <c r="H70" t="n">
-        <v>21.073668</v>
+        <v>21.79571</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -4597,13 +4603,13 @@
         <v>39.04430486073013</v>
       </c>
       <c r="M70" t="n">
-        <v>15.97</v>
+        <v>16.18</v>
       </c>
       <c r="N70" t="n">
-        <v>18.84959044558964</v>
+        <v>18.84223971945769</v>
       </c>
       <c r="O70" t="n">
-        <v>26.37276626823514</v>
+        <v>26.51539250962787</v>
       </c>
     </row>
     <row r="71">
@@ -4623,7 +4629,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>320.9500122070312</v>
+        <v>319.7999877929688</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -4634,10 +4640,10 @@
         <v>84</v>
       </c>
       <c r="G71" t="n">
-        <v>30.107882</v>
+        <v>30.112993</v>
       </c>
       <c r="H71" t="n">
-        <v>22.087536</v>
+        <v>22.015726</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -4654,13 +4660,13 @@
         <v>49.74994619120307</v>
       </c>
       <c r="M71" t="n">
-        <v>10.66</v>
+        <v>10.62</v>
       </c>
       <c r="N71" t="n">
-        <v>14.53082010628217</v>
+        <v>14.52597964713808</v>
       </c>
       <c r="O71" t="n">
-        <v>23.7277467474399</v>
+        <v>23.87372526099652</v>
       </c>
     </row>
     <row r="72">
@@ -4680,7 +4686,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>332.6499938964844</v>
+        <v>332.7699890136719</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -4688,13 +4694,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G72" t="n">
-        <v>69.88445</v>
+        <v>66.68738</v>
       </c>
       <c r="H72" t="n">
-        <v>22.914656</v>
+        <v>19.474709</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -4702,22 +4708,22 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>54.789</v>
+        <v>54.603</v>
       </c>
       <c r="K72" t="n">
-        <v>23125999616</v>
+        <v>24971999232</v>
       </c>
       <c r="L72" t="n">
-        <v>36.19828725432142</v>
+        <v>36.57186295957928</v>
       </c>
       <c r="M72" t="n">
-        <v>4.76</v>
+        <v>4.99</v>
       </c>
       <c r="N72" t="n">
-        <v>14.51690978457125</v>
+        <v>17.08728941796624</v>
       </c>
       <c r="O72" t="n">
-        <v>50.73381881235107</v>
+        <v>49.16193897619095</v>
       </c>
     </row>
     <row r="73">
@@ -4737,7 +4743,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>532.2999877929688</v>
+        <v>534.469970703125</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -4745,13 +4751,13 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>59</v>
+        <v>56.99999999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>18.795904</v>
+        <v>19.232456</v>
       </c>
       <c r="H73" t="n">
-        <v>16.00213</v>
+        <v>16.067366</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -4768,13 +4774,13 @@
         <v>8.973544608905701</v>
       </c>
       <c r="M73" t="n">
-        <v>28.32</v>
+        <v>27.79</v>
       </c>
       <c r="N73" t="n">
-        <v>33.26432092433749</v>
+        <v>33.26431791639806</v>
       </c>
       <c r="O73" t="n">
-        <v>27.5796235900371</v>
+        <v>26.86538750222751</v>
       </c>
     </row>
     <row r="74">
@@ -4794,7 +4800,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>18.36000061035156</v>
+        <v>18.1299991607666</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -4802,13 +4808,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="G74" t="n">
-        <v>15.559323</v>
+        <v>16.044247</v>
       </c>
       <c r="H74" t="n">
-        <v>10.212425</v>
+        <v>10.064506</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -4825,13 +4831,13 @@
         <v>10.39903721413522</v>
       </c>
       <c r="M74" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="N74" t="n">
-        <v>1.797810080402212</v>
+        <v>1.801379934670077</v>
       </c>
       <c r="O74" t="n">
-        <v>28.18521055216054</v>
+        <v>28.20647361024212</v>
       </c>
     </row>
     <row r="75">
@@ -4851,7 +4857,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>526.4099731445312</v>
+        <v>524.6599731445312</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -4859,13 +4865,13 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G75" t="n">
-        <v>31.845732</v>
+        <v>31.644148</v>
       </c>
       <c r="H75" t="n">
-        <v>23.27283</v>
+        <v>23.182648</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -4882,13 +4888,13 @@
         <v>45.64667424051743</v>
       </c>
       <c r="M75" t="n">
-        <v>16.53</v>
+        <v>16.58</v>
       </c>
       <c r="N75" t="n">
-        <v>22.61907869152704</v>
+        <v>22.63158087654746</v>
       </c>
       <c r="O75" t="n">
-        <v>23.51867704211811</v>
+        <v>23.96401785613576</v>
       </c>
     </row>
     <row r="76">
@@ -4908,7 +4914,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>264.5799865722656</v>
+        <v>260.2900085449219</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -4916,13 +4922,13 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G76" t="n">
-        <v>33.4488</v>
+        <v>33.242657</v>
       </c>
       <c r="H76" t="n">
-        <v>28.452002</v>
+        <v>27.943462</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -4939,13 +4945,13 @@
         <v>27.03682291889199</v>
       </c>
       <c r="M76" t="n">
-        <v>7.91</v>
+        <v>7.83</v>
       </c>
       <c r="N76" t="n">
-        <v>9.299169407209574</v>
+        <v>9.314880473468959</v>
       </c>
       <c r="O76" t="n">
-        <v>32.42995163677143</v>
+        <v>32.44612456451752</v>
       </c>
     </row>
     <row r="77">
@@ -4965,7 +4971,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>314.9800109863281</v>
+        <v>300.8800048828125</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -4973,13 +4979,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G77" t="n">
-        <v>29.164816</v>
+        <v>28.014898</v>
       </c>
       <c r="H77" t="n">
-        <v>23.526636</v>
+        <v>22.431484</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -4996,13 +5002,13 @@
         <v>32.80987782321161</v>
       </c>
       <c r="M77" t="n">
-        <v>10.8</v>
+        <v>10.74</v>
       </c>
       <c r="N77" t="n">
-        <v>13.38822987639746</v>
+        <v>13.41329021667993</v>
       </c>
       <c r="O77" t="n">
-        <v>31.14107116368039</v>
+        <v>30.92041776641582</v>
       </c>
     </row>
     <row r="78">
@@ -5022,7 +5028,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>189.8200073242188</v>
+        <v>183.3399963378906</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -5033,10 +5039,10 @@
         <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>46.98515</v>
+        <v>37.416325</v>
       </c>
       <c r="H78" t="n">
-        <v>24.464714</v>
+        <v>17.067266</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -5044,22 +5050,22 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>60.220003</v>
+        <v>61.698</v>
       </c>
       <c r="K78" t="n">
-        <v>99198001152</v>
+        <v>120066998272</v>
       </c>
       <c r="L78" t="n">
-        <v>53.0068092592338</v>
+        <v>55.60253144772194</v>
       </c>
       <c r="M78" t="n">
-        <v>4.04</v>
+        <v>4.9</v>
       </c>
       <c r="N78" t="n">
-        <v>7.758930160565897</v>
+        <v>10.74220067454803</v>
       </c>
       <c r="O78" t="n">
-        <v>44.44061078893194</v>
+        <v>42.41813254917302</v>
       </c>
     </row>
     <row r="79">
@@ -5078,18 +5084,18 @@
           <t>GC=F</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Error: single positional indexer is out-of-bounds</t>
-        </is>
+      <c r="D79" t="n">
+        <v>5139.2998046875</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>0</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5126,15 +5132,9 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="n">
+        <v>26.0047590425187</v>
       </c>
     </row>
     <row r="80">
@@ -5221,7 +5221,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6.357999801635742</v>
+        <v>6.342000007629395</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
-        <v>2.322358854734227</v>
+        <v>2.335855093945712</v>
       </c>
     </row>
     <row r="82">
@@ -5288,7 +5288,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>6.47599983215332</v>
+        <v>6.48199987411499</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
-        <v>2.539682142606309</v>
+        <v>2.545097131547008</v>
       </c>
     </row>
     <row r="83">
@@ -5430,7 +5430,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>25.83499908447266</v>
+        <v>24.08250045776367</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>36.41737</v>
+        <v>33.947025</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="n">
-        <v>25.69922098947354</v>
+        <v>25.30309672753317</v>
       </c>
     </row>
     <row r="85">
@@ -5566,7 +5566,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>76.62000274658203</v>
+        <v>74.26999664306641</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -5613,7 +5613,7 @@
       </c>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="n">
-        <v>53.75775803040747</v>
+        <v>55.03924362920414</v>
       </c>
     </row>
     <row r="87">
@@ -5633,7 +5633,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>171.3999938964844</v>
+        <v>167.3999938964844</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -5641,13 +5641,13 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>53</v>
+        <v>56.00000000000001</v>
       </c>
       <c r="G87" t="n">
-        <v>61.654675</v>
+        <v>58.736843</v>
       </c>
       <c r="H87" t="n">
-        <v>19.274258</v>
+        <v>15.195209</v>
       </c>
       <c r="I87" t="inlineStr">
         <is>
@@ -5655,22 +5655,22 @@
         </is>
       </c>
       <c r="J87" t="n">
-        <v>30.283</v>
+        <v>28.323</v>
       </c>
       <c r="K87" t="n">
-        <v>960000000</v>
+        <v>752000000</v>
       </c>
       <c r="L87" t="n">
-        <v>5.5843173545811</v>
+        <v>4.239485757810209</v>
       </c>
       <c r="M87" t="n">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="N87" t="n">
-        <v>8.892689612045475</v>
+        <v>11.01662990594498</v>
       </c>
       <c r="O87" t="n">
-        <v>58.48037528183523</v>
+        <v>55.25950799334925</v>
       </c>
     </row>
     <row r="88">
@@ -5690,7 +5690,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>16.25</v>
+        <v>13.69999980926514</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>224.13794</v>
+        <v>188.96552</v>
       </c>
       <c r="I88" t="inlineStr">
         <is>
@@ -5725,13 +5725,13 @@
         <v>-156.4603015075377</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="N88" t="n">
-        <v>0.07249999710000012</v>
+        <v>0.07249999793224254</v>
       </c>
       <c r="O88" t="n">
-        <v>75.83129674543078</v>
+        <v>75.34783954981718</v>
       </c>
     </row>
     <row r="89">
@@ -5751,7 +5751,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>487.5400085449219</v>
+        <v>487.2300109863281</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="n">
-        <v>23.33750277804529</v>
+        <v>23.79745147986449</v>
       </c>
     </row>
     <row r="90">
@@ -5820,7 +5820,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>168.4199981689453</v>
+        <v>163.9299926757812</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>19.371313</v>
+        <v>18.866924</v>
       </c>
       <c r="I90" t="inlineStr">
         <is>
@@ -5853,13 +5853,13 @@
         <v>-13.1715570367568</v>
       </c>
       <c r="M90" t="n">
-        <v>-5.76</v>
+        <v>-5.61</v>
       </c>
       <c r="N90" t="n">
-        <v>8.694299563945165</v>
+        <v>8.688750358870436</v>
       </c>
       <c r="O90" t="n">
-        <v>64.11628191392398</v>
+        <v>64.55432461041862</v>
       </c>
     </row>
     <row r="91">
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>31.64999961853027</v>
+        <v>30.76000022888184</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -5890,7 +5890,7 @@
         <v>428</v>
       </c>
       <c r="G91" t="n">
-        <v>17.755882</v>
+        <v>17.256586</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="n">
-        <v>16.24804692320324</v>
+        <v>16.25656520058645</v>
       </c>
     </row>
     <row r="92">
@@ -5944,7 +5944,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>9.645999908447266</v>
+        <v>8.937000274658203</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -5955,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>24.72293</v>
+        <v>22.905746</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="N92" t="inlineStr"/>
       <c r="O92" t="n">
-        <v>16.40510607052377</v>
+        <v>16.62570795405736</v>
       </c>
     </row>
     <row r="93">
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>90.12999725341797</v>
+        <v>85.77999877929688</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -6017,13 +6017,13 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="G93" t="n">
-        <v>24.2938</v>
+        <v>23.630854</v>
       </c>
       <c r="H93" t="n">
-        <v>17.764437</v>
+        <v>16.90706</v>
       </c>
       <c r="I93" t="inlineStr">
         <is>
@@ -6040,13 +6040,13 @@
         <v>2.175543896079772</v>
       </c>
       <c r="M93" t="n">
-        <v>3.71</v>
+        <v>3.63</v>
       </c>
       <c r="N93" t="n">
-        <v>5.073619684846639</v>
+        <v>5.07362006045385</v>
       </c>
       <c r="O93" t="n">
-        <v>22.99644795253068</v>
+        <v>23.33025334165441</v>
       </c>
     </row>
     <row r="94">
@@ -6066,7 +6066,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>243.9700012207031</v>
+        <v>238.3800048828125</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -6074,13 +6074,13 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="G94" t="n">
-        <v>32.271164</v>
+        <v>31.44855</v>
       </c>
       <c r="H94" t="n">
-        <v>21.230309</v>
+        <v>20.735928</v>
       </c>
       <c r="I94" t="inlineStr">
         <is>
@@ -6097,13 +6097,13 @@
         <v>11.81827913077981</v>
       </c>
       <c r="M94" t="n">
-        <v>7.56</v>
+        <v>7.58</v>
       </c>
       <c r="N94" t="n">
-        <v>11.49158974656013</v>
+        <v>11.49598922617847</v>
       </c>
       <c r="O94" t="n">
-        <v>24.96504910934104</v>
+        <v>25.21608699088841</v>
       </c>
     </row>
     <row r="95">
@@ -6123,7 +6123,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>35.68000030517578</v>
+        <v>33.75</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -6131,13 +6131,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>401</v>
+        <v>421</v>
       </c>
       <c r="G95" t="n">
-        <v>14.102767</v>
+        <v>13.339921</v>
       </c>
       <c r="H95" t="n">
-        <v>11.647607</v>
+        <v>11.019185</v>
       </c>
       <c r="I95" t="inlineStr">
         <is>
@@ -6157,10 +6157,10 @@
         <v>2.53</v>
       </c>
       <c r="N95" t="n">
-        <v>3.063290193872079</v>
+        <v>3.062839946874474</v>
       </c>
       <c r="O95" t="n">
-        <v>19.96586561308679</v>
+        <v>20.58682858215199</v>
       </c>
     </row>
     <row r="96">
@@ -6180,7 +6180,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>37.90000152587891</v>
+        <v>35.2400016784668</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -6198,7 +6198,7 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>21.264778</v>
+        <v>18.731829</v>
       </c>
       <c r="I96" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="J96" t="n">
-        <v>-22.825001</v>
+        <v>-18.535</v>
       </c>
       <c r="K96" t="n">
         <v>-405448000</v>
@@ -6215,13 +6215,13 @@
         <v>-34.23108133825271</v>
       </c>
       <c r="M96" t="n">
-        <v>-9.630000000000001</v>
+        <v>-6.38</v>
       </c>
       <c r="N96" t="n">
-        <v>1.782290016189161</v>
+        <v>1.881289951903084</v>
       </c>
       <c r="O96" t="n">
-        <v>105.670745485795</v>
+        <v>106.7639599704333</v>
       </c>
     </row>
     <row r="97">
@@ -6241,7 +6241,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>38.40999984741211</v>
+        <v>37.2599983215332</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -6249,13 +6249,13 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="G97" t="n">
-        <v>21.458101</v>
+        <v>21.917646</v>
       </c>
       <c r="H97" t="n">
-        <v>11.461189</v>
+        <v>12.14187</v>
       </c>
       <c r="I97" t="inlineStr">
         <is>
@@ -6263,22 +6263,22 @@
         </is>
       </c>
       <c r="J97" t="n">
-        <v>36.222</v>
+        <v>44.053</v>
       </c>
       <c r="K97" t="n">
-        <v>435344000</v>
+        <v>791065984</v>
       </c>
       <c r="L97" t="n">
-        <v>30.92289680433018</v>
+        <v>45.68307630671112</v>
       </c>
       <c r="M97" t="n">
-        <v>1.79</v>
+        <v>1.7</v>
       </c>
       <c r="N97" t="n">
-        <v>3.351310221601974</v>
+        <v>3.068719918886728</v>
       </c>
       <c r="O97" t="n">
-        <v>43.88925848484119</v>
+        <v>45.683204830093</v>
       </c>
     </row>
     <row r="98">
@@ -6298,7 +6298,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>2.299999952316284</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -6306,13 +6306,13 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>640</v>
+        <v>657</v>
       </c>
       <c r="G98" t="n">
-        <v>5.2272725</v>
+        <v>5.214286</v>
       </c>
       <c r="H98" t="n">
-        <v>15.333332</v>
+        <v>14.599999</v>
       </c>
       <c r="I98" t="inlineStr">
         <is>
@@ -6329,13 +6329,13 @@
         <v>9.473367521098524</v>
       </c>
       <c r="M98" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="N98" t="n">
-        <v>0.1500000099336716</v>
+        <v>0.1500000141931831</v>
       </c>
       <c r="O98" t="n">
-        <v>29.73393804765353</v>
+        <v>30.15583432749423</v>
       </c>
     </row>
     <row r="99">
@@ -6355,7 +6355,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>8.090000152587891</v>
+        <v>7.25</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -6363,13 +6363,13 @@
         </is>
       </c>
       <c r="F99" t="n">
-        <v>692</v>
+        <v>772</v>
       </c>
       <c r="G99" t="n">
-        <v>9.517647</v>
+        <v>8.529411</v>
       </c>
       <c r="H99" t="n">
-        <v>11.826448</v>
+        <v>10.947692</v>
       </c>
       <c r="I99" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         </is>
       </c>
       <c r="J99" t="n">
-        <v>23.271999</v>
+        <v>22.573</v>
       </c>
       <c r="K99" t="n">
         <v>165075008</v>
@@ -6389,10 +6389,10 @@
         <v>0.85</v>
       </c>
       <c r="N99" t="n">
-        <v>0.6840600113058368</v>
+        <v>0.6622400410972468</v>
       </c>
       <c r="O99" t="n">
-        <v>39.61075547688601</v>
+        <v>39.90676271380941</v>
       </c>
     </row>
     <row r="100">
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>59.02000045776367</v>
+        <v>60.86000061035156</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -6425,10 +6425,10 @@
         </is>
       </c>
       <c r="G100" t="n">
-        <v>8.730769</v>
+        <v>9.0700445</v>
       </c>
       <c r="H100" t="n">
-        <v>12.083382</v>
+        <v>9.105297999999999</v>
       </c>
       <c r="I100" t="inlineStr">
         <is>
@@ -6436,22 +6436,22 @@
         </is>
       </c>
       <c r="J100" t="n">
-        <v>61.33300000000001</v>
+        <v>84.817004</v>
       </c>
       <c r="K100" t="n">
-        <v>727139008</v>
+        <v>719062976</v>
       </c>
       <c r="L100" t="n">
-        <v>32.65910753432706</v>
+        <v>29.06247878907776</v>
       </c>
       <c r="M100" t="n">
-        <v>6.76</v>
+        <v>6.71</v>
       </c>
       <c r="N100" t="n">
-        <v>4.884394158668796</v>
+        <v>6.684020732803206</v>
       </c>
       <c r="O100" t="n">
-        <v>55.87776580615891</v>
+        <v>55.07996475717841</v>
       </c>
     </row>
     <row r="101">
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>239.6000061035156</v>
+        <v>221.4799957275391</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -6479,13 +6479,13 @@
         </is>
       </c>
       <c r="F101" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="G101" t="n">
-        <v>12.88865</v>
+        <v>12.884234</v>
       </c>
       <c r="H101" t="n">
-        <v>15.183778</v>
+        <v>14.035488</v>
       </c>
       <c r="I101" t="inlineStr">
         <is>
@@ -6502,13 +6502,13 @@
         <v>7.325137888259277</v>
       </c>
       <c r="M101" t="n">
-        <v>18.59</v>
+        <v>17.19</v>
       </c>
       <c r="N101" t="n">
-        <v>15.7799992928977</v>
+        <v>15.77999964999714</v>
       </c>
       <c r="O101" t="n">
-        <v>31.18082334693826</v>
+        <v>31.09941596627081</v>
       </c>
     </row>
     <row r="102">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>44.11000061035156</v>
+        <v>45.95000076293945</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>44.502514</v>
+        <v>46.358887</v>
       </c>
       <c r="I102" t="inlineStr">
         <is>
@@ -6566,10 +6566,10 @@
         <v>-0.06</v>
       </c>
       <c r="N102" t="n">
-        <v>0.9911799726719162</v>
+        <v>0.9911799815845331</v>
       </c>
       <c r="O102" t="n">
-        <v>67.02616062391348</v>
+        <v>66.8717892332506</v>
       </c>
     </row>
     <row r="103">
@@ -6589,7 +6589,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>121.3499984741211</v>
+        <v>114.2399978637695</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -6597,13 +6597,13 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G103" t="n">
-        <v>121.35</v>
+        <v>115.393936</v>
       </c>
       <c r="H103" t="n">
-        <v>65.95817599999999</v>
+        <v>61.46383</v>
       </c>
       <c r="I103" t="inlineStr">
         <is>
@@ -6620,13 +6620,13 @@
         <v>16.93246293130341</v>
       </c>
       <c r="M103" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="N103" t="n">
-        <v>1.839802217607126</v>
+        <v>1.858654071244332</v>
       </c>
       <c r="O103" t="n">
-        <v>52.88988521258774</v>
+        <v>53.32752348877126</v>
       </c>
     </row>
     <row r="104">
@@ -6646,7 +6646,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>38.81000137329102</v>
+        <v>35.58000183105469</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -6654,10 +6654,10 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="G104" t="n">
-        <v>10.920676</v>
+        <v>9.862434</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -6691,7 +6691,7 @@
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="n">
-        <v>25.27361934636467</v>
+        <v>24.43731726035189</v>
       </c>
     </row>
     <row r="105">
@@ -6711,7 +6711,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>10.96500015258789</v>
+        <v>10.04500007629395</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -6719,13 +6719,13 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>413.9999999999999</v>
+        <v>494.0000000000001</v>
       </c>
       <c r="G105" t="n">
-        <v>13.879746</v>
+        <v>12.55625</v>
       </c>
       <c r="H105" t="n">
-        <v>11.04452</v>
+        <v>9.967057</v>
       </c>
       <c r="I105" t="inlineStr">
         <is>
@@ -6736,19 +6736,19 @@
         <v>0</v>
       </c>
       <c r="K105" t="n">
-        <v>5890999808</v>
+        <v>5610999808</v>
       </c>
       <c r="L105" t="n">
-        <v>38.48314416960512</v>
+        <v>36.54184225438188</v>
       </c>
       <c r="M105" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="N105" t="n">
-        <v>0.9928000630709067</v>
+        <v>1.007820069283636</v>
       </c>
       <c r="O105" t="n">
-        <v>28.8147667736332</v>
+        <v>28.3863435644206</v>
       </c>
     </row>
     <row r="106">
@@ -6768,7 +6768,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>27.22500038146973</v>
+        <v>26.75</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -6817,7 +6817,7 @@
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
-        <v>14.48867354500374</v>
+        <v>14.3612290862041</v>
       </c>
     </row>
   </sheetData>
